--- a/DuAn/exps/feature1/x_train.xlsx
+++ b/DuAn/exps/feature1/x_train.xlsx
@@ -458,7 +458,7 @@
         <v>0.1510333721369793</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.723970631989554</v>
+        <v>-0.7239706319895539</v>
       </c>
       <c r="D2" t="n">
         <v>-0.4703605420011441</v>
@@ -486,7 +486,7 @@
         <v>0.1464317990183076</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.8443816968529017</v>
+        <v>-0.8443816968529015</v>
       </c>
       <c r="D4" t="n">
         <v>-0.548281314805785</v>
@@ -511,10 +511,10 @@
         <v>0.3927451245729815</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4582781854621169</v>
+        <v>0.458278185462117</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004370029534162015</v>
+        <v>0.004370029534162021</v>
       </c>
       <c r="D6" t="n">
         <v>0.6072446677955451</v>
@@ -556,7 +556,7 @@
         <v>0.3368753437401359</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3951380807380031</v>
+        <v>-0.395138080738003</v>
       </c>
       <c r="D9" t="n">
         <v>-1.26971938228948</v>
@@ -570,7 +570,7 @@
         <v>0.1315664940364277</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.8603689321724278</v>
+        <v>-0.8603689321724277</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5373111999638024</v>
@@ -584,7 +584,7 @@
         <v>1.117038708882364</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.093888535103317</v>
+        <v>-1.093888535103316</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1598545017312903</v>
@@ -595,7 +595,7 @@
         <v>1.246159451451268</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3070113215883451</v>
+        <v>-0.307011321588345</v>
       </c>
       <c r="C12" t="n">
         <v>-0.1073517195330397</v>
@@ -612,7 +612,7 @@
         <v>0.1945687014567541</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2603246822698028</v>
+        <v>-0.2603246822698027</v>
       </c>
       <c r="D13" t="n">
         <v>0.4909605088297694</v>
@@ -626,7 +626,7 @@
         <v>-0.1852441173852201</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7358666726699458</v>
+        <v>0.7358666726699457</v>
       </c>
       <c r="D14" t="n">
         <v>1.149685301766164</v>
@@ -657,7 +657,7 @@
         <v>-1.059333991905493</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.04294980150535438</v>
+        <v>-0.04294980150535439</v>
       </c>
     </row>
     <row r="17">
@@ -696,7 +696,7 @@
         <v>-0.902042623247955</v>
       </c>
       <c r="C19" t="n">
-        <v>0.484010125482079</v>
+        <v>0.4840101254820789</v>
       </c>
       <c r="D19" t="n">
         <v>0.9627931521298967</v>
@@ -713,7 +713,7 @@
         <v>-0.2697995380146458</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05502791946531516</v>
+        <v>0.05502791946531515</v>
       </c>
     </row>
     <row r="21">
@@ -724,7 +724,7 @@
         <v>0.1213027621732195</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.006687424289141346</v>
+        <v>-0.006687424289141338</v>
       </c>
       <c r="D21" t="n">
         <v>0.4824386599611047</v>
@@ -738,7 +738,7 @@
         <v>0.6848329601226661</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.7768851558064871</v>
+        <v>-0.776885155806487</v>
       </c>
       <c r="D22" t="n">
         <v>0.5378396231946353</v>
@@ -752,7 +752,7 @@
         <v>-0.4061247589473923</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6527745144602473</v>
+        <v>0.6527745144602471</v>
       </c>
       <c r="D23" t="n">
         <v>0.1019310456695347</v>
@@ -791,10 +791,10 @@
         <v>1.757564198973764</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.081884916278759</v>
+        <v>-0.08188491627875898</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3029594598490049</v>
+        <v>-0.3029594598490048</v>
       </c>
       <c r="D26" t="n">
         <v>1.476622973280018</v>
@@ -819,10 +819,10 @@
         <v>-0.09162148073872899</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.4255933476699211</v>
+        <v>-0.425593347669921</v>
       </c>
       <c r="C28" t="n">
-        <v>1.467386352167862</v>
+        <v>1.467386352167861</v>
       </c>
       <c r="D28" t="n">
         <v>0.9968852558083502</v>
@@ -836,7 +836,7 @@
         <v>0.6476611445580804</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.8264133343900335</v>
+        <v>-0.8264133343900334</v>
       </c>
       <c r="D29" t="n">
         <v>0.2553478663244731</v>
@@ -850,7 +850,7 @@
         <v>0.3538618199737456</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.419161968405492</v>
+        <v>-1.419161968405491</v>
       </c>
       <c r="D30" t="n">
         <v>-0.4253030316845027</v>
@@ -864,7 +864,7 @@
         <v>1.159855576971714</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.09471857853991558</v>
+        <v>-0.09471857853991557</v>
       </c>
       <c r="D31" t="n">
         <v>-1.421323544483404</v>
@@ -878,7 +878,7 @@
         <v>-1.043288679905472</v>
       </c>
       <c r="C32" t="n">
-        <v>0.675281040263096</v>
+        <v>0.6752810402630959</v>
       </c>
       <c r="D32" t="n">
         <v>1.294603814571412</v>
@@ -892,7 +892,7 @@
         <v>0.8253605555497586</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.6683147810789268</v>
+        <v>-0.6683147810789267</v>
       </c>
       <c r="D33" t="n">
         <v>0.3058810176545161</v>
@@ -920,7 +920,7 @@
         <v>0.9591654066064497</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.7600916478123451</v>
+        <v>-0.760091647812345</v>
       </c>
       <c r="D35" t="n">
         <v>0.3923330557354116</v>
@@ -948,7 +948,7 @@
         <v>0.9510228459949711</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3783606981973534</v>
+        <v>-0.3783606981973533</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2164941933832439</v>
@@ -962,7 +962,7 @@
         <v>-2.135999786502162</v>
       </c>
       <c r="C38" t="n">
-        <v>1.754189060709794</v>
+        <v>1.754189060709793</v>
       </c>
       <c r="D38" t="n">
         <v>-0.5342979495351032</v>
@@ -976,7 +976,7 @@
         <v>1.305703206747903</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3789527327041427</v>
+        <v>-0.3789527327041426</v>
       </c>
       <c r="D39" t="n">
         <v>-0.2146579939032553</v>
@@ -987,10 +987,10 @@
         <v>-0.8492878219416268</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.3112587959577361</v>
+        <v>-0.311258795957736</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.02523169580530643</v>
+        <v>-0.02523169580530642</v>
       </c>
       <c r="D40" t="n">
         <v>0.3941598388078105</v>
@@ -1029,10 +1029,10 @@
         <v>-0.06172800993418103</v>
       </c>
       <c r="B43" t="n">
-        <v>0.4890864872715136</v>
+        <v>0.4890864872715137</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.498706526846881</v>
+        <v>-1.49870652684688</v>
       </c>
       <c r="D43" t="n">
         <v>-2.365600897576988</v>
@@ -1060,7 +1060,7 @@
         <v>-2.049271252258053</v>
       </c>
       <c r="C45" t="n">
-        <v>1.639905668173527</v>
+        <v>1.639905668173526</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3132948634052029</v>
@@ -1074,7 +1074,7 @@
         <v>0.8497882373841942</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.7389903400995411</v>
+        <v>-0.738990340099541</v>
       </c>
       <c r="D46" t="n">
         <v>0.5080089147708936</v>
@@ -1088,7 +1088,7 @@
         <v>0.1435921665361533</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.6923877795067436</v>
+        <v>-0.6923877795067435</v>
       </c>
       <c r="D47" t="n">
         <v>-0.5762951273850973</v>
@@ -1102,7 +1102,7 @@
         <v>1.038811965864945</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3698717987517548</v>
+        <v>-0.3698717987517547</v>
       </c>
       <c r="D48" t="n">
         <v>-0.9707955233549386</v>
@@ -1116,7 +1116,7 @@
         <v>0.7867689237440957</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3584250304084226</v>
+        <v>-0.3584250304084225</v>
       </c>
       <c r="D49" t="n">
         <v>-2.661464424044882</v>
@@ -1144,7 +1144,7 @@
         <v>0.5460673053320912</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.8982637478793738</v>
+        <v>-0.8982637478793737</v>
       </c>
       <c r="D51" t="n">
         <v>0.8258079627189582</v>
@@ -1158,7 +1158,7 @@
         <v>0.1220041171838721</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.8959140389419219</v>
+        <v>-0.8959140389419218</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4831197742851668</v>
@@ -1172,7 +1172,7 @@
         <v>-0.1339220368252246</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6589021867873279</v>
+        <v>0.6589021867873278</v>
       </c>
       <c r="D53" t="n">
         <v>0.9944511144464167</v>
@@ -1200,7 +1200,7 @@
         <v>-0.6404543104943218</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4336272345879517</v>
+        <v>-0.4336272345879516</v>
       </c>
       <c r="D55" t="n">
         <v>0.4696511784543129</v>
@@ -1214,7 +1214,7 @@
         <v>0.5793389027886579</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.7322637223570314</v>
+        <v>-0.7322637223570313</v>
       </c>
       <c r="D56" t="n">
         <v>0.6796935661498203</v>
@@ -1242,7 +1242,7 @@
         <v>-0.2992245703481244</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2646670365316625</v>
+        <v>-0.2646670365316624</v>
       </c>
       <c r="D58" t="n">
         <v>0.7271805096246003</v>
@@ -1267,10 +1267,10 @@
         <v>-0.2518418062916544</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.3770989252382396</v>
+        <v>-0.3770989252382395</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8177839764109185</v>
+        <v>0.8177839764109184</v>
       </c>
       <c r="D60" t="n">
         <v>0.6413358298332397</v>
@@ -1284,7 +1284,7 @@
         <v>-0.5165642244174898</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8880679172752908</v>
+        <v>0.8880679172752907</v>
       </c>
       <c r="D61" t="n">
         <v>0.4306860838481975</v>
@@ -1298,7 +1298,7 @@
         <v>-0.2765690928820695</v>
       </c>
       <c r="C62" t="n">
-        <v>0.01029037460205572</v>
+        <v>0.01029037460205573</v>
       </c>
       <c r="D62" t="n">
         <v>1.131417471042176</v>
@@ -1312,7 +1312,7 @@
         <v>-1.58593218351329</v>
       </c>
       <c r="C63" t="n">
-        <v>1.197169824360885</v>
+        <v>1.197169824360884</v>
       </c>
       <c r="D63" t="n">
         <v>0.5086162730604283</v>
@@ -1326,10 +1326,10 @@
         <v>1.056499797109208</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.9174069648109678</v>
+        <v>-0.9174069648109677</v>
       </c>
       <c r="D64" t="n">
-        <v>0.08181759905796818</v>
+        <v>0.08181759905796816</v>
       </c>
     </row>
     <row r="65">
@@ -1337,10 +1337,10 @@
         <v>0.8671985608820834</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03811521542191693</v>
+        <v>0.03811521542191696</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.002540879105402566</v>
+        <v>-0.002540879105402559</v>
       </c>
       <c r="D65" t="n">
         <v>0.5512335213502029</v>
@@ -1382,7 +1382,7 @@
         <v>-1.058855339898004</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4938927248366564</v>
+        <v>0.4938927248366563</v>
       </c>
       <c r="D68" t="n">
         <v>0.5317514448675247</v>
@@ -1410,7 +1410,7 @@
         <v>1.482684156509156</v>
       </c>
       <c r="C70" t="n">
-        <v>0.07956071553262517</v>
+        <v>0.07956071553262516</v>
       </c>
       <c r="D70" t="n">
         <v>-0.7979102800083272</v>
@@ -1421,10 +1421,10 @@
         <v>-0.9232254361403975</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.0741015862824928</v>
+        <v>-0.07410158628249278</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3021697733551239</v>
+        <v>-0.3021697733551238</v>
       </c>
       <c r="D71" t="n">
         <v>-0.2213436432919315</v>
@@ -1435,10 +1435,10 @@
         <v>1.213022243383953</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.1877210980082077</v>
+        <v>-0.1877210980082076</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1316297415838303</v>
+        <v>-0.1316297415838302</v>
       </c>
       <c r="D72" t="n">
         <v>0.8872971042795995</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.005725628916254537</v>
+        <v>0.005725628916254535</v>
       </c>
       <c r="B75" t="n">
         <v>0.2635922982368293</v>
@@ -1494,7 +1494,7 @@
         <v>-1.767155475778003</v>
       </c>
       <c r="C76" t="n">
-        <v>2.579651024981525</v>
+        <v>2.579651024981524</v>
       </c>
       <c r="D76" t="n">
         <v>-0.1421987375006314</v>
@@ -1505,13 +1505,13 @@
         <v>-1.396034259166328</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1453712133924427</v>
+        <v>0.1453712133924428</v>
       </c>
       <c r="C77" t="n">
         <v>-0.2769039520961182</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0003405571620309882</v>
+        <v>-0.0003405571620309958</v>
       </c>
     </row>
     <row r="78">
@@ -1522,7 +1522,7 @@
         <v>0.1071388122019922</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.951961508008791</v>
+        <v>-0.9519615080087909</v>
       </c>
       <c r="D78" t="n">
         <v>0.2596134989626003</v>
@@ -1578,7 +1578,7 @@
         <v>0.2388224920069535</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.226923526414936</v>
+        <v>-1.226923526414935</v>
       </c>
       <c r="D82" t="n">
         <v>-0.2371632080426019</v>
@@ -1659,10 +1659,10 @@
         <v>-0.3398006235237652</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.04329328447309614</v>
+        <v>-0.04329328447309611</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.8301682614175304</v>
+        <v>-0.8301682614175303</v>
       </c>
       <c r="D88" t="n">
         <v>0.2480454422386726</v>
@@ -1690,7 +1690,7 @@
         <v>-1.055314352405198</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8929976987715136</v>
+        <v>0.8929976987715135</v>
       </c>
       <c r="D90" t="n">
         <v>0.3795502824324147</v>
@@ -1704,7 +1704,7 @@
         <v>-2.429097756075844</v>
       </c>
       <c r="C91" t="n">
-        <v>2.997507597691734</v>
+        <v>2.997507597691733</v>
       </c>
       <c r="D91" t="n">
         <v>0.2784839797723285</v>
@@ -1743,10 +1743,10 @@
         <v>1.037258572716454</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.233384441067621</v>
+        <v>-0.2333844410676209</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1721438549406593</v>
+        <v>0.1721438549406592</v>
       </c>
       <c r="D94" t="n">
         <v>1.459579275542689</v>
@@ -1757,7 +1757,7 @@
         <v>-0.08148436439543326</v>
       </c>
       <c r="B95" t="n">
-        <v>0.01050577670988685</v>
+        <v>0.01050577670988688</v>
       </c>
       <c r="C95" t="n">
         <v>-1.084789172061223</v>
@@ -1771,10 +1771,10 @@
         <v>1.710045372621691</v>
       </c>
       <c r="B96" t="n">
-        <v>0.295803310067531</v>
+        <v>0.2958033100675311</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.7121299418537665</v>
+        <v>-0.7121299418537664</v>
       </c>
       <c r="D96" t="n">
         <v>1.076661060908159</v>
@@ -1802,7 +1802,7 @@
         <v>-0.3063031240897837</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8041694863909762</v>
+        <v>0.8041694863909761</v>
       </c>
       <c r="D98" t="n">
         <v>1.245261838801464</v>
@@ -1813,10 +1813,10 @@
         <v>1.489562217360709</v>
       </c>
       <c r="B99" t="n">
-        <v>0.01368753358748142</v>
+        <v>0.01368753358748145</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.377768663690564</v>
+        <v>-0.3777686636905639</v>
       </c>
       <c r="D99" t="n">
         <v>1.304349796426736</v>
@@ -1897,10 +1897,10 @@
         <v>0.6256503588877083</v>
       </c>
       <c r="B105" t="n">
-        <v>-0.3523202237740823</v>
+        <v>-0.3523202237740822</v>
       </c>
       <c r="C105" t="n">
-        <v>0.7783226880790046</v>
+        <v>0.7783226880790045</v>
       </c>
       <c r="D105" t="n">
         <v>0.4379932161377928</v>
@@ -1914,7 +1914,7 @@
         <v>0.1018358840726679</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1139079314712614</v>
+        <v>0.1139079314712613</v>
       </c>
       <c r="D106" t="n">
         <v>0.7582311136515858</v>
@@ -1928,10 +1928,10 @@
         <v>0.9602259922323145</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.7922734457105843</v>
+        <v>-0.7922734457105842</v>
       </c>
       <c r="D107" t="n">
-        <v>0.01792727356195735</v>
+        <v>0.01792727356195734</v>
       </c>
     </row>
     <row r="108">
@@ -1942,10 +1942,10 @@
         <v>-2.480416415391885</v>
       </c>
       <c r="C108" t="n">
-        <v>3.136071315915005</v>
+        <v>3.136071315915004</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.08499406139329674</v>
+        <v>-0.08499406139329675</v>
       </c>
     </row>
     <row r="109">
@@ -1953,13 +1953,13 @@
         <v>-0.5934629769784404</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.04755273319632757</v>
+        <v>-0.04755273319632754</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.6535254365902585</v>
+        <v>-0.6535254365902584</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.09897742666397848</v>
+        <v>-0.09897742666397849</v>
       </c>
     </row>
     <row r="110">
@@ -1970,7 +1970,7 @@
         <v>1.284115157395622</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.02183079435479</v>
+        <v>-1.021830794354789</v>
       </c>
       <c r="D110" t="n">
         <v>-0.7376452714343449</v>
@@ -1984,7 +1984,7 @@
         <v>-2.619883425193113</v>
       </c>
       <c r="C111" t="n">
-        <v>3.674730571644804</v>
+        <v>3.674730571644803</v>
       </c>
       <c r="D111" t="n">
         <v>-0.9470661762289332</v>
@@ -1998,7 +1998,7 @@
         <v>-1.377082346316775</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8949788259148554</v>
+        <v>0.8949788259148553</v>
       </c>
       <c r="D112" t="n">
         <v>0.7076979623215427</v>
@@ -2009,10 +2009,10 @@
         <v>1.96664003656849</v>
       </c>
       <c r="B113" t="n">
-        <v>0.1609378733849751</v>
+        <v>0.1609378733849752</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.6181876570799515</v>
+        <v>-0.6181876570799514</v>
       </c>
       <c r="D113" t="n">
         <v>1.253783687670129</v>
@@ -2040,7 +2040,7 @@
         <v>0.1290860921694857</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.1602501178964806</v>
+        <v>-0.1602501178964805</v>
       </c>
       <c r="D115" t="n">
         <v>0.7296146509865339</v>
@@ -2051,13 +2051,13 @@
         <v>-0.3282638363011742</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0533397510190091</v>
+        <v>0.05333975101900913</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.9993242685519405</v>
+        <v>-0.9993242685519403</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0775802156426101</v>
+        <v>0.07758021564261008</v>
       </c>
     </row>
     <row r="117">
@@ -2068,7 +2068,7 @@
         <v>-1.240797093393142</v>
       </c>
       <c r="C117" t="n">
-        <v>0.9843829473486897</v>
+        <v>0.9843829473486896</v>
       </c>
       <c r="D117" t="n">
         <v>1.000538821953148</v>
@@ -2079,10 +2079,10 @@
         <v>-0.8880237135261224</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.3176308628228112</v>
+        <v>-0.3176308628228111</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.5441718255502144</v>
+        <v>-0.5441718255502143</v>
       </c>
       <c r="D118" t="n">
         <v>0.1780297436055718</v>
@@ -2138,10 +2138,10 @@
         <v>0.1336876652881574</v>
       </c>
       <c r="C122" t="n">
-        <v>-1.03664317520559</v>
+        <v>-1.036643175205589</v>
       </c>
       <c r="D122" t="n">
-        <v>0.002060626773338561</v>
+        <v>0.002060626773338553</v>
       </c>
     </row>
     <row r="123">
@@ -2149,13 +2149,13 @@
         <v>-0.3640464223303568</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.1041914268614649</v>
+        <v>-0.1041914268614648</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.6408784737798552</v>
+        <v>-0.6408784737798551</v>
       </c>
       <c r="D123" t="n">
-        <v>0.03920835471464478</v>
+        <v>0.03920835471464477</v>
       </c>
     </row>
     <row r="124">
@@ -2163,10 +2163,10 @@
         <v>-0.1110559108977433</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.3264799103108739</v>
+        <v>-0.3264799103108738</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.7001049608209241</v>
+        <v>-0.700104960820924</v>
       </c>
       <c r="D124" t="n">
         <v>0.8489440761668136</v>
@@ -2222,7 +2222,7 @@
         <v>1.496146751469731</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.6324010925153227</v>
+        <v>-0.6324010925153226</v>
       </c>
       <c r="D128" t="n">
         <v>-1.468829320773364</v>
@@ -2247,7 +2247,7 @@
         <v>1.091600794605092</v>
       </c>
       <c r="B130" t="n">
-        <v>0.1687383096010134</v>
+        <v>0.1687383096010135</v>
       </c>
       <c r="C130" t="n">
         <v>-0.1446568043694096</v>
@@ -2292,7 +2292,7 @@
         <v>0.9142102610455977</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.3844791559795813</v>
+        <v>-0.3844791559795812</v>
       </c>
       <c r="D133" t="n">
         <v>-2.621303445674877</v>
@@ -2320,7 +2320,7 @@
         <v>1.409777447840834</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.9928280144307498</v>
+        <v>-0.9928280144307496</v>
       </c>
       <c r="D135" t="n">
         <v>-2.192103587737047</v>
@@ -2331,10 +2331,10 @@
         <v>0.5961173033345788</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.4850614100853495</v>
+        <v>-0.4850614100853494</v>
       </c>
       <c r="C136" t="n">
-        <v>0.8627970280166162</v>
+        <v>0.8627970280166161</v>
       </c>
       <c r="D136" t="n">
         <v>0.2486528005282073</v>
@@ -2362,7 +2362,7 @@
         <v>-1.562565087304719</v>
       </c>
       <c r="C138" t="n">
-        <v>0.9879305471169999</v>
+        <v>0.9879305471169998</v>
       </c>
       <c r="D138" t="n">
         <v>0.7162245193940022</v>
@@ -2376,7 +2376,7 @@
         <v>1.211550573122739</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.4555371186115847</v>
+        <v>-0.4555371186115846</v>
       </c>
       <c r="D139" t="n">
         <v>-0.2377752745359314</v>
@@ -2390,10 +2390,10 @@
         <v>-1.226291019026474</v>
       </c>
       <c r="C140" t="n">
-        <v>0.67606427657558</v>
+        <v>0.6760642765755799</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.01922045437934887</v>
+        <v>-0.01922045437934888</v>
       </c>
     </row>
     <row r="141">
@@ -2404,7 +2404,7 @@
         <v>0.8593335080169777</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.448036479101444</v>
+        <v>-0.4480364791014439</v>
       </c>
       <c r="D141" t="n">
         <v>0.7655382459411811</v>
@@ -2418,7 +2418,7 @@
         <v>-0.980987827495798</v>
       </c>
       <c r="C142" t="n">
-        <v>0.9038478253356301</v>
+        <v>0.90384782533563</v>
       </c>
       <c r="D142" t="n">
         <v>0.7630993963754528</v>
@@ -2443,7 +2443,7 @@
         <v>0.9392116276218231</v>
       </c>
       <c r="B144" t="n">
-        <v>0.1478516152593847</v>
+        <v>0.1478516152593848</v>
       </c>
       <c r="C144" t="n">
         <v>-0.175053284202428</v>
@@ -2471,7 +2471,7 @@
         <v>1.000167294415131</v>
       </c>
       <c r="B146" t="n">
-        <v>-0.1905538880024532</v>
+        <v>-0.1905538880024531</v>
       </c>
       <c r="C146" t="n">
         <v>0.05154849918025655</v>
@@ -2488,7 +2488,7 @@
         <v>0.6908372432626431</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.8777383492198668</v>
+        <v>-0.8777383492198667</v>
       </c>
       <c r="D147" t="n">
         <v>0.2474333757453431</v>
@@ -2502,7 +2502,7 @@
         <v>1.002341505311012</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.6959584156371853</v>
+        <v>-0.6959584156371852</v>
       </c>
       <c r="D148" t="n">
         <v>-0.296863232161203</v>
@@ -2516,7 +2516,7 @@
         <v>-0.9211502707332941</v>
       </c>
       <c r="C149" t="n">
-        <v>0.004162702274975099</v>
+        <v>0.004162702274975105</v>
       </c>
       <c r="D149" t="n">
         <v>1.207549126404777</v>
@@ -2558,7 +2558,7 @@
         <v>-0.1700161605441735</v>
       </c>
       <c r="C152" t="n">
-        <v>0.9905106196757704</v>
+        <v>0.9905106196757703</v>
       </c>
       <c r="D152" t="n">
         <v>0.3740699332152181</v>
@@ -2583,7 +2583,7 @@
         <v>0.8133812155731817</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0161679354544234</v>
+        <v>0.01616793545442343</v>
       </c>
       <c r="C154" t="n">
         <v>0.1109592771183805</v>
@@ -2597,10 +2597,10 @@
         <v>-0.670514858883643</v>
       </c>
       <c r="B155" t="n">
-        <v>0.02006815356244255</v>
+        <v>0.02006815356244258</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.4213903190234959</v>
+        <v>-0.4213903190234958</v>
       </c>
       <c r="D155" t="n">
         <v>-0.2164941933832439</v>
@@ -2614,7 +2614,7 @@
         <v>-0.9367340369455988</v>
       </c>
       <c r="C156" t="n">
-        <v>0.5266504317881927</v>
+        <v>0.5266504317881926</v>
       </c>
       <c r="D156" t="n">
         <v>1.080898444323517</v>
@@ -2628,7 +2628,7 @@
         <v>-2.579889083366145</v>
       </c>
       <c r="C157" t="n">
-        <v>3.594011158734689</v>
+        <v>3.594011158734688</v>
       </c>
       <c r="D157" t="n">
         <v>-0.5166421853044445</v>
@@ -2642,7 +2642,7 @@
         <v>0.2143948101725179</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.6051490761133062</v>
+        <v>-0.605149076113306</v>
       </c>
       <c r="D158" t="n">
         <v>1.095493876087529</v>
@@ -2670,7 +2670,7 @@
         <v>0.2172344426546723</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.8323336794579272</v>
+        <v>-0.8323336794579271</v>
       </c>
       <c r="D160" t="n">
         <v>-0.5915026256424379</v>
@@ -2681,7 +2681,7 @@
         <v>1.118019582451789</v>
       </c>
       <c r="B161" t="n">
-        <v>0.3892545886820417</v>
+        <v>0.3892545886820418</v>
       </c>
       <c r="C161" t="n">
         <v>-0.1837379927261475</v>
@@ -2695,10 +2695,10 @@
         <v>0.05070755179960509</v>
       </c>
       <c r="B162" t="n">
-        <v>0.319529636891314</v>
+        <v>0.3195296368913141</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.401608260460998</v>
+        <v>-1.401608260460997</v>
       </c>
       <c r="D162" t="n">
         <v>-1.500468450274704</v>
@@ -2726,7 +2726,7 @@
         <v>-0.7962064415185063</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4137492209798386</v>
+        <v>0.4137492209798385</v>
       </c>
       <c r="D164" t="n">
         <v>0.528098820363486</v>
@@ -2793,10 +2793,10 @@
         <v>-0.9629760891123823</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.3990444945837559</v>
+        <v>-0.3990444945837558</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.005097915302041504</v>
+        <v>-0.005097915302041496</v>
       </c>
       <c r="D169" t="n">
         <v>1.216683041766771</v>
@@ -2804,13 +2804,13 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.008762914724325182</v>
+        <v>0.00876291472432518</v>
       </c>
       <c r="B170" t="n">
         <v>0.5988057808892094</v>
       </c>
       <c r="C170" t="n">
-        <v>0.09713745983925121</v>
+        <v>0.09713745983925119</v>
       </c>
       <c r="D170" t="n">
         <v>0.3466728953330304</v>
@@ -2835,10 +2835,10 @@
         <v>0.6718744896764335</v>
       </c>
       <c r="B172" t="n">
-        <v>0.4327899180018165</v>
+        <v>0.4327899180018166</v>
       </c>
       <c r="C172" t="n">
-        <v>-1.461802274711606</v>
+        <v>-1.461802274711605</v>
       </c>
       <c r="D172" t="n">
         <v>-0.7960740805283385</v>
@@ -2852,7 +2852,7 @@
         <v>-0.7215206859938945</v>
       </c>
       <c r="C173" t="n">
-        <v>0.255236013150358</v>
+        <v>0.2552360131503579</v>
       </c>
       <c r="D173" t="n">
         <v>1.105851924436182</v>
@@ -2866,7 +2866,7 @@
         <v>1.457555119664068</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.6391046738957004</v>
+        <v>-0.6391046738957002</v>
       </c>
       <c r="D174" t="n">
         <v>-1.329984390863463</v>
@@ -2880,7 +2880,7 @@
         <v>1.564109762623942</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.6310189107874098</v>
+        <v>-0.6310189107874097</v>
       </c>
       <c r="D175" t="n">
         <v>-1.34886428808078</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2022829596330084</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.4779811457217131</v>
+        <v>-0.477981145721713</v>
       </c>
       <c r="C176" t="n">
         <v>1.474481551704481</v>
@@ -2950,7 +2950,7 @@
         <v>0.6274758052271044</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.2907216228300638</v>
+        <v>-0.2907216228300637</v>
       </c>
       <c r="D180" t="n">
         <v>0.5561041581759674</v>
@@ -2961,10 +2961,10 @@
         <v>-1.051925173491594</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.4790434419695551</v>
+        <v>-0.479043441969555</v>
       </c>
       <c r="C181" t="n">
-        <v>0.4615035996792302</v>
+        <v>0.4615035996792301</v>
       </c>
       <c r="D181" t="n">
         <v>0.5694980563315349</v>
@@ -2975,7 +2975,7 @@
         <v>-1.402297786351174</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.2946229972294528</v>
+        <v>-0.2946229972294527</v>
       </c>
       <c r="C182" t="n">
         <v>-0.1612383778319383</v>
@@ -2992,7 +2992,7 @@
         <v>0.9542046028725656</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.4225743880370746</v>
+        <v>-0.4225743880370745</v>
       </c>
       <c r="D183" t="n">
         <v>-0.3004885490832316</v>
@@ -3017,7 +3017,7 @@
         <v>0.02370790053800003</v>
       </c>
       <c r="B185" t="n">
-        <v>0.319529636891314</v>
+        <v>0.3195296368913141</v>
       </c>
       <c r="C185" t="n">
         <v>-1.422133659120504</v>
@@ -3034,7 +3034,7 @@
         <v>1.522336373940684</v>
       </c>
       <c r="C186" t="n">
-        <v>-1.20934678210831</v>
+        <v>-1.209346782108309</v>
       </c>
       <c r="D186" t="n">
         <v>-1.399430396837387</v>
@@ -3059,7 +3059,7 @@
         <v>1.483578624351722</v>
       </c>
       <c r="B188" t="n">
-        <v>0.00838460545815716</v>
+        <v>0.008384605458157189</v>
       </c>
       <c r="C188" t="n">
         <v>-0.3748084911566171</v>
@@ -3073,7 +3073,7 @@
         <v>1.654968323521424</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.2907279109873653</v>
+        <v>-0.2907279109873652</v>
       </c>
       <c r="C189" t="n">
         <v>-0.2711794161063455</v>
@@ -3087,10 +3087,10 @@
         <v>0.0816332798776333</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.3172767640735305</v>
+        <v>-0.3172767640735304</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.723970631989554</v>
+        <v>-0.7239706319895539</v>
       </c>
       <c r="D190" t="n">
         <v>0.738748566348528</v>
@@ -3118,7 +3118,7 @@
         <v>1.456135303422991</v>
       </c>
       <c r="C192" t="n">
-        <v>-1.261063415094385</v>
+        <v>-1.261063415094384</v>
       </c>
       <c r="D192" t="n">
         <v>-1.446277024596069</v>
@@ -3132,7 +3132,7 @@
         <v>-0.2910820097366459</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.3900055792550198</v>
+        <v>-0.3900055792550197</v>
       </c>
       <c r="D193" t="n">
         <v>0.3990281215316774</v>
@@ -3143,10 +3143,10 @@
         <v>1.398478634890572</v>
       </c>
       <c r="B194" t="n">
-        <v>0.04519719040753065</v>
+        <v>0.04519719040753068</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.09195421508408973</v>
+        <v>-0.09195421508408971</v>
       </c>
       <c r="D194" t="n">
         <v>0.9597469442746338</v>
@@ -3160,7 +3160,7 @@
         <v>-0.1158578687459782</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.6466145279506939</v>
+        <v>-0.6466145279506937</v>
       </c>
       <c r="D195" t="n">
         <v>0.3052736593649815</v>
@@ -3174,7 +3174,7 @@
         <v>-0.8985016357551481</v>
       </c>
       <c r="C196" t="n">
-        <v>0.5641536293388968</v>
+        <v>0.5641536293388967</v>
       </c>
       <c r="D196" t="n">
         <v>1.125955954640159</v>
@@ -3188,7 +3188,7 @@
         <v>-0.3898413483464125</v>
       </c>
       <c r="C197" t="n">
-        <v>0.8785769360769554</v>
+        <v>0.8785769360769553</v>
       </c>
       <c r="D197" t="n">
         <v>1.0754369279215</v>
@@ -3216,7 +3216,7 @@
         <v>-0.6209874323937701</v>
       </c>
       <c r="C199" t="n">
-        <v>1.639905668173527</v>
+        <v>1.639905668173526</v>
       </c>
       <c r="D199" t="n">
         <v>0.924435415813316</v>
@@ -3230,7 +3230,7 @@
         <v>0.8338452405566773</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.7747197377660903</v>
+        <v>-0.7747197377660902</v>
       </c>
       <c r="D200" t="n">
         <v>-0.7084073258683738</v>
@@ -3241,10 +3241,10 @@
         <v>1.684921280338342</v>
       </c>
       <c r="B201" t="n">
-        <v>0.2104945920644988</v>
+        <v>0.2104945920644989</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.6286461654878259</v>
+        <v>-0.6286461654878258</v>
       </c>
       <c r="D201" t="n">
         <v>1.118046172264824</v>
@@ -3258,7 +3258,7 @@
         <v>0.5566902678105118</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.8331399521325431</v>
+        <v>-0.833139952132543</v>
       </c>
       <c r="D202" t="n">
         <v>0.6042003432217999</v>
@@ -3269,7 +3269,7 @@
         <v>0.05234516672838053</v>
       </c>
       <c r="B203" t="n">
-        <v>0.2823578213267282</v>
+        <v>0.2823578213267283</v>
       </c>
       <c r="C203" t="n">
         <v>-1.251779761155236</v>
@@ -3286,7 +3286,7 @@
         <v>-0.7487708940907123</v>
       </c>
       <c r="C204" t="n">
-        <v>0.08015966094805414</v>
+        <v>0.08015966094805413</v>
       </c>
       <c r="D204" t="n">
         <v>0.9968852558083502</v>
@@ -3300,7 +3300,7 @@
         <v>0.8731382273729928</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.6128432210653548</v>
+        <v>-0.6128432210653547</v>
       </c>
       <c r="D205" t="n">
         <v>0.6687328677154273</v>
@@ -3339,10 +3339,10 @@
         <v>0.0127799701479025</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.2648889660217386</v>
+        <v>-0.2648889660217385</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.7687763563360646</v>
+        <v>-0.7687763563360644</v>
       </c>
       <c r="D208" t="n">
         <v>0.8404222272981489</v>
@@ -3356,7 +3356,7 @@
         <v>-1.18097664285041</v>
       </c>
       <c r="C209" t="n">
-        <v>1.179593080054259</v>
+        <v>1.179593080054258</v>
       </c>
       <c r="D209" t="n">
         <v>0.7296146509865339</v>
@@ -3370,7 +3370,7 @@
         <v>-1.465572821197402</v>
       </c>
       <c r="C210" t="n">
-        <v>0.7966596323359827</v>
+        <v>0.7966596323359826</v>
       </c>
       <c r="D210" t="n">
         <v>0.5530598336022222</v>
@@ -3381,7 +3381,7 @@
         <v>-0.6222262135479575</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.3034720447175155</v>
+        <v>-0.3034720447175154</v>
       </c>
       <c r="C211" t="n">
         <v>-0.1369580521449346</v>
@@ -3409,7 +3409,7 @@
         <v>-0.1616430607596356</v>
       </c>
       <c r="B213" t="n">
-        <v>0.2625317126109644</v>
+        <v>0.2625317126109645</v>
       </c>
       <c r="C213" t="n">
         <v>-1.327776719828315</v>
@@ -3423,13 +3423,13 @@
         <v>-0.5606406948589672</v>
       </c>
       <c r="B214" t="n">
-        <v>-0.03090838135815823</v>
+        <v>-0.0309083813581582</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.6252828566165711</v>
+        <v>-0.625282856616571</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.08132166243331967</v>
+        <v>-0.08132166243331969</v>
       </c>
     </row>
     <row r="215">
@@ -3482,7 +3482,7 @@
         <v>0.8391652749057736</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.5534324431272308</v>
+        <v>-0.5534324431272307</v>
       </c>
       <c r="D218" t="n">
         <v>0.6790862078602856</v>
@@ -3493,10 +3493,10 @@
         <v>-0.2516108605965707</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.01534172136562579</v>
+        <v>-0.01534172136562576</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.8814932762473636</v>
+        <v>-0.8814932762473635</v>
       </c>
       <c r="D219" t="n">
         <v>0.1895978003294995</v>
@@ -3510,7 +3510,7 @@
         <v>1.161634623828004</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.3268428690164762</v>
+        <v>-0.3268428690164761</v>
       </c>
       <c r="D220" t="n">
         <v>-1.185112960096163</v>
@@ -3524,10 +3524,10 @@
         <v>0.5418249628286319</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.7265507045483247</v>
+        <v>-0.7265507045483246</v>
       </c>
       <c r="D221" t="n">
-        <v>0.01486694109530984</v>
+        <v>0.01486694109530983</v>
       </c>
     </row>
     <row r="222">
@@ -3538,10 +3538,10 @@
         <v>0.2805958806902109</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.473104648373358</v>
+        <v>-0.4731046483733579</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.01860838788601943</v>
+        <v>-0.01860838788601944</v>
       </c>
     </row>
     <row r="223">
@@ -3549,13 +3549,13 @@
         <v>-0.8434791877925516</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.0779846981707399</v>
+        <v>-0.07798469817073987</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.3019723517316537</v>
+        <v>-0.3019723517316536</v>
       </c>
       <c r="D223" t="n">
-        <v>0.04043248770130377</v>
+        <v>0.04043248770130376</v>
       </c>
     </row>
     <row r="224">
@@ -3594,7 +3594,7 @@
         <v>-0.560807751235826</v>
       </c>
       <c r="C226" t="n">
-        <v>0.2088638161788794</v>
+        <v>0.2088638161788793</v>
       </c>
       <c r="D226" t="n">
         <v>0.932349906392446</v>
@@ -3636,7 +3636,7 @@
         <v>-0.5091315719265499</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.5597674427134984</v>
+        <v>-0.5597674427134983</v>
       </c>
       <c r="D229" t="n">
         <v>0.719873377335005</v>
@@ -3650,7 +3650,7 @@
         <v>1.263228463053993</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0860800060159478</v>
+        <v>0.08608000601594779</v>
       </c>
       <c r="D230" t="n">
         <v>-1.720859469911275</v>
@@ -3661,10 +3661,10 @@
         <v>-0.6822371024977407</v>
       </c>
       <c r="B231" t="n">
-        <v>-0.3222324359414829</v>
+        <v>-0.3222324359414828</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.5802928413730054</v>
+        <v>-0.5802928413730053</v>
       </c>
       <c r="D231" t="n">
         <v>0.3399731213329698</v>
@@ -3675,10 +3675,10 @@
         <v>1.843608966278439</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.4224081695483722</v>
+        <v>-0.4224081695483721</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.224991510031922</v>
+        <v>-0.2249915100319219</v>
       </c>
       <c r="D232" t="n">
         <v>1.216683041766771</v>
@@ -3692,7 +3692,7 @@
         <v>1.147128549461336</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.9807799970357755</v>
+        <v>-0.9807799970357753</v>
       </c>
       <c r="D233" t="n">
         <v>0.1134943941896676</v>
@@ -3717,7 +3717,7 @@
         <v>0.6224311158653293</v>
       </c>
       <c r="B235" t="n">
-        <v>0.2650121144779063</v>
+        <v>0.2650121144779064</v>
       </c>
       <c r="C235" t="n">
         <v>-0.231308080528484</v>
@@ -3734,7 +3734,7 @@
         <v>-0.3063031240897837</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.7453023033236769</v>
+        <v>-0.7453023033236768</v>
       </c>
       <c r="D236" t="n">
         <v>1.192906612602817</v>
@@ -3748,7 +3748,7 @@
         <v>0.9609273472429671</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.08484980100261727</v>
+        <v>-0.08484980100261726</v>
       </c>
       <c r="D237" t="n">
         <v>0.1573324797234448</v>
@@ -3804,7 +3804,7 @@
         <v>0.9039465291823895</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.501132990179219</v>
+        <v>-0.5011329901792189</v>
       </c>
       <c r="D241" t="n">
         <v>-0.3156960473405725</v>
@@ -3815,7 +3815,7 @@
         <v>-0.3029472892719217</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.3501963155271891</v>
+        <v>-0.350196315527189</v>
       </c>
       <c r="C242" t="n">
         <v>-0.327829746770206</v>
@@ -3846,7 +3846,7 @@
         <v>1.20765035501472</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.5954738040179157</v>
+        <v>-0.5954738040179156</v>
       </c>
       <c r="D244" t="n">
         <v>-0.1373492875919438</v>
@@ -3885,10 +3885,10 @@
         <v>0.6028007317832137</v>
       </c>
       <c r="B247" t="n">
-        <v>0.4317293323759517</v>
+        <v>0.4317293323759518</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.458853620358725</v>
+        <v>-1.458853620358724</v>
       </c>
       <c r="D247" t="n">
         <v>-0.7144809087637205</v>
@@ -3899,7 +3899,7 @@
         <v>-0.6050802452765909</v>
       </c>
       <c r="B248" t="n">
-        <v>-0.07480294129314537</v>
+        <v>-0.07480294129314534</v>
       </c>
       <c r="C248" t="n">
         <v>1.301777944801761</v>
@@ -3916,7 +3916,7 @@
         <v>-1.474074612424092</v>
       </c>
       <c r="C249" t="n">
-        <v>0.9873546380637025</v>
+        <v>0.9873546380637024</v>
       </c>
       <c r="D249" t="n">
         <v>0.827634745791357</v>
@@ -3972,10 +3972,10 @@
         <v>-1.274427921464921</v>
       </c>
       <c r="C253" t="n">
-        <v>0.5686917926788776</v>
+        <v>0.5686917926788775</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.0210566538593374</v>
+        <v>-0.02105665385933741</v>
       </c>
     </row>
     <row r="254">
@@ -3986,7 +3986,7 @@
         <v>1.443391169692841</v>
       </c>
       <c r="C254" t="n">
-        <v>-1.322455320175851</v>
+        <v>-1.32245532017585</v>
       </c>
       <c r="D254" t="n">
         <v>-1.473678770682051</v>
@@ -4000,7 +4000,7 @@
         <v>0.2405844326434709</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.5923178224058478</v>
+        <v>-0.5923178224058477</v>
       </c>
       <c r="D255" t="n">
         <v>-0.5513416472724325</v>
@@ -4028,7 +4028,7 @@
         <v>0.1577561165073807</v>
       </c>
       <c r="C257" t="n">
-        <v>0.6831825124743315</v>
+        <v>0.6831825124743314</v>
       </c>
       <c r="D257" t="n">
         <v>0.9055649350035878</v>
@@ -4056,7 +4056,7 @@
         <v>0.8264211411756234</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.5583852609855855</v>
+        <v>-0.5583852609855854</v>
       </c>
       <c r="D259" t="n">
         <v>0.6042003432217999</v>
@@ -4081,10 +4081,10 @@
         <v>0.447192321777566</v>
       </c>
       <c r="B261" t="n">
-        <v>-0.3767448264889589</v>
+        <v>-0.3767448264889588</v>
       </c>
       <c r="C261" t="n">
-        <v>0.8813412995327812</v>
+        <v>0.8813412995327811</v>
       </c>
       <c r="D261" t="n">
         <v>1.177087047852147</v>
@@ -4098,7 +4098,7 @@
         <v>-1.476897138686475</v>
       </c>
       <c r="C262" t="n">
-        <v>0.7990323776355666</v>
+        <v>0.7990323776355664</v>
       </c>
       <c r="D262" t="n">
         <v>0.3710237253599551</v>
@@ -4112,7 +4112,7 @@
         <v>1.560209544515922</v>
       </c>
       <c r="C263" t="n">
-        <v>0.1332584756620424</v>
+        <v>0.1332584756620423</v>
       </c>
       <c r="D263" t="n">
         <v>-1.062134676974881</v>
@@ -4126,7 +4126,7 @@
         <v>-0.9961952568731183</v>
       </c>
       <c r="C264" t="n">
-        <v>0.7569910167448818</v>
+        <v>0.7569910167448817</v>
       </c>
       <c r="D264" t="n">
         <v>0.4294713672691282</v>
@@ -4137,10 +4137,10 @@
         <v>0.1916824027622211</v>
       </c>
       <c r="B265" t="n">
-        <v>-0.1579904880444479</v>
+        <v>-0.1579904880444478</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.8424005697095597</v>
+        <v>-0.8424005697095596</v>
       </c>
       <c r="D265" t="n">
         <v>0.8483367178772789</v>
@@ -4154,7 +4154,7 @@
         <v>-0.9760270237619141</v>
       </c>
       <c r="C266" t="n">
-        <v>0.5692907380943065</v>
+        <v>0.5692907380943064</v>
       </c>
       <c r="D266" t="n">
         <v>1.335988925928077</v>
@@ -4165,10 +4165,10 @@
         <v>-0.6179222255941246</v>
       </c>
       <c r="B267" t="n">
-        <v>0.110679799694799</v>
+        <v>0.1106797996947991</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.5062654916622024</v>
+        <v>-0.5062654916622022</v>
       </c>
       <c r="D267" t="n">
         <v>-0.3881553037431965</v>
@@ -4182,7 +4182,7 @@
         <v>1.223217015007253</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.835904315588369</v>
+        <v>-0.8359043155883689</v>
       </c>
       <c r="D268" t="n">
         <v>0.2224751874288838</v>
@@ -4210,10 +4210,10 @@
         <v>0.8862415917183553</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.6998976335617372</v>
+        <v>-0.6998976335617371</v>
       </c>
       <c r="D270" t="n">
-        <v>0.1226283095516618</v>
+        <v>0.1226283095516617</v>
       </c>
     </row>
     <row r="271">
@@ -4221,7 +4221,7 @@
         <v>-0.5636149954774696</v>
       </c>
       <c r="B271" t="n">
-        <v>-0.03657054010269478</v>
+        <v>-0.03657054010269475</v>
       </c>
       <c r="C271" t="n">
         <v>1.280261982570583</v>
@@ -4252,7 +4252,7 @@
         <v>-1.985909814222514</v>
       </c>
       <c r="C273" t="n">
-        <v>1.853867399654448</v>
+        <v>1.853867399654447</v>
       </c>
       <c r="D273" t="n">
         <v>0.6072446677955451</v>
@@ -4263,7 +4263,7 @@
         <v>0.2618059138149123</v>
       </c>
       <c r="B274" t="n">
-        <v>0.01226771734640426</v>
+        <v>0.01226771734640428</v>
       </c>
       <c r="C274" t="n">
         <v>-1.048668156238432</v>
@@ -4294,7 +4294,7 @@
         <v>0.7977511168377286</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.5899681134683958</v>
+        <v>-0.5899681134683957</v>
       </c>
       <c r="D276" t="n">
         <v>0.3862453482286805</v>
@@ -4319,10 +4319,10 @@
         <v>1.185098809342013</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.2124994573479695</v>
+        <v>-0.2124994573479694</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.05840405727521666</v>
+        <v>-0.05840405727521665</v>
       </c>
       <c r="D278" t="n">
         <v>1.369464254909406</v>
@@ -4336,7 +4336,7 @@
         <v>0.8285423124273532</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.5560125156860016</v>
+        <v>-0.5560125156860015</v>
       </c>
       <c r="D279" t="n">
         <v>0.2243019705012826</v>
@@ -4350,7 +4350,7 @@
         <v>-1.526453857365998</v>
       </c>
       <c r="C280" t="n">
-        <v>0.9772877478120702</v>
+        <v>0.9772877478120701</v>
       </c>
       <c r="D280" t="n">
         <v>0.3466728953330304</v>
@@ -4364,7 +4364,7 @@
         <v>-0.2585168991566635</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.07577347432265574</v>
+        <v>-0.07577347432265573</v>
       </c>
       <c r="D281" t="n">
         <v>1.089420293192182</v>
@@ -4389,10 +4389,10 @@
         <v>-0.1738815379857892</v>
       </c>
       <c r="B283" t="n">
-        <v>-0.3763907277396782</v>
+        <v>-0.3763907277396781</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.3386851716976129</v>
+        <v>-0.3386851716976128</v>
       </c>
       <c r="D283" t="n">
         <v>1.142999652377488</v>
@@ -4406,7 +4406,7 @@
         <v>-0.4135574114383322</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.09728482928140723</v>
+        <v>-0.09728482928140722</v>
       </c>
       <c r="D284" t="n">
         <v>0.7710138869545827</v>
@@ -4434,7 +4434,7 @@
         <v>1.812953941647425</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.1430788135633757</v>
+        <v>-0.1430788135633756</v>
       </c>
       <c r="D286" t="n">
         <v>-3.038356137822013</v>
@@ -4445,10 +4445,10 @@
         <v>-0.8446689080399525</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.2822329622485833</v>
+        <v>-0.2822329622485832</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.609687239453287</v>
+        <v>-0.6096872394532868</v>
       </c>
       <c r="D287" t="n">
         <v>0.1804638849675053</v>
@@ -4462,7 +4462,7 @@
         <v>-1.340971116378054</v>
       </c>
       <c r="C288" t="n">
-        <v>2.195335395535336</v>
+        <v>2.195335395535335</v>
       </c>
       <c r="D288" t="n">
         <v>0.3198832157403773</v>
@@ -4476,7 +4476,7 @@
         <v>-1.511588552384119</v>
       </c>
       <c r="C289" t="n">
-        <v>1.637141304717701</v>
+        <v>1.6371413047177</v>
       </c>
       <c r="D289" t="n">
         <v>0.2851837537723891</v>
@@ -4493,7 +4493,7 @@
         <v>-1.148945440598515</v>
       </c>
       <c r="D290" t="n">
-        <v>-0.08861937831532526</v>
+        <v>-0.08861937831532528</v>
       </c>
     </row>
     <row r="291">
@@ -4546,7 +4546,7 @@
         <v>0.8090754343268015</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.310262608626589</v>
+        <v>-0.3102626086265889</v>
       </c>
       <c r="D294" t="n">
         <v>0.7545775475067881</v>
@@ -4560,7 +4560,7 @@
         <v>-0.9388552081973284</v>
       </c>
       <c r="C295" t="n">
-        <v>0.08015966094805414</v>
+        <v>0.08015966094805413</v>
       </c>
       <c r="D295" t="n">
         <v>1.086972027218864</v>
@@ -4574,7 +4574,7 @@
         <v>-1.200802751566174</v>
       </c>
       <c r="C296" t="n">
-        <v>2.084415311870324</v>
+        <v>2.084415311870323</v>
       </c>
       <c r="D296" t="n">
         <v>0.3186684991613081</v>
@@ -4605,7 +4605,7 @@
         <v>-1.069216591260071</v>
       </c>
       <c r="D298" t="n">
-        <v>0.02216465697731543</v>
+        <v>0.02216465697731542</v>
       </c>
     </row>
     <row r="299">
@@ -4630,7 +4630,7 @@
         <v>0.9347377247720141</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.3088809567350051</v>
+        <v>-0.308880956735005</v>
       </c>
       <c r="D300" t="n">
         <v>-0.2511936553512321</v>
@@ -4658,7 +4658,7 @@
         <v>-2.558643158409304</v>
       </c>
       <c r="C302" t="n">
-        <v>2.723144524701018</v>
+        <v>2.723144524701017</v>
       </c>
       <c r="D302" t="n">
         <v>-0.6402325349190564</v>
@@ -4686,7 +4686,7 @@
         <v>1.646938078760032</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.3258559912627464</v>
+        <v>-0.3258559912627463</v>
       </c>
       <c r="D304" t="n">
         <v>-2.775308791804171</v>
@@ -4697,7 +4697,7 @@
         <v>-1.485858137845099</v>
       </c>
       <c r="B305" t="n">
-        <v>0.08377171599342147</v>
+        <v>0.08377171599342149</v>
       </c>
       <c r="C305" t="n">
         <v>-0.1205768950329532</v>
@@ -4739,7 +4739,7 @@
         <v>-1.528058214855851</v>
       </c>
       <c r="B308" t="n">
-        <v>0.3442994431211898</v>
+        <v>0.3442994431211899</v>
       </c>
       <c r="C308" t="n">
         <v>-0.3821110179524237</v>
@@ -4753,7 +4753,7 @@
         <v>0.5350566612253244</v>
       </c>
       <c r="B309" t="n">
-        <v>-0.02772662448056369</v>
+        <v>-0.02772662448056366</v>
       </c>
       <c r="C309" t="n">
         <v>0.2976920285594166</v>
@@ -4781,10 +4781,10 @@
         <v>-0.7621233179335162</v>
       </c>
       <c r="B311" t="n">
-        <v>0.2193556139064019</v>
+        <v>0.219355613906402</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.8384613517850079</v>
+        <v>-0.8384613517850078</v>
       </c>
       <c r="D311" t="n">
         <v>-0.4660760765478375</v>
@@ -4798,7 +4798,7 @@
         <v>1.699317323701937</v>
       </c>
       <c r="C312" t="n">
-        <v>0.3977619856603125</v>
+        <v>0.3977619856603124</v>
       </c>
       <c r="D312" t="n">
         <v>-1.994217782239823</v>
@@ -4812,7 +4812,7 @@
         <v>-1.668401269034168</v>
       </c>
       <c r="C313" t="n">
-        <v>2.44385167021408</v>
+        <v>2.443851670214079</v>
       </c>
       <c r="D313" t="n">
         <v>-0.1160211244013078</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-0.000908811051604884</v>
+        <v>-0.0009088110516048859</v>
       </c>
       <c r="B314" t="n">
         <v>-0.4549732801283546</v>
@@ -4840,7 +4840,7 @@
         <v>-0.4153279051847357</v>
       </c>
       <c r="C315" t="n">
-        <v>0.02964091879283669</v>
+        <v>0.0296409187928367</v>
       </c>
       <c r="D315" t="n">
         <v>1.095493876087529</v>
@@ -4871,7 +4871,7 @@
         <v>-1.088152480932478</v>
       </c>
       <c r="D317" t="n">
-        <v>0.08732619749793376</v>
+        <v>0.08732619749793374</v>
       </c>
     </row>
     <row r="318">
@@ -4882,7 +4882,7 @@
         <v>1.060742139612667</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.8692609679553343</v>
+        <v>-0.8692609679553341</v>
       </c>
       <c r="D318" t="n">
         <v>-0.1787343989486081</v>
@@ -4910,7 +4910,7 @@
         <v>1.223935476237677</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.6886558888413787</v>
+        <v>-0.6886558888413786</v>
       </c>
       <c r="D320" t="n">
         <v>-0.2493574558712436</v>
@@ -4921,10 +4921,10 @@
         <v>-0.4540592565778334</v>
       </c>
       <c r="B321" t="n">
-        <v>0.1598772877591103</v>
+        <v>0.1598772877591104</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.608904003140803</v>
+        <v>-0.6089040031408028</v>
       </c>
       <c r="D321" t="n">
         <v>-0.1209176563479439</v>
@@ -4938,7 +4938,7 @@
         <v>0.725887887575499</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.2761161085112079</v>
+        <v>-0.2761161085112078</v>
       </c>
       <c r="D322" t="n">
         <v>-2.042335625023112</v>
@@ -4949,10 +4949,10 @@
         <v>-0.9632210315162588</v>
       </c>
       <c r="B323" t="n">
-        <v>-0.4932022600748508</v>
+        <v>-0.4932022600748507</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3136792638789429</v>
+        <v>0.3136792638789428</v>
       </c>
       <c r="D323" t="n">
         <v>0.5895889035648861</v>
@@ -4966,7 +4966,7 @@
         <v>1.261107291802263</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.1144561336145122</v>
+        <v>-0.1144561336145121</v>
       </c>
       <c r="D324" t="n">
         <v>-1.942474622534505</v>
@@ -5022,7 +5022,7 @@
         <v>1.161634623828004</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.665550417623101</v>
+        <v>-0.6655504176231009</v>
       </c>
       <c r="D328" t="n">
         <v>-0.2767592019572261</v>
@@ -5036,7 +5036,7 @@
         <v>-1.850343022529305</v>
       </c>
       <c r="C329" t="n">
-        <v>1.524240093909347</v>
+        <v>1.524240093909346</v>
       </c>
       <c r="D329" t="n">
         <v>0.3545873859121604</v>
@@ -5044,16 +5044,16 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>0.01992528998670467</v>
+        <v>0.01992528998670466</v>
       </c>
       <c r="B330" t="n">
-        <v>-0.1817048405143905</v>
+        <v>-0.1817048405143904</v>
       </c>
       <c r="C330" t="n">
-        <v>0.6144880805970592</v>
+        <v>0.6144880805970591</v>
       </c>
       <c r="D330" t="n">
-        <v>0.07513194966929203</v>
+        <v>0.07513194966929201</v>
       </c>
     </row>
     <row r="331">
@@ -5061,13 +5061,13 @@
         <v>-0.4302368582122285</v>
       </c>
       <c r="B331" t="n">
-        <v>0.08697057909078802</v>
+        <v>0.08697057909078805</v>
       </c>
       <c r="C331" t="n">
         <v>-1.014343976661928</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.02590610376802502</v>
+        <v>-0.02590610376802503</v>
       </c>
     </row>
     <row r="332">
@@ -5078,7 +5078,7 @@
         <v>-1.065218853653193</v>
       </c>
       <c r="C332" t="n">
-        <v>0.6529818417194341</v>
+        <v>0.652981841719434</v>
       </c>
       <c r="D332" t="n">
         <v>0.648642962122835</v>
@@ -5095,7 +5095,7 @@
         <v>-0.2490737230045915</v>
       </c>
       <c r="D333" t="n">
-        <v>0.0246129229506335</v>
+        <v>0.02461292295063349</v>
       </c>
     </row>
     <row r="334">
@@ -5106,7 +5106,7 @@
         <v>1.135787125752491</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.9592640348045975</v>
+        <v>-0.9592640348045974</v>
       </c>
       <c r="D334" t="n">
         <v>0.3582409520569581</v>
@@ -5120,7 +5120,7 @@
         <v>1.170837770065347</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.8512926054924662</v>
+        <v>-0.8512926054924661</v>
       </c>
       <c r="D335" t="n">
         <v>0.2127339137773549</v>
@@ -5159,10 +5159,10 @@
         <v>-1.311984022864649</v>
       </c>
       <c r="B338" t="n">
-        <v>-0.0383495869589842</v>
+        <v>-0.03834958695898417</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2709836070282246</v>
+        <v>-0.2709836070282245</v>
       </c>
       <c r="D338" t="n">
         <v>-0.5580272966611088</v>
@@ -5176,7 +5176,7 @@
         <v>-1.1639901666168</v>
       </c>
       <c r="C339" t="n">
-        <v>1.118201174972793</v>
+        <v>1.118201174972792</v>
       </c>
       <c r="D339" t="n">
         <v>0.7557969722896523</v>
@@ -5201,7 +5201,7 @@
         <v>0.2656900005049566</v>
       </c>
       <c r="B341" t="n">
-        <v>0.3191704062761017</v>
+        <v>0.3191704062761018</v>
       </c>
       <c r="C341" t="n">
         <v>-1.424690695317143</v>
@@ -5218,7 +5218,7 @@
         <v>0.1790020414642217</v>
       </c>
       <c r="C342" t="n">
-        <v>-1.092506353375404</v>
+        <v>-1.092506353375403</v>
       </c>
       <c r="D342" t="n">
         <v>-0.8039838629036739</v>
@@ -5229,10 +5229,10 @@
         <v>0.4927866006706083</v>
       </c>
       <c r="B343" t="n">
-        <v>0.07598838599715523</v>
+        <v>0.07598838599715525</v>
       </c>
       <c r="C343" t="n">
-        <v>0.2617553036336807</v>
+        <v>0.2617553036336806</v>
       </c>
       <c r="D343" t="n">
         <v>0.7460556986381234</v>
@@ -5243,10 +5243,10 @@
         <v>0.2364018873557038</v>
       </c>
       <c r="B344" t="n">
-        <v>0.2689123325859255</v>
+        <v>0.2689123325859256</v>
       </c>
       <c r="C344" t="n">
-        <v>0.1340417119745264</v>
+        <v>0.1340417119745263</v>
       </c>
       <c r="D344" t="n">
         <v>0.3643286595636893</v>
@@ -5260,7 +5260,7 @@
         <v>1.868874174082137</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4542010728834236</v>
+        <v>0.4542010728834235</v>
       </c>
       <c r="D345" t="n">
         <v>-2.229204233640405</v>
@@ -5288,7 +5288,7 @@
         <v>0.7046590688384301</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.07814621962223958</v>
+        <v>-0.07814621962223957</v>
       </c>
       <c r="D347" t="n">
         <v>-0.3918277027031734</v>
@@ -5302,10 +5302,10 @@
         <v>0.8979251398226407</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.8830827852344635</v>
+        <v>-0.8830827852344634</v>
       </c>
       <c r="D348" t="n">
-        <v>-0.0009526236553605325</v>
+        <v>-0.00095262365536054</v>
       </c>
     </row>
     <row r="349">
@@ -5313,7 +5313,7 @@
         <v>1.256761958361929</v>
       </c>
       <c r="B349" t="n">
-        <v>0.2664319307189835</v>
+        <v>0.2664319307189836</v>
       </c>
       <c r="C349" t="n">
         <v>-0.1454469515905331</v>
@@ -5344,7 +5344,7 @@
         <v>0.920933005415999</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.5376502314306785</v>
+        <v>-0.5376502314306784</v>
       </c>
       <c r="D351" t="n">
         <v>0.152459488795783</v>
@@ -5358,7 +5358,7 @@
         <v>-0.1572720268140233</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.8817006035065507</v>
+        <v>-0.8817006035065506</v>
       </c>
       <c r="D352" t="n">
         <v>0.5390571646959815</v>
@@ -5428,7 +5428,7 @@
         <v>1.394552912243742</v>
       </c>
       <c r="C357" t="n">
-        <v>-1.284353177209718</v>
+        <v>-1.284353177209717</v>
       </c>
       <c r="D357" t="n">
         <v>-1.514451815545386</v>
@@ -5439,7 +5439,7 @@
         <v>-0.09428435458658818</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.01852347824322036</v>
+        <v>-0.01852347824322033</v>
       </c>
       <c r="C358" t="n">
         <v>-1.068801936741697</v>
@@ -5456,7 +5456,7 @@
         <v>0.3241312100099857</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.1499874185667271</v>
+        <v>-0.149987418566727</v>
       </c>
       <c r="D359" t="n">
         <v>0.7271805096246003</v>
@@ -5467,10 +5467,10 @@
         <v>-0.9567125619275362</v>
       </c>
       <c r="B360" t="n">
-        <v>-0.3636474493205166</v>
+        <v>-0.3636474493205165</v>
       </c>
       <c r="C360" t="n">
-        <v>0.3353795170071758</v>
+        <v>0.3353795170071757</v>
       </c>
       <c r="D360" t="n">
         <v>0.7978035665472358</v>
@@ -5481,10 +5481,10 @@
         <v>-1.468257276537962</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.02100388011016234</v>
+        <v>-0.02100388011016231</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.3207239505070057</v>
+        <v>-0.3207239505070056</v>
       </c>
       <c r="D361" t="n">
         <v>-0.612830788833074</v>
@@ -5495,7 +5495,7 @@
         <v>0.4515313015033812</v>
       </c>
       <c r="B362" t="n">
-        <v>0.4005789061711148</v>
+        <v>0.4005789061711149</v>
       </c>
       <c r="C362" t="n">
         <v>0.1800453271518948</v>
@@ -5512,7 +5512,7 @@
         <v>-1.580612149164194</v>
       </c>
       <c r="C363" t="n">
-        <v>2.369628511425156</v>
+        <v>2.369628511425155</v>
       </c>
       <c r="D363" t="n">
         <v>0.1232356678411964</v>
@@ -5540,7 +5540,7 @@
         <v>0.7081829501114649</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.9093212017026772</v>
+        <v>-0.9093212017026771</v>
       </c>
       <c r="D365" t="n">
         <v>0.396593980169744</v>
@@ -5576,13 +5576,13 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>0.024456724458423</v>
+        <v>0.02445672445842299</v>
       </c>
       <c r="B368" t="n">
         <v>0.6851750845181065</v>
       </c>
       <c r="C368" t="n">
-        <v>0.07502255219264443</v>
+        <v>0.07502255219264442</v>
       </c>
       <c r="D368" t="n">
         <v>0.3515411780568974</v>
@@ -5596,7 +5596,7 @@
         <v>1.132964599490109</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.5342938334680633</v>
+        <v>-0.5342938334680631</v>
       </c>
       <c r="D369" t="n">
         <v>-0.2840569178392318</v>
@@ -5624,10 +5624,10 @@
         <v>0.9807534559587309</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.876747785648196</v>
+        <v>-0.8767477856481959</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.006461222095326116</v>
+        <v>-0.006461222095326124</v>
       </c>
     </row>
     <row r="372">
@@ -5666,7 +5666,7 @@
         <v>-0.1753361948932697</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.836088606485424</v>
+        <v>-0.8360886064854239</v>
       </c>
       <c r="D374" t="n">
         <v>0.5658451493352685</v>
@@ -5694,7 +5694,7 @@
         <v>-1.230533361529934</v>
       </c>
       <c r="C376" t="n">
-        <v>0.4798635802983403</v>
+        <v>0.4798635802983402</v>
       </c>
       <c r="D376" t="n">
         <v>0.5932419988893044</v>
@@ -5733,10 +5733,10 @@
         <v>0.8028137004345025</v>
       </c>
       <c r="B379" t="n">
-        <v>-0.233384441067621</v>
+        <v>-0.2333844410676209</v>
       </c>
       <c r="C379" t="n">
-        <v>0.6433065696240436</v>
+        <v>0.6433065696240435</v>
       </c>
       <c r="D379" t="n">
         <v>0.4349517164863247</v>
@@ -5761,10 +5761,10 @@
         <v>0.3625472253521868</v>
       </c>
       <c r="B381" t="n">
-        <v>-0.01144150325760668</v>
+        <v>-0.01144150325760665</v>
       </c>
       <c r="C381" t="n">
-        <v>-1.017108340117754</v>
+        <v>-1.017108340117753</v>
       </c>
       <c r="D381" t="n">
         <v>0.5110504144223618</v>
@@ -5831,7 +5831,7 @@
         <v>0.3778386297084872</v>
       </c>
       <c r="B386" t="n">
-        <v>0.3036037462835692</v>
+        <v>0.3036037462835693</v>
       </c>
       <c r="C386" t="n">
         <v>-1.444640184923353</v>
@@ -5848,7 +5848,7 @@
         <v>-0.1084337693649242</v>
       </c>
       <c r="C387" t="n">
-        <v>0.08193346083220901</v>
+        <v>0.081933460832209</v>
       </c>
       <c r="D387" t="n">
         <v>0.7637114628687823</v>
@@ -5890,7 +5890,7 @@
         <v>0.9581048209805847</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.03472267700364188</v>
+        <v>-0.03472267700364186</v>
       </c>
       <c r="D390" t="n">
         <v>-1.137607183806204</v>
@@ -5901,10 +5901,10 @@
         <v>1.544359332285118</v>
       </c>
       <c r="B391" t="n">
-        <v>-0.07304100065662796</v>
+        <v>-0.07304100065662793</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.3126312327209875</v>
+        <v>-0.3126312327209874</v>
       </c>
       <c r="D391" t="n">
         <v>1.340885457874712</v>
@@ -5929,10 +5929,10 @@
         <v>-0.177665198290244</v>
       </c>
       <c r="B393" t="n">
-        <v>-0.08578513438677815</v>
+        <v>-0.08578513438677812</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.6371235467523585</v>
+        <v>-0.6371235467523584</v>
       </c>
       <c r="D393" t="n">
         <v>0.2102997724154214</v>
@@ -5946,7 +5946,7 @@
         <v>-1.511947782999331</v>
       </c>
       <c r="C394" t="n">
-        <v>1.332185942815846</v>
+        <v>1.332185942815845</v>
       </c>
       <c r="D394" t="n">
         <v>1.195966945069465</v>
@@ -5960,7 +5960,7 @@
         <v>-1.751930940180911</v>
       </c>
       <c r="C395" t="n">
-        <v>2.067437512979127</v>
+        <v>2.067437512979126</v>
       </c>
       <c r="D395" t="n">
         <v>1.030977359486804</v>
@@ -6002,7 +6002,7 @@
         <v>0.228199529528533</v>
       </c>
       <c r="C398" t="n">
-        <v>0.1555576742057042</v>
+        <v>0.1555576742057041</v>
       </c>
       <c r="D398" t="n">
         <v>0.6949151890185457</v>
@@ -6027,10 +6027,10 @@
         <v>1.433365431557006</v>
       </c>
       <c r="B400" t="n">
-        <v>0.199529505190638</v>
+        <v>0.1995295051906381</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.7975948453630491</v>
+        <v>-0.797594845363049</v>
       </c>
       <c r="D400" t="n">
         <v>0.7083053206110773</v>
@@ -6055,10 +6055,10 @@
         <v>-0.9772177403092113</v>
       </c>
       <c r="B402" t="n">
-        <v>0.1949279320719663</v>
+        <v>0.1949279320719664</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.5429739347193564</v>
+        <v>-0.5429739347193563</v>
       </c>
       <c r="D402" t="n">
         <v>-0.7096314588550329</v>
@@ -6072,7 +6072,7 @@
         <v>-0.7101963685048214</v>
       </c>
       <c r="C403" t="n">
-        <v>0.08253240624763798</v>
+        <v>0.08253240624763797</v>
       </c>
       <c r="D403" t="n">
         <v>0.7813672270994412</v>
@@ -6083,7 +6083,7 @@
         <v>0.0671991739349012</v>
       </c>
       <c r="B404" t="n">
-        <v>-0.3544439609587778</v>
+        <v>-0.3544439609587777</v>
       </c>
       <c r="C404" t="n">
         <v>-0.3558587796669309</v>
@@ -6097,7 +6097,7 @@
         <v>0.2898343231727994</v>
       </c>
       <c r="B405" t="n">
-        <v>0.09403544785662969</v>
+        <v>0.09403544785662972</v>
       </c>
       <c r="C405" t="n">
         <v>0.1506278927094814</v>
@@ -6114,7 +6114,7 @@
         <v>0.8986264948332932</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.83530537017294</v>
+        <v>-0.8353053701729399</v>
       </c>
       <c r="D406" t="n">
         <v>0.03007443935265066</v>
@@ -6159,7 +6159,7 @@
         <v>2.046105841645003</v>
       </c>
       <c r="D409" t="n">
-        <v>0.02522498944396294</v>
+        <v>0.02522498944396293</v>
       </c>
     </row>
     <row r="410">
@@ -6170,7 +6170,7 @@
         <v>-0.1654145874255018</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.8524674599611922</v>
+        <v>-0.8524674599611921</v>
       </c>
       <c r="D410" t="n">
         <v>0.7570116888687216</v>
@@ -6195,7 +6195,7 @@
         <v>1.331644350404224</v>
       </c>
       <c r="B412" t="n">
-        <v>0.08023072850061461</v>
+        <v>0.08023072850061463</v>
       </c>
       <c r="C412" t="n">
         <v>-0.2007134879811314</v>
@@ -6212,7 +6212,7 @@
         <v>-0.695673187918382</v>
       </c>
       <c r="C413" t="n">
-        <v>0.2765676844844808</v>
+        <v>0.2765676844844807</v>
       </c>
       <c r="D413" t="n">
         <v>0.5396659354466546</v>
@@ -6237,10 +6237,10 @@
         <v>0.772720776529655</v>
       </c>
       <c r="B415" t="n">
-        <v>0.1896078977228701</v>
+        <v>0.1896078977228702</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.2340724439843099</v>
+        <v>-0.2340724439843098</v>
       </c>
       <c r="D415" t="n">
         <v>0.8440710852391516</v>
@@ -6251,10 +6251,10 @@
         <v>1.210502835801222</v>
       </c>
       <c r="B416" t="n">
-        <v>-0.0294885651170811</v>
+        <v>-0.02948856511708107</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.3179605085056651</v>
+        <v>-0.317960508505665</v>
       </c>
       <c r="D416" t="n">
         <v>1.148461168779505</v>
@@ -6268,7 +6268,7 @@
         <v>-0.8762122313922143</v>
       </c>
       <c r="C417" t="n">
-        <v>0.3345962806946918</v>
+        <v>0.3345962806946917</v>
       </c>
       <c r="D417" t="n">
         <v>0.6839544905841527</v>
@@ -6279,10 +6279,10 @@
         <v>0.3039709990536812</v>
       </c>
       <c r="B418" t="n">
-        <v>0.3602253337289345</v>
+        <v>0.3602253337289346</v>
       </c>
       <c r="C418" t="n">
-        <v>-1.395687915393104</v>
+        <v>-1.395687915393103</v>
       </c>
       <c r="D418" t="n">
         <v>-0.6548279666830678</v>
@@ -6324,7 +6324,7 @@
         <v>0.2278402989133207</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.7111393782820956</v>
+        <v>-0.7111393782820955</v>
       </c>
       <c r="D421" t="n">
         <v>-1.109593371226892</v>
@@ -6352,7 +6352,7 @@
         <v>1.089070039555122</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.626089129291187</v>
+        <v>-0.6260891292911869</v>
       </c>
       <c r="D423" t="n">
         <v>-0.121482640803325</v>
@@ -6380,7 +6380,7 @@
         <v>0.2200569689170545</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.5161342691995006</v>
+        <v>-0.5161342691995005</v>
       </c>
       <c r="D425" t="n">
         <v>-0.7954620140350093</v>
@@ -6422,7 +6422,7 @@
         <v>-1.928928996161936</v>
       </c>
       <c r="C428" t="n">
-        <v>1.75891151494683</v>
+        <v>1.758911514946829</v>
       </c>
       <c r="D428" t="n">
         <v>0.3332780555367039</v>
@@ -6433,7 +6433,7 @@
         <v>0.5456591681359858</v>
       </c>
       <c r="B429" t="n">
-        <v>-0.02984779573229339</v>
+        <v>-0.02984779573229335</v>
       </c>
       <c r="C429" t="n">
         <v>-1.006442504450692</v>
@@ -6464,7 +6464,7 @@
         <v>-0.5264755681533945</v>
       </c>
       <c r="C431" t="n">
-        <v>0.01049770186124269</v>
+        <v>0.0104977018612427</v>
       </c>
       <c r="D431" t="n">
         <v>0.9329619728857755</v>
@@ -6478,7 +6478,7 @@
         <v>0.8235815086934692</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.3193422295063354</v>
+        <v>-0.3193422295063353</v>
       </c>
       <c r="D432" t="n">
         <v>0.780147802316577</v>
@@ -6506,7 +6506,7 @@
         <v>0.9835759822211131</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.9454422175254684</v>
+        <v>-0.9454422175254683</v>
       </c>
       <c r="D434" t="n">
         <v>-0.3424857269332255</v>
@@ -6517,10 +6517,10 @@
         <v>-0.269502153611162</v>
       </c>
       <c r="B435" t="n">
-        <v>0.07704897162302012</v>
+        <v>0.07704897162302014</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.9924133599123758</v>
+        <v>-0.9924133599123757</v>
       </c>
       <c r="D435" t="n">
         <v>0.257174649396872</v>
@@ -6531,7 +6531,7 @@
         <v>-0.1264207979752068</v>
       </c>
       <c r="B436" t="n">
-        <v>-0.008961101390664701</v>
+        <v>-0.008961101390664672</v>
       </c>
       <c r="C436" t="n">
         <v>-1.088152480932478</v>
@@ -6576,7 +6576,7 @@
         <v>0.8965053235815634</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.4067829617956695</v>
+        <v>-0.4067829617956694</v>
       </c>
       <c r="D439" t="n">
         <v>-0.4874042397384734</v>
@@ -6601,10 +6601,10 @@
         <v>-1.056019210813533</v>
       </c>
       <c r="B441" t="n">
-        <v>0.1853655552194107</v>
+        <v>0.1853655552194108</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.5042912754275</v>
+        <v>-0.5042912754274999</v>
       </c>
       <c r="D441" t="n">
         <v>-0.8606235545556274</v>
@@ -6618,7 +6618,7 @@
         <v>0.6830539132663768</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.420008137295583</v>
+        <v>-0.4200081372955829</v>
       </c>
       <c r="D442" t="n">
         <v>0.2425650930214761</v>
@@ -6632,7 +6632,7 @@
         <v>1.140388698871162</v>
       </c>
       <c r="C443" t="n">
-        <v>0.009691429186626806</v>
+        <v>0.009691429186626811</v>
       </c>
       <c r="D443" t="n">
         <v>-1.298957327855451</v>
@@ -6646,7 +6646,7 @@
         <v>-1.502385406146775</v>
       </c>
       <c r="C444" t="n">
-        <v>0.8527301377649837</v>
+        <v>0.8527301377649836</v>
       </c>
       <c r="D444" t="n">
         <v>0.3095345837993138</v>
@@ -6660,7 +6660,7 @@
         <v>-0.959741902538957</v>
       </c>
       <c r="C445" t="n">
-        <v>0.5371089401960673</v>
+        <v>0.5371089401960671</v>
       </c>
       <c r="D445" t="n">
         <v>0.9213939161618478</v>
@@ -6716,7 +6716,7 @@
         <v>-1.432660454356047</v>
       </c>
       <c r="C449" t="n">
-        <v>0.981019638477435</v>
+        <v>0.9810196384774349</v>
       </c>
       <c r="D449" t="n">
         <v>0.7691871038821839</v>
@@ -6727,10 +6727,10 @@
         <v>0.6751987080147596</v>
       </c>
       <c r="B450" t="n">
-        <v>-0.06914078254860881</v>
+        <v>-0.06914078254860878</v>
       </c>
       <c r="C450" t="n">
-        <v>0.3857139682653382</v>
+        <v>0.3857139682653381</v>
       </c>
       <c r="D450" t="n">
         <v>0.9061722932931225</v>
@@ -6741,10 +6741,10 @@
         <v>-0.6538937671920122</v>
       </c>
       <c r="B451" t="n">
-        <v>0.2211175545429193</v>
+        <v>0.2211175545429194</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.6333916560869935</v>
+        <v>-0.6333916560869934</v>
       </c>
       <c r="D451" t="n">
         <v>-0.3704995395125375</v>
@@ -6758,7 +6758,7 @@
         <v>1.770821322348955</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.1503813403591823</v>
+        <v>-0.1503813403591822</v>
       </c>
       <c r="D452" t="n">
         <v>-3.001820476374037</v>
@@ -6772,7 +6772,7 @@
         <v>0.7113818132088315</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.7834044462898097</v>
+        <v>-0.7834044462898095</v>
       </c>
       <c r="D453" t="n">
         <v>0.5530598336022222</v>
@@ -6786,10 +6786,10 @@
         <v>0.7135029844605612</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.05939462084688759</v>
+        <v>-0.05939462084688758</v>
       </c>
       <c r="D454" t="n">
-        <v>0.03619510428594569</v>
+        <v>0.03619510428594568</v>
       </c>
     </row>
     <row r="455">
@@ -6800,7 +6800,7 @@
         <v>0.8264211411756234</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.5802928413730054</v>
+        <v>-0.5802928413730053</v>
       </c>
       <c r="D455" t="n">
         <v>0.7016102548148115</v>
@@ -6811,10 +6811,10 @@
         <v>-1.357648285301656</v>
       </c>
       <c r="B456" t="n">
-        <v>0.4844849141528419</v>
+        <v>0.484484914152842</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.4896862218358867</v>
+        <v>-0.4896862218358866</v>
       </c>
       <c r="D456" t="n">
         <v>-1.722695669391264</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>-0.03038238059236426</v>
+        <v>-0.03038238059236427</v>
       </c>
       <c r="B458" t="n">
         <v>0.7821673506254241</v>
@@ -6895,7 +6895,7 @@
         <v>0.6420964917194273</v>
       </c>
       <c r="B462" t="n">
-        <v>0.258289370107505</v>
+        <v>0.2582893701075051</v>
       </c>
       <c r="C462" t="n">
         <v>-0.1799876729710771</v>
@@ -6912,7 +6912,7 @@
         <v>1.283755926780409</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.3073018141108646</v>
+        <v>-0.3073018141108645</v>
       </c>
       <c r="D463" t="n">
         <v>-2.657227040629524</v>
@@ -6923,10 +6923,10 @@
         <v>-0.6530189728924527</v>
       </c>
       <c r="B464" t="n">
-        <v>0.04908030229577775</v>
+        <v>0.04908030229577778</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.4150737485269339</v>
+        <v>-0.4150737485269338</v>
       </c>
       <c r="D464" t="n">
         <v>-0.1330648221386372</v>
@@ -6982,7 +6982,7 @@
         <v>-1.401510028151211</v>
       </c>
       <c r="C468" t="n">
-        <v>1.54948794680589</v>
+        <v>1.549487946805889</v>
       </c>
       <c r="D468" t="n">
         <v>0.4069426121108075</v>
@@ -6996,7 +6996,7 @@
         <v>0.1517347271476318</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.5019231374003426</v>
+        <v>-0.5019231374003424</v>
       </c>
       <c r="D469" t="n">
         <v>0.5110504144223618</v>
@@ -7010,7 +7010,7 @@
         <v>1.061460600843092</v>
       </c>
       <c r="C470" t="n">
-        <v>-1.061499409945891</v>
+        <v>-1.06149940994589</v>
       </c>
       <c r="D470" t="n">
         <v>-0.1702125500799434</v>
@@ -7038,10 +7038,10 @@
         <v>0.9602259922323145</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.8710347678394892</v>
+        <v>-0.8710347678394891</v>
       </c>
       <c r="D472" t="n">
-        <v>-0.01437100447066125</v>
+        <v>-0.01437100447066126</v>
       </c>
     </row>
     <row r="473">
@@ -7066,10 +7066,10 @@
         <v>0.9598667616171022</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.9547258714646167</v>
+        <v>-0.9547258714646166</v>
       </c>
       <c r="D474" t="n">
-        <v>0.08181759905796818</v>
+        <v>0.08181759905796816</v>
       </c>
     </row>
     <row r="475">
@@ -7077,13 +7077,13 @@
         <v>-0.4988557230696773</v>
       </c>
       <c r="B475" t="n">
-        <v>-0.007541285149587571</v>
+        <v>-0.007541285149587541</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.8461554967370565</v>
+        <v>-0.8461554967370564</v>
       </c>
       <c r="D475" t="n">
-        <v>0.005733025733315618</v>
+        <v>0.00573302573331561</v>
       </c>
     </row>
     <row r="476">
@@ -7094,7 +7094,7 @@
         <v>-0.7250616734867013</v>
       </c>
       <c r="C476" t="n">
-        <v>0.6685774588827184</v>
+        <v>0.6685774588827182</v>
       </c>
       <c r="D476" t="n">
         <v>0.7003908300319474</v>
@@ -7108,7 +7108,7 @@
         <v>-1.59867631724344</v>
       </c>
       <c r="C477" t="n">
-        <v>1.506870676861908</v>
+        <v>1.506870676861907</v>
       </c>
       <c r="D477" t="n">
         <v>1.147284117830795</v>
@@ -7119,10 +7119,10 @@
         <v>-0.8023988474852365</v>
       </c>
       <c r="B478" t="n">
-        <v>0.1241252884356017</v>
+        <v>0.1241252884356018</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.4790272970774649</v>
+        <v>-0.4790272970774648</v>
       </c>
       <c r="D478" t="n">
         <v>-0.5391473994437911</v>
@@ -7136,7 +7136,7 @@
         <v>1.809755078550058</v>
       </c>
       <c r="C479" t="n">
-        <v>0.3661791331775022</v>
+        <v>0.3661791331775021</v>
       </c>
       <c r="D479" t="n">
         <v>-2.156792059275729</v>
@@ -7175,10 +7175,10 @@
         <v>0.5410052624623291</v>
       </c>
       <c r="B482" t="n">
-        <v>-0.03905094196963676</v>
+        <v>-0.03905094196963673</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.9940028688994756</v>
+        <v>-0.9940028688994755</v>
       </c>
       <c r="D482" t="n">
         <v>0.6675181511363579</v>
@@ -7192,7 +7192,7 @@
         <v>-0.809651930259309</v>
       </c>
       <c r="C483" t="n">
-        <v>0.2390644869337768</v>
+        <v>0.2390644869337767</v>
       </c>
       <c r="D483" t="n">
         <v>0.9749685671433591</v>
@@ -7203,10 +7203,10 @@
         <v>0.514166573351843</v>
       </c>
       <c r="B484" t="n">
-        <v>-0.2673659466447262</v>
+        <v>-0.2673659466447261</v>
       </c>
       <c r="C484" t="n">
-        <v>0.7579815803165526</v>
+        <v>0.7579815803165525</v>
       </c>
       <c r="D484" t="n">
         <v>1.080898444323517</v>
@@ -7220,7 +7220,7 @@
         <v>0.1439513971513656</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.7297066861603926</v>
+        <v>-0.7297066861603925</v>
       </c>
       <c r="D485" t="n">
         <v>-0.4959260886071381</v>
@@ -7234,10 +7234,10 @@
         <v>1.222156429381388</v>
       </c>
       <c r="C486" t="n">
-        <v>-1.152493040366825</v>
+        <v>-1.152493040366824</v>
       </c>
       <c r="D486" t="n">
-        <v>0.001495642317957435</v>
+        <v>0.001495642317957428</v>
       </c>
     </row>
     <row r="487">
@@ -7248,7 +7248,7 @@
         <v>1.243043123723017</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.4075731090167931</v>
+        <v>-0.407573109016793</v>
       </c>
       <c r="D487" t="n">
         <v>-0.3559041077485262</v>
@@ -7276,7 +7276,7 @@
         <v>0.7269484732013638</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.6695126719097847</v>
+        <v>-0.6695126719097846</v>
       </c>
       <c r="D489" t="n">
         <v>-0.5963991575890741</v>
@@ -7287,7 +7287,7 @@
         <v>0.2929135991072488</v>
       </c>
       <c r="B490" t="n">
-        <v>0.4954500010267026</v>
+        <v>0.4954500010267027</v>
       </c>
       <c r="C490" t="n">
         <v>0.1484624746690845</v>
@@ -7301,10 +7301,10 @@
         <v>1.655668158961071</v>
       </c>
       <c r="B491" t="n">
-        <v>0.2540470276040456</v>
+        <v>0.2540470276040457</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.6013941490858093</v>
+        <v>-0.6013941490858092</v>
       </c>
       <c r="D491" t="n">
         <v>1.0455869158622</v>
@@ -7318,7 +7318,7 @@
         <v>0.5103153060085825</v>
       </c>
       <c r="C492" t="n">
-        <v>-1.473458673950338</v>
+        <v>-1.473458673950337</v>
       </c>
       <c r="D492" t="n">
         <v>-2.438060153979612</v>
@@ -7332,7 +7332,7 @@
         <v>0.8161574093124152</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.4054030837039698</v>
+        <v>-0.4054030837039697</v>
       </c>
       <c r="D493" t="n">
         <v>0.780147802316577</v>
@@ -7343,7 +7343,7 @@
         <v>0.1463750563994344</v>
       </c>
       <c r="B494" t="n">
-        <v>0.04059561728885891</v>
+        <v>0.04059561728885894</v>
       </c>
       <c r="C494" t="n">
         <v>-1.027751139422683</v>
@@ -7374,7 +7374,7 @@
         <v>0.8483684211431169</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.7725312833635614</v>
+        <v>-0.7725312833635612</v>
       </c>
       <c r="D496" t="n">
         <v>0.4039011124593394</v>
@@ -7405,7 +7405,7 @@
         <v>-0.1677507574066213</v>
       </c>
       <c r="D498" t="n">
-        <v>0.02277672347064497</v>
+        <v>0.02277672347064496</v>
       </c>
     </row>
     <row r="499">
@@ -7416,7 +7416,7 @@
         <v>0.9980991628075527</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.5143581656791324</v>
+        <v>-0.5143581656791323</v>
       </c>
       <c r="D499" t="n">
         <v>-1.105968054304863</v>
@@ -7430,7 +7430,7 @@
         <v>-1.111251691059682</v>
       </c>
       <c r="C500" t="n">
-        <v>1.581462417444942</v>
+        <v>1.581462417444941</v>
       </c>
       <c r="D500" t="n">
         <v>-0.2822207183592432</v>
@@ -7444,7 +7444,7 @@
         <v>-1.519371882380385</v>
       </c>
       <c r="C501" t="n">
-        <v>1.119583356700706</v>
+        <v>1.119583356700705</v>
       </c>
       <c r="D501" t="n">
         <v>0.2754424801208603</v>
@@ -7458,7 +7458,7 @@
         <v>-0.491785865077728</v>
       </c>
       <c r="C502" t="n">
-        <v>0.2720295211445001</v>
+        <v>0.2720295211445</v>
       </c>
       <c r="D502" t="n">
         <v>0.6145503876240019</v>
@@ -7472,7 +7472,7 @@
         <v>-1.494961306765721</v>
       </c>
       <c r="C503" t="n">
-        <v>0.8359596661329735</v>
+        <v>0.8359596661329733</v>
       </c>
       <c r="D503" t="n">
         <v>0.7235269434798027</v>
@@ -7489,7 +7489,7 @@
         <v>-1.068018700429213</v>
       </c>
       <c r="D504" t="n">
-        <v>0.003284759759997544</v>
+        <v>0.003284759759997537</v>
       </c>
     </row>
     <row r="505">
@@ -7514,7 +7514,7 @@
         <v>-0.5271769231640471</v>
       </c>
       <c r="C506" t="n">
-        <v>0.5846790279984037</v>
+        <v>0.5846790279984035</v>
       </c>
       <c r="D506" t="n">
         <v>0.9347887559581745</v>
@@ -7528,7 +7528,7 @@
         <v>0.954563833487778</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.5380441532231337</v>
+        <v>-0.5380441532231336</v>
       </c>
       <c r="D507" t="n">
         <v>-0.5927267586290971</v>
@@ -7542,7 +7542,7 @@
         <v>-0.3169226653242498</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.7166681051937474</v>
+        <v>-0.7166681051937472</v>
       </c>
       <c r="D508" t="n">
         <v>0.7990229913301</v>
@@ -7556,7 +7556,7 @@
         <v>-0.2663036503968841</v>
       </c>
       <c r="C509" t="n">
-        <v>0.07147495242433458</v>
+        <v>0.07147495242433456</v>
       </c>
       <c r="D509" t="n">
         <v>0.9999314636636133</v>
@@ -7567,7 +7567,7 @@
         <v>-1.166453243189927</v>
       </c>
       <c r="B510" t="n">
-        <v>0.4264264042466275</v>
+        <v>0.4264264042466276</v>
       </c>
       <c r="C510" t="n">
         <v>-0.44645848829541</v>
@@ -7584,7 +7584,7 @@
         <v>-0.9264703050823905</v>
       </c>
       <c r="C511" t="n">
-        <v>0.4913126522778856</v>
+        <v>0.4913126522778855</v>
       </c>
       <c r="D511" t="n">
         <v>1.264141736018782</v>
@@ -7598,7 +7598,7 @@
         <v>0.8051752162187824</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.06589087496807834</v>
+        <v>-0.06589087496807833</v>
       </c>
       <c r="D512" t="n">
         <v>0.1293233753479276</v>
@@ -7637,10 +7637,10 @@
         <v>0.5401654599347518</v>
       </c>
       <c r="B515" t="n">
-        <v>-0.2719675197633979</v>
+        <v>-0.2719675197633978</v>
       </c>
       <c r="C515" t="n">
-        <v>0.7439754721403684</v>
+        <v>0.7439754721403683</v>
       </c>
       <c r="D515" t="n">
         <v>0.420337451907134</v>
@@ -7654,7 +7654,7 @@
         <v>0.5018306210016638</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.462051801822481</v>
+        <v>-0.4620518018224809</v>
       </c>
       <c r="D516" t="n">
         <v>-2.007589081017175</v>
@@ -7682,7 +7682,7 @@
         <v>-1.439383198726449</v>
       </c>
       <c r="C518" t="n">
-        <v>0.960309948920873</v>
+        <v>0.9603099489208728</v>
       </c>
       <c r="D518" t="n">
         <v>0.945137387899238</v>
@@ -7710,7 +7710,7 @@
         <v>1.387470937258128</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.6191782206516223</v>
+        <v>-0.6191782206516222</v>
       </c>
       <c r="D520" t="n">
         <v>-2.007024096561794</v>
@@ -7752,7 +7752,7 @@
         <v>-1.233715118407528</v>
       </c>
       <c r="C523" t="n">
-        <v>0.5382837946647931</v>
+        <v>0.538283794664793</v>
       </c>
       <c r="D523" t="n">
         <v>0.0306865058459801</v>
@@ -7766,10 +7766,10 @@
         <v>0.1135194321769533</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.2753259612900844</v>
+        <v>-0.2753259612900843</v>
       </c>
       <c r="D524" t="n">
-        <v>0.08732619749793376</v>
+        <v>0.08732619749793374</v>
       </c>
     </row>
     <row r="525">
@@ -7780,7 +7780,7 @@
         <v>-1.523973455499056</v>
       </c>
       <c r="C525" t="n">
-        <v>0.9470870770571728</v>
+        <v>0.9470870770571727</v>
       </c>
       <c r="D525" t="n">
         <v>0.5956770818919969</v>
@@ -7791,7 +7791,7 @@
         <v>1.321251794125457</v>
       </c>
       <c r="B526" t="n">
-        <v>-0.09320923376783206</v>
+        <v>-0.09320923376783204</v>
       </c>
       <c r="C526" t="n">
         <v>-0.4239565697649875</v>
@@ -7805,7 +7805,7 @@
         <v>-0.748056625596599</v>
       </c>
       <c r="B527" t="n">
-        <v>-0.3979821983359139</v>
+        <v>-0.3979821983359138</v>
       </c>
       <c r="C527" t="n">
         <v>0.01542748335746543</v>
@@ -7822,7 +7822,7 @@
         <v>1.391713279761588</v>
       </c>
       <c r="C528" t="n">
-        <v>-1.193359546788784</v>
+        <v>-1.193359546788783</v>
       </c>
       <c r="D528" t="n">
         <v>-1.322686674981457</v>
@@ -7836,7 +7836,7 @@
         <v>-0.1109141712318662</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.04575709446481342</v>
+        <v>-0.0457570944648134</v>
       </c>
       <c r="D529" t="n">
         <v>0.9725344257814256</v>
@@ -7847,10 +7847,10 @@
         <v>0.7659673645370556</v>
       </c>
       <c r="B530" t="n">
-        <v>0.1952871626871786</v>
+        <v>0.1952871626871787</v>
       </c>
       <c r="C530" t="n">
-        <v>0.139386147989123</v>
+        <v>0.1393861479891229</v>
       </c>
       <c r="D530" t="n">
         <v>0.656557452701965</v>
@@ -7861,7 +7861,7 @@
         <v>-1.026556138804368</v>
       </c>
       <c r="B531" t="n">
-        <v>0.1262464596873314</v>
+        <v>0.1262464596873315</v>
       </c>
       <c r="C531" t="n">
         <v>-0.4567211876251634</v>
@@ -7878,7 +7878,7 @@
         <v>-0.4213458733005301</v>
       </c>
       <c r="C532" t="n">
-        <v>0.0772110065951732</v>
+        <v>0.07721100659517319</v>
       </c>
       <c r="D532" t="n">
         <v>0.3661554426360881</v>
@@ -7892,7 +7892,7 @@
         <v>-0.179934346767987</v>
       </c>
       <c r="C533" t="n">
-        <v>0.6610676048277246</v>
+        <v>0.6610676048277245</v>
       </c>
       <c r="D533" t="n">
         <v>0.9518324536955037</v>
@@ -7920,7 +7920,7 @@
         <v>0.5676553546843724</v>
       </c>
       <c r="C535" t="n">
-        <v>0.158529364920717</v>
+        <v>0.1585293649207169</v>
       </c>
       <c r="D535" t="n">
         <v>0.4775656690334429</v>
@@ -7931,10 +7931,10 @@
         <v>1.203889390896552</v>
       </c>
       <c r="B536" t="n">
-        <v>0.16199845901084</v>
+        <v>0.1619984590108401</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.09866701100932015</v>
+        <v>-0.09866701100932014</v>
       </c>
       <c r="D536" t="n">
         <v>0.8538123588906805</v>
@@ -7948,7 +7948,7 @@
         <v>-1.480078895564069</v>
       </c>
       <c r="C537" t="n">
-        <v>1.680564847336299</v>
+        <v>1.680564847336298</v>
       </c>
       <c r="D537" t="n">
         <v>1.42549188006803</v>
@@ -7979,7 +7979,7 @@
         <v>-0.249863870225715</v>
       </c>
       <c r="D539" t="n">
-        <v>0.06359685037192826</v>
+        <v>0.06359685037192825</v>
       </c>
     </row>
     <row r="540">
@@ -7993,7 +7993,7 @@
         <v>-1.139869113918553</v>
       </c>
       <c r="D540" t="n">
-        <v>-0.06973948109800748</v>
+        <v>-0.0697394810980075</v>
       </c>
     </row>
     <row r="541">
@@ -8021,7 +8021,7 @@
         <v>-0.4586954038598657</v>
       </c>
       <c r="D542" t="n">
-        <v>0.01547900758863928</v>
+        <v>0.01547900758863927</v>
       </c>
     </row>
     <row r="543">
@@ -8029,7 +8029,7 @@
         <v>0.9798370748933672</v>
       </c>
       <c r="B543" t="n">
-        <v>-0.04153134383657874</v>
+        <v>-0.04153134383657871</v>
       </c>
       <c r="C543" t="n">
         <v>0.1749082183964851</v>
@@ -8060,7 +8060,7 @@
         <v>1.190304648165899</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.5279772629715012</v>
+        <v>-0.527977262971501</v>
       </c>
       <c r="D545" t="n">
         <v>-0.5769071938784266</v>
@@ -8088,7 +8088,7 @@
         <v>1.69967655431715</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.2944719425851342</v>
+        <v>-0.2944719425851341</v>
       </c>
       <c r="D547" t="n">
         <v>-3.096784946916007</v>
@@ -8099,10 +8099,10 @@
         <v>0.4560102483171259</v>
       </c>
       <c r="B548" t="n">
-        <v>-0.4783352444709937</v>
+        <v>-0.4783352444709936</v>
       </c>
       <c r="C548" t="n">
-        <v>0.9741087298378704</v>
+        <v>0.9741087298378703</v>
       </c>
       <c r="D548" t="n">
         <v>1.182595646292112</v>
@@ -8113,7 +8113,7 @@
         <v>-0.5608856372628439</v>
       </c>
       <c r="B549" t="n">
-        <v>-0.02100388011016234</v>
+        <v>-0.02100388011016231</v>
       </c>
       <c r="C549" t="n">
         <v>1.422972245977593</v>
@@ -8130,7 +8130,7 @@
         <v>-1.023804695585148</v>
       </c>
       <c r="C550" t="n">
-        <v>0.6881122939705543</v>
+        <v>0.6881122939705542</v>
       </c>
       <c r="D550" t="n">
         <v>1.205100860431459</v>
@@ -8158,7 +8158,7 @@
         <v>-0.5169183231667706</v>
       </c>
       <c r="C552" t="n">
-        <v>0.9176696426147593</v>
+        <v>0.9176696426147591</v>
       </c>
       <c r="D552" t="n">
         <v>0.4958334997574313</v>
@@ -8172,7 +8172,7 @@
         <v>1.019327981544622</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.8994616387102317</v>
+        <v>-0.8994616387102315</v>
       </c>
       <c r="D553" t="n">
         <v>-0.3126827969118734</v>
@@ -8183,10 +8183,10 @@
         <v>-0.870072934499161</v>
       </c>
       <c r="B554" t="n">
-        <v>0.2841197619632456</v>
+        <v>0.2841197619632457</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.759124120602806</v>
+        <v>-0.7591241206028059</v>
       </c>
       <c r="D554" t="n">
         <v>-1.263645799394133</v>
@@ -8203,7 +8203,7 @@
         <v>2.542332118327876</v>
       </c>
       <c r="D555" t="n">
-        <v>-0.03504001913001924</v>
+        <v>-0.03504001913001925</v>
       </c>
     </row>
     <row r="556">
@@ -8211,10 +8211,10 @@
         <v>-0.9115031925263001</v>
       </c>
       <c r="B556" t="n">
-        <v>-0.07834392878595219</v>
+        <v>-0.07834392878595216</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.3319749097722169</v>
+        <v>-0.3319749097722168</v>
       </c>
       <c r="D556" t="n">
         <v>-0.2530298548312206</v>
@@ -8242,7 +8242,7 @@
         <v>0.9542046028725656</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.8522831690641373</v>
+        <v>-0.8522831690641371</v>
       </c>
       <c r="D558" t="n">
         <v>0.1670737533749737</v>
@@ -8295,10 +8295,10 @@
         <v>-1.326855525957161</v>
       </c>
       <c r="B562" t="n">
-        <v>-0.3512582696506357</v>
+        <v>-0.3512582696506356</v>
       </c>
       <c r="C562" t="n">
-        <v>0.369726732945812</v>
+        <v>0.3697267329458119</v>
       </c>
       <c r="D562" t="n">
         <v>0.3570215272740939</v>
@@ -8315,7 +8315,7 @@
         <v>1.319746307264629</v>
       </c>
       <c r="D563" t="n">
-        <v>-0.001564690148690077</v>
+        <v>-0.001564690148690084</v>
       </c>
     </row>
     <row r="564">
@@ -8323,7 +8323,7 @@
         <v>-0.6524940963127169</v>
       </c>
       <c r="B564" t="n">
-        <v>-0.07870315940116447</v>
+        <v>-0.07870315940116444</v>
       </c>
       <c r="C564" t="n">
         <v>1.423962809549264</v>
@@ -8343,7 +8343,7 @@
         <v>-1.002295959266953</v>
       </c>
       <c r="D565" t="n">
-        <v>-0.04723426695866097</v>
+        <v>-0.04723426695866098</v>
       </c>
     </row>
     <row r="566">
@@ -8368,7 +8368,7 @@
         <v>-1.16611133786853</v>
       </c>
       <c r="C567" t="n">
-        <v>0.4696123991496527</v>
+        <v>0.4696123991496526</v>
       </c>
       <c r="D567" t="n">
         <v>0.315622291306045</v>
@@ -8399,7 +8399,7 @@
         <v>1.596873743711171</v>
       </c>
       <c r="D569" t="n">
-        <v>-0.04294980150535438</v>
+        <v>-0.04294980150535439</v>
       </c>
     </row>
     <row r="570">
@@ -8407,13 +8407,13 @@
         <v>-0.5478686980853983</v>
       </c>
       <c r="B570" t="n">
-        <v>0.04801971666991287</v>
+        <v>0.04801971666991289</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.8939329117985799</v>
+        <v>-0.8939329117985798</v>
       </c>
       <c r="D570" t="n">
-        <v>-0.1117837409859497</v>
+        <v>-0.1117837409859498</v>
       </c>
     </row>
     <row r="571">
@@ -8435,7 +8435,7 @@
         <v>-0.3800201662403138</v>
       </c>
       <c r="B572" t="n">
-        <v>-0.362231567509987</v>
+        <v>-0.3622315675099869</v>
       </c>
       <c r="C572" t="n">
         <v>-0.3858613377074941</v>
@@ -8452,7 +8452,7 @@
         <v>0.650842901435675</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.8676714589682344</v>
+        <v>-0.8676714589682343</v>
       </c>
       <c r="D573" t="n">
         <v>0.4532148390065182</v>
@@ -8480,7 +8480,7 @@
         <v>-0.5328561881283557</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.08130220123430744</v>
+        <v>-0.08130220123430743</v>
       </c>
       <c r="D575" t="n">
         <v>0.7984109248367706</v>
@@ -8491,7 +8491,7 @@
         <v>0.09414983671573096</v>
       </c>
       <c r="B576" t="n">
-        <v>-0.0507344900739221</v>
+        <v>-0.05073449007392208</v>
       </c>
       <c r="C576" t="n">
         <v>-1.048875483497619</v>
@@ -8505,10 +8505,10 @@
         <v>-0.3373267052446108</v>
       </c>
       <c r="B577" t="n">
-        <v>-0.1937390661240021</v>
+        <v>-0.193739066124002</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.6876653252697077</v>
+        <v>-0.6876653252697076</v>
       </c>
       <c r="D577" t="n">
         <v>0.3010127349306492</v>
@@ -8536,7 +8536,7 @@
         <v>-0.8401010014534933</v>
       </c>
       <c r="C579" t="n">
-        <v>0.2070900162947244</v>
+        <v>0.2070900162947243</v>
       </c>
       <c r="D579" t="n">
         <v>0.4946140749745671</v>
@@ -8550,7 +8550,7 @@
         <v>-0.5986809218110644</v>
       </c>
       <c r="C580" t="n">
-        <v>0.3489940070271181</v>
+        <v>0.348994007027118</v>
       </c>
       <c r="D580" t="n">
         <v>0.7789283775337128</v>
@@ -8564,7 +8564,7 @@
         <v>-0.2744462110083626</v>
       </c>
       <c r="C581" t="n">
-        <v>0.2915643562323361</v>
+        <v>0.291564356232336</v>
       </c>
       <c r="D581" t="n">
         <v>0.5384483939453084</v>
@@ -8617,7 +8617,7 @@
         <v>0.07355018054970332</v>
       </c>
       <c r="B585" t="n">
-        <v>0.4830650979117647</v>
+        <v>0.4830650979117648</v>
       </c>
       <c r="C585" t="n">
         <v>-1.51351890769768</v>
@@ -8648,7 +8648,7 @@
         <v>-1.049652193660661</v>
       </c>
       <c r="C587" t="n">
-        <v>0.7402205451128716</v>
+        <v>0.7402205451128715</v>
       </c>
       <c r="D587" t="n">
         <v>1.034630925631602</v>
@@ -8662,7 +8662,7 @@
         <v>0.8812807879844713</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.6626017632702201</v>
+        <v>-0.66260176327022</v>
       </c>
       <c r="D588" t="n">
         <v>0.7576237553620512</v>
@@ -8673,13 +8673,13 @@
         <v>-0.3901117932800324</v>
       </c>
       <c r="B589" t="n">
-        <v>0.07668974100780783</v>
+        <v>0.07668974100780786</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.9910311781844628</v>
+        <v>-0.9910311781844627</v>
       </c>
       <c r="D589" t="n">
-        <v>0.08487793152461569</v>
+        <v>0.08487793152461567</v>
       </c>
     </row>
     <row r="590">
@@ -8732,7 +8732,7 @@
         <v>0.2703150426072307</v>
       </c>
       <c r="C593" t="n">
-        <v>-1.246849979659014</v>
+        <v>-1.246849979659013</v>
       </c>
       <c r="D593" t="n">
         <v>-0.1830188644019147</v>
@@ -8746,7 +8746,7 @@
         <v>0.5754557909004108</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.8662892772403215</v>
+        <v>-0.8662892772403213</v>
       </c>
       <c r="D594" t="n">
         <v>0.5396659354466546</v>
@@ -8788,7 +8788,7 @@
         <v>0.1145800178028181</v>
       </c>
       <c r="C597" t="n">
-        <v>0.6758799856785249</v>
+        <v>0.6758799856785248</v>
       </c>
       <c r="D597" t="n">
         <v>0.8264153210084929</v>
@@ -8799,10 +8799,10 @@
         <v>1.681002201876315</v>
       </c>
       <c r="B598" t="n">
-        <v>-0.3229406334400443</v>
+        <v>-0.3229406334400442</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.2846027043205933</v>
+        <v>-0.2846027043205932</v>
       </c>
       <c r="D598" t="n">
         <v>1.107076057422841</v>
@@ -8819,7 +8819,7 @@
         <v>-0.3850711904863706</v>
       </c>
       <c r="D599" t="n">
-        <v>0.01180660862866222</v>
+        <v>0.01180660862866221</v>
       </c>
     </row>
     <row r="600">
@@ -8830,7 +8830,7 @@
         <v>-0.3891331508478512</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.4176399992684255</v>
+        <v>-0.4176399992684254</v>
       </c>
       <c r="D600" t="n">
         <v>0.7661456042307159</v>
@@ -8844,7 +8844,7 @@
         <v>0.7563369587696833</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.06294222061519744</v>
+        <v>-0.06294222061519743</v>
       </c>
       <c r="D601" t="n">
         <v>-2.547007989792265</v>
@@ -8855,10 +8855,10 @@
         <v>-0.9140226001090314</v>
       </c>
       <c r="B602" t="n">
-        <v>-0.3753284314918361</v>
+        <v>-0.375328431491836</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.008253896914109361</v>
+        <v>-0.008253896914109353</v>
       </c>
       <c r="D602" t="n">
         <v>0.4702632449476424</v>
@@ -8872,7 +8872,7 @@
         <v>0.2158146264135951</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.835512697432127</v>
+        <v>-0.8355126974321269</v>
       </c>
       <c r="D603" t="n">
         <v>-0.4776582578831496</v>
@@ -8897,7 +8897,7 @@
         <v>0.4456526838103413</v>
       </c>
       <c r="B605" t="n">
-        <v>0.4749225373002863</v>
+        <v>0.4749225373002864</v>
       </c>
       <c r="C605" t="n">
         <v>0.1683889279131625</v>
@@ -8914,7 +8914,7 @@
         <v>-0.4616994457427104</v>
       </c>
       <c r="C606" t="n">
-        <v>0.3107075731639301</v>
+        <v>0.31070757316393</v>
       </c>
       <c r="D606" t="n">
         <v>0.9725344257814256</v>
@@ -8942,7 +8942,7 @@
         <v>-0.825937051482266</v>
       </c>
       <c r="C608" t="n">
-        <v>0.5424303398485321</v>
+        <v>0.542430339848532</v>
       </c>
       <c r="D608" t="n">
         <v>1.038284491776399</v>
@@ -8953,7 +8953,7 @@
         <v>0.1204496525376884</v>
       </c>
       <c r="B609" t="n">
-        <v>0.4812860510554753</v>
+        <v>0.4812860510554754</v>
       </c>
       <c r="C609" t="n">
         <v>-1.524576361520984</v>
@@ -8970,7 +8970,7 @@
         <v>0.658284107036501</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.9614294528449946</v>
+        <v>-0.9614294528449945</v>
       </c>
       <c r="D610" t="n">
         <v>0.4270372259071947</v>
@@ -8984,7 +8984,7 @@
         <v>-1.136021497289558</v>
       </c>
       <c r="C611" t="n">
-        <v>0.6048128085016686</v>
+        <v>0.6048128085016685</v>
       </c>
       <c r="D611" t="n">
         <v>0.4568684051513159</v>
@@ -8998,7 +8998,7 @@
         <v>-1.10877128919274</v>
       </c>
       <c r="C612" t="n">
-        <v>0.7406121632691135</v>
+        <v>0.7406121632691134</v>
       </c>
       <c r="D612" t="n">
         <v>0.1031457622486041</v>
@@ -9012,7 +9012,7 @@
         <v>-0.8655892689137937</v>
       </c>
       <c r="C613" t="n">
-        <v>0.2710389575728291</v>
+        <v>0.271038957572829</v>
       </c>
       <c r="D613" t="n">
         <v>0.6638645849915603</v>
@@ -9040,10 +9040,10 @@
         <v>1.131544783249031</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.6892317978946758</v>
+        <v>-0.6892317978946757</v>
       </c>
       <c r="D615" t="n">
-        <v>-0.04539806747867245</v>
+        <v>-0.04539806747867246</v>
       </c>
     </row>
     <row r="616">
@@ -9054,10 +9054,10 @@
         <v>0.7053604238490826</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.5799012232167634</v>
+        <v>-0.5799012232167633</v>
       </c>
       <c r="D616" t="n">
-        <v>-0.01375893797733181</v>
+        <v>-0.01375893797733182</v>
       </c>
     </row>
     <row r="617">
@@ -9065,10 +9065,10 @@
         <v>1.561540292328467</v>
       </c>
       <c r="B617" t="n">
-        <v>0.06572465413394701</v>
+        <v>0.06572465413394704</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.3530944162111051</v>
+        <v>-0.353094416211105</v>
       </c>
       <c r="D617" t="n">
         <v>1.333540659954759</v>
@@ -9110,10 +9110,10 @@
         <v>1.202347426885396</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.8674871680711793</v>
+        <v>-0.8674871680711792</v>
       </c>
       <c r="D620" t="n">
-        <v>-0.08499406139329674</v>
+        <v>-0.08499406139329675</v>
       </c>
     </row>
     <row r="621">
@@ -9121,10 +9121,10 @@
         <v>-0.1237124348237705</v>
       </c>
       <c r="B621" t="n">
-        <v>-0.2797559816255957</v>
+        <v>-0.2797559816255956</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.5388343004442572</v>
+        <v>-0.5388343004442571</v>
       </c>
       <c r="D621" t="n">
         <v>0.7704065286650481</v>
@@ -9138,7 +9138,7 @@
         <v>-0.5930187630665278</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.05287533036356496</v>
+        <v>-0.05287533036356495</v>
       </c>
       <c r="D622" t="n">
         <v>0.6443820376885027</v>
@@ -9163,7 +9163,7 @@
         <v>0.391415437237651</v>
       </c>
       <c r="B624" t="n">
-        <v>0.04589854541818317</v>
+        <v>0.0458985454181832</v>
       </c>
       <c r="C624" t="n">
         <v>0.4338830014831035</v>
@@ -9180,7 +9180,7 @@
         <v>-1.324343870759657</v>
       </c>
       <c r="C625" t="n">
-        <v>0.5696823562505485</v>
+        <v>0.5696823562505484</v>
       </c>
       <c r="D625" t="n">
         <v>1.050483447808836</v>
@@ -9208,7 +9208,7 @@
         <v>1.692594579331536</v>
       </c>
       <c r="C627" t="n">
-        <v>0.3037966645243655</v>
+        <v>0.3037966645243654</v>
       </c>
       <c r="D627" t="n">
         <v>-0.9963610699609329</v>
@@ -9219,10 +9219,10 @@
         <v>0.1695885979325458</v>
       </c>
       <c r="B628" t="n">
-        <v>0.07634761661236751</v>
+        <v>0.07634761661236754</v>
       </c>
       <c r="C628" t="n">
-        <v>0.714350710438768</v>
+        <v>0.7143507104387679</v>
       </c>
       <c r="D628" t="n">
         <v>0.6705596507878262</v>
@@ -9236,7 +9236,7 @@
         <v>0.3347541724884062</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.6712864717939396</v>
+        <v>-0.6712864717939395</v>
       </c>
       <c r="D629" t="n">
         <v>1.044362782875541</v>
@@ -9264,7 +9264,7 @@
         <v>-1.097789096099107</v>
       </c>
       <c r="C631" t="n">
-        <v>0.7808797242756434</v>
+        <v>0.7808797242756433</v>
       </c>
       <c r="D631" t="n">
         <v>1.104015724956193</v>
@@ -9306,7 +9306,7 @@
         <v>-0.1445449993036451</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.4405358395913031</v>
+        <v>-0.440535839591303</v>
       </c>
       <c r="D634" t="n">
         <v>0.1865515924742365</v>
@@ -9320,7 +9320,7 @@
         <v>1.172257586306424</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.7533880664319674</v>
+        <v>-0.7533880664319673</v>
       </c>
       <c r="D635" t="n">
         <v>0.315622291306045</v>
@@ -9331,10 +9331,10 @@
         <v>1.05160519922923</v>
       </c>
       <c r="B636" t="n">
-        <v>-0.3728514508688486</v>
+        <v>-0.3728514508688485</v>
       </c>
       <c r="C636" t="n">
-        <v>0.2702557212603451</v>
+        <v>0.270255721260345</v>
       </c>
       <c r="D636" t="n">
         <v>1.721967473029253</v>
@@ -9359,7 +9359,7 @@
         <v>0.2061340045909444</v>
       </c>
       <c r="B638" t="n">
-        <v>0.07316585973477302</v>
+        <v>0.07316585973477305</v>
       </c>
       <c r="C638" t="n">
         <v>0.2676756487015743</v>
@@ -9387,10 +9387,10 @@
         <v>1.088696477530554</v>
       </c>
       <c r="B640" t="n">
-        <v>-0.09993197813823347</v>
+        <v>-0.09993197813823344</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.07715565605056866</v>
+        <v>-0.07715565605056865</v>
       </c>
       <c r="D640" t="n">
         <v>1.228218141064135</v>
@@ -9404,7 +9404,7 @@
         <v>0.7552763731438186</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.4985667394377273</v>
+        <v>-0.4985667394377272</v>
       </c>
       <c r="D641" t="n">
         <v>0.2431724513110108</v>
@@ -9418,7 +9418,7 @@
         <v>0.2076720658021166</v>
       </c>
       <c r="C642" t="n">
-        <v>-1.019066430898964</v>
+        <v>-1.019066430898963</v>
       </c>
       <c r="D642" t="n">
         <v>-0.739434388876385</v>
@@ -9443,10 +9443,10 @@
         <v>-0.4374276673546078</v>
       </c>
       <c r="B644" t="n">
-        <v>0.2352815045141466</v>
+        <v>0.2352815045141467</v>
       </c>
       <c r="C644" t="n">
-        <v>-1.11558878823155</v>
+        <v>-1.115588788231549</v>
       </c>
       <c r="D644" t="n">
         <v>-1.105968054304863</v>
@@ -9460,7 +9460,7 @@
         <v>-0.1250610149833215</v>
       </c>
       <c r="C645" t="n">
-        <v>1.461466007099968</v>
+        <v>1.461466007099967</v>
       </c>
       <c r="D645" t="n">
         <v>0.8635536325422095</v>
@@ -9471,7 +9471,7 @@
         <v>-0.9071992045724672</v>
       </c>
       <c r="B646" t="n">
-        <v>-0.3562139415185881</v>
+        <v>-0.356213941518588</v>
       </c>
       <c r="C646" t="n">
         <v>0.1364144572741102</v>
@@ -9485,7 +9485,7 @@
         <v>0.6360429151664754</v>
       </c>
       <c r="B647" t="n">
-        <v>0.2919201981792839</v>
+        <v>0.291920198179284</v>
       </c>
       <c r="C647" t="n">
         <v>-0.167158722899832</v>
@@ -9499,7 +9499,7 @@
         <v>-0.2868300790968371</v>
       </c>
       <c r="B648" t="n">
-        <v>-0.412849213939771</v>
+        <v>-0.4128492139397709</v>
       </c>
       <c r="C648" t="n">
         <v>-0.4227725007514088</v>
@@ -9527,10 +9527,10 @@
         <v>-1.224049699872926</v>
       </c>
       <c r="B650" t="n">
-        <v>-0.3572758956420347</v>
+        <v>-0.3572758956420346</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.1545255819067079</v>
+        <v>-0.1545255819067078</v>
       </c>
       <c r="D650" t="n">
         <v>0.5427102600203998</v>
@@ -9544,7 +9544,7 @@
         <v>0.6158093633425911</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.8017413905467878</v>
+        <v>-0.8017413905467877</v>
       </c>
       <c r="D651" t="n">
         <v>0.659603660557228</v>
@@ -9569,7 +9569,7 @@
         <v>0.09779248017909677</v>
       </c>
       <c r="B653" t="n">
-        <v>-0.01888270885843265</v>
+        <v>-0.01888270885843261</v>
       </c>
       <c r="C653" t="n">
         <v>-1.028949030253541</v>
@@ -9589,7 +9589,7 @@
         <v>2.079669821271156</v>
       </c>
       <c r="D654" t="n">
-        <v>0.06905836677394542</v>
+        <v>0.0690583667739454</v>
       </c>
     </row>
     <row r="655">
@@ -9628,7 +9628,7 @@
         <v>1.087650223314044</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.7962126636351361</v>
+        <v>-0.796212663635136</v>
       </c>
       <c r="D657" t="n">
         <v>-0.3577403072285147</v>
@@ -9656,7 +9656,7 @@
         <v>0.1404104096585588</v>
       </c>
       <c r="C659" t="n">
-        <v>0.6881122939705543</v>
+        <v>0.6881122939705542</v>
       </c>
       <c r="D659" t="n">
         <v>0.8519855758182817</v>
@@ -9667,7 +9667,7 @@
         <v>1.46870712125921</v>
       </c>
       <c r="B660" t="n">
-        <v>-0.1225977193361516</v>
+        <v>-0.1225977193361515</v>
       </c>
       <c r="C660" t="n">
         <v>-0.2998011746007238</v>
@@ -9684,7 +9684,7 @@
         <v>0.1297874471801383</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.8155632078259171</v>
+        <v>-0.815563207825917</v>
       </c>
       <c r="D661" t="n">
         <v>-0.3388604100111969</v>
@@ -9709,7 +9709,7 @@
         <v>0.2748928365363228</v>
       </c>
       <c r="B663" t="n">
-        <v>0.4869482098000119</v>
+        <v>0.486948209800012</v>
       </c>
       <c r="C663" t="n">
         <v>-1.530289379329691</v>
@@ -9726,7 +9726,7 @@
         <v>0.1782835802337971</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.1545255819067079</v>
+        <v>-0.1545255819067078</v>
       </c>
       <c r="D664" t="n">
         <v>0.9487909540440356</v>
@@ -9754,7 +9754,7 @@
         <v>0.8717355173516876</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.3317774881487467</v>
+        <v>-0.3317774881487466</v>
       </c>
       <c r="D666" t="n">
         <v>-2.452655585743624</v>
@@ -9796,7 +9796,7 @@
         <v>0.9697712628650981</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.950579326280878</v>
+        <v>-0.9505793262808779</v>
       </c>
       <c r="D669" t="n">
         <v>0.06176065089193972</v>
@@ -9807,7 +9807,7 @@
         <v>0.5401654599347518</v>
       </c>
       <c r="B670" t="n">
-        <v>-0.03054915074294594</v>
+        <v>-0.03054915074294591</v>
       </c>
       <c r="C670" t="n">
         <v>0.4102016212115288</v>
@@ -9821,10 +9821,10 @@
         <v>-1.03775350583873</v>
       </c>
       <c r="B671" t="n">
-        <v>0.2597091863485822</v>
+        <v>0.2597091863485823</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.6286461654878259</v>
+        <v>-0.6286461654878258</v>
       </c>
       <c r="D671" t="n">
         <v>-0.7723447334023331</v>
@@ -9838,7 +9838,7 @@
         <v>-0.1923226711268793</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.8540569689482921</v>
+        <v>-0.854056968948292</v>
       </c>
       <c r="D672" t="n">
         <v>0.7697991703755135</v>
@@ -9852,7 +9852,7 @@
         <v>0.1400511790433465</v>
       </c>
       <c r="C673" t="n">
-        <v>-1.151917131313528</v>
+        <v>-1.151917131313527</v>
       </c>
       <c r="D673" t="n">
         <v>-0.891038551070309</v>
@@ -9905,10 +9905,10 @@
         <v>0.3096746578868093</v>
       </c>
       <c r="B677" t="n">
-        <v>0.3779302711929687</v>
+        <v>0.3779302711929688</v>
       </c>
       <c r="C677" t="n">
-        <v>0.179054763580224</v>
+        <v>0.1790547635802239</v>
       </c>
       <c r="D677" t="n">
         <v>0.719873377335005</v>
@@ -9922,7 +9922,7 @@
         <v>0.1775822252231445</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.2269657262666243</v>
+        <v>-0.2269657262666242</v>
       </c>
       <c r="D678" t="n">
         <v>0.8446831517324812</v>
@@ -9947,10 +9947,10 @@
         <v>0.5415651308140471</v>
       </c>
       <c r="B680" t="n">
-        <v>-0.2057750023555909</v>
+        <v>-0.2057750023555908</v>
       </c>
       <c r="C680" t="n">
-        <v>0.7556088350169687</v>
+        <v>0.7556088350169686</v>
       </c>
       <c r="D680" t="n">
         <v>1.237352056426129</v>
@@ -9964,10 +9964,10 @@
         <v>0.78960855622625</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.5757546780330246</v>
+        <v>-0.5757546780330245</v>
       </c>
       <c r="D681" t="n">
-        <v>0.07089456625393395</v>
+        <v>0.07089456625393394</v>
       </c>
     </row>
     <row r="682">
@@ -9989,10 +9989,10 @@
         <v>-1.110781333965959</v>
       </c>
       <c r="B683" t="n">
-        <v>-0.06736173569231939</v>
+        <v>-0.06736173569231936</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.1199848605261639</v>
+        <v>-0.1199848605261638</v>
       </c>
       <c r="D683" t="n">
         <v>0.525663266540414</v>
@@ -10003,7 +10003,7 @@
         <v>0.1733747076610394</v>
       </c>
       <c r="B684" t="n">
-        <v>0.3106686150494109</v>
+        <v>0.310668615049411</v>
       </c>
       <c r="C684" t="n">
         <v>-1.448579402847905</v>
@@ -10020,7 +10020,7 @@
         <v>-0.5877158349372036</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.04575709446481342</v>
+        <v>-0.0457570944648134</v>
       </c>
       <c r="D685" t="n">
         <v>0.740575349420927</v>
@@ -10031,10 +10031,10 @@
         <v>-1.554127084982724</v>
       </c>
       <c r="B686" t="n">
-        <v>0.2830591763373808</v>
+        <v>0.2830591763373809</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.4508008425572698</v>
+        <v>-0.4508008425572697</v>
       </c>
       <c r="D686" t="n">
         <v>-1.320850475501468</v>
@@ -10048,7 +10048,7 @@
         <v>0.2543891519994859</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.1711071553692366</v>
+        <v>-0.1711071553692365</v>
       </c>
       <c r="D687" t="n">
         <v>0.3771114328666862</v>
@@ -10073,7 +10073,7 @@
         <v>-0.6335285558982664</v>
       </c>
       <c r="B689" t="n">
-        <v>-0.08116645504833443</v>
+        <v>-0.0811664550483344</v>
       </c>
       <c r="C689" t="n">
         <v>1.318548416433771</v>
@@ -10090,7 +10090,7 @@
         <v>-0.9866499862403346</v>
       </c>
       <c r="C690" t="n">
-        <v>0.9723349299537156</v>
+        <v>0.9723349299537155</v>
       </c>
       <c r="D690" t="n">
         <v>0.2693547726141291</v>
@@ -10115,10 +10115,10 @@
         <v>-0.544089586711301</v>
       </c>
       <c r="B692" t="n">
-        <v>-0.400106790831598</v>
+        <v>-0.4001067908315979</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.01735325995620276</v>
+        <v>-0.01735325995620274</v>
       </c>
       <c r="D692" t="n">
         <v>0.7630993963754528</v>
@@ -10160,7 +10160,7 @@
         <v>-1.41637533313309</v>
       </c>
       <c r="C695" t="n">
-        <v>0.9204340060705852</v>
+        <v>0.9204340060705851</v>
       </c>
       <c r="D695" t="n">
         <v>0.8507708592392124</v>
@@ -10188,7 +10188,7 @@
         <v>0.7485365225536452</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.8728085677236441</v>
+        <v>-0.872808567723644</v>
       </c>
       <c r="D697" t="n">
         <v>0.1055799036105376</v>
@@ -10213,7 +10213,7 @@
         <v>-1.207288641093365</v>
       </c>
       <c r="B699" t="n">
-        <v>0.05440033664487399</v>
+        <v>0.05440033664487402</v>
       </c>
       <c r="C699" t="n">
         <v>-0.1912386322362883</v>
@@ -10230,7 +10230,7 @@
         <v>0.2381040307765289</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.2648651492459967</v>
+        <v>-0.2648651492459966</v>
       </c>
       <c r="D700" t="n">
         <v>0.5372308524439622</v>
@@ -10241,7 +10241,7 @@
         <v>-0.4723704508562133</v>
       </c>
       <c r="B701" t="n">
-        <v>0.2104945920644988</v>
+        <v>0.2104945920644989</v>
       </c>
       <c r="C701" t="n">
         <v>-1.159795567162631</v>
@@ -10258,7 +10258,7 @@
         <v>-0.8004487840219657</v>
       </c>
       <c r="C702" t="n">
-        <v>0.179837999892708</v>
+        <v>0.1798379998927079</v>
       </c>
       <c r="D702" t="n">
         <v>1.013321595256145</v>
@@ -10314,7 +10314,7 @@
         <v>-0.3717891546210065</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.3023671949785942</v>
+        <v>-0.3023671949785941</v>
       </c>
       <c r="D706" t="n">
         <v>0.4952214332641017</v>
@@ -10328,7 +10328,7 @@
         <v>0.99951897904863</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.2506517138106255</v>
+        <v>-0.2506517138106254</v>
       </c>
       <c r="D707" t="n">
         <v>-1.214915890117515</v>
@@ -10353,10 +10353,10 @@
         <v>-1.523614259814088</v>
       </c>
       <c r="B709" t="n">
-        <v>0.4912076585232432</v>
+        <v>0.4912076585232433</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.5252152031518885</v>
+        <v>-0.5252152031518884</v>
       </c>
       <c r="D709" t="n">
         <v>-1.823121656335251</v>
@@ -10367,7 +10367,7 @@
         <v>-0.2871100132726961</v>
       </c>
       <c r="B710" t="n">
-        <v>0.199529505190638</v>
+        <v>0.1995295051906381</v>
       </c>
       <c r="C710" t="n">
         <v>-1.097044516715384</v>
@@ -10387,7 +10387,7 @@
         <v>1.902428051028455</v>
       </c>
       <c r="D711" t="n">
-        <v>-0.01192273849734328</v>
+        <v>-0.01192273849734329</v>
       </c>
     </row>
     <row r="712">
@@ -10412,7 +10412,7 @@
         <v>1.050136283354018</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.3179605085056651</v>
+        <v>-0.317960508505665</v>
       </c>
       <c r="D713" t="n">
         <v>-0.494701955620479</v>
@@ -10423,7 +10423,7 @@
         <v>-0.3821231717364548</v>
       </c>
       <c r="B714" t="n">
-        <v>-0.2510825360437464</v>
+        <v>-0.2510825360437463</v>
       </c>
       <c r="C714" t="n">
         <v>-0.4014546512345651</v>
@@ -10468,7 +10468,7 @@
         <v>-0.3077195190869064</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.09116637149917935</v>
+        <v>-0.09116637149917933</v>
       </c>
       <c r="D717" t="n">
         <v>1.026716435052471</v>
@@ -10482,7 +10482,7 @@
         <v>1.084827697051662</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.6351654559711485</v>
+        <v>-0.6351654559711484</v>
       </c>
       <c r="D718" t="n">
         <v>-0.2085844110079087</v>
@@ -10493,7 +10493,7 @@
         <v>-1.417659174251439</v>
       </c>
       <c r="B719" t="n">
-        <v>-0.2680741441432876</v>
+        <v>-0.2680741441432875</v>
       </c>
       <c r="C719" t="n">
         <v>0.2277997058512864</v>
@@ -10510,7 +10510,7 @@
         <v>0.5935028527598852</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.8832670761315186</v>
+        <v>-0.8832670761315184</v>
       </c>
       <c r="D720" t="n">
         <v>0.3302318476814409</v>
@@ -10538,7 +10538,7 @@
         <v>-0.1094943549907891</v>
       </c>
       <c r="C722" t="n">
-        <v>0.9020740254514752</v>
+        <v>0.9020740254514751</v>
       </c>
       <c r="D722" t="n">
         <v>0.3637165930703598</v>
@@ -10563,13 +10563,13 @@
         <v>-0.5430048417798473</v>
       </c>
       <c r="B724" t="n">
-        <v>0.02961342419522619</v>
+        <v>0.02961342419522622</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.9083306381310062</v>
+        <v>-0.9083306381310061</v>
       </c>
       <c r="D724" t="n">
-        <v>-0.03202676870132015</v>
+        <v>-0.03202676870132016</v>
       </c>
     </row>
     <row r="725">
@@ -10594,7 +10594,7 @@
         <v>0.6384579983207371</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.4861317111589373</v>
+        <v>-0.4861317111589372</v>
       </c>
       <c r="D726" t="n">
         <v>0.2803107628447273</v>
@@ -10608,7 +10608,7 @@
         <v>-1.297795017673491</v>
       </c>
       <c r="C727" t="n">
-        <v>0.6200168075087109</v>
+        <v>0.6200168075087108</v>
       </c>
       <c r="D727" t="n">
         <v>0.993843756156882</v>
@@ -10647,10 +10647,10 @@
         <v>1.14506822219417</v>
       </c>
       <c r="B730" t="n">
-        <v>-0.2107306742235433</v>
+        <v>-0.2107306742235432</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.09175840600596873</v>
+        <v>-0.09175840600596871</v>
       </c>
       <c r="D730" t="n">
         <v>1.043138649888882</v>
@@ -10664,7 +10664,7 @@
         <v>1.052958809616401</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.2484816884978022</v>
+        <v>-0.2484816884978021</v>
       </c>
       <c r="D731" t="n">
         <v>-1.800616442195905</v>
@@ -10692,7 +10692,7 @@
         <v>-0.2348008360647437</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.5842320592975572</v>
+        <v>-0.5842320592975571</v>
       </c>
       <c r="D733" t="n">
         <v>0.7570116888687216</v>
@@ -10706,7 +10706,7 @@
         <v>-0.3254176140630318</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.5536397703864178</v>
+        <v>-0.5536397703864177</v>
       </c>
       <c r="D734" t="n">
         <v>0.1628081207368465</v>
@@ -10714,13 +10714,13 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-0.0311766938163643</v>
+        <v>-0.03117669381636431</v>
       </c>
       <c r="B735" t="n">
         <v>0.8186378111793572</v>
       </c>
       <c r="C735" t="n">
-        <v>0.1050389320504868</v>
+        <v>0.1050389320504867</v>
       </c>
       <c r="D735" t="n">
         <v>0.2803107628447273</v>
@@ -10734,7 +10734,7 @@
         <v>1.503570850850785</v>
       </c>
       <c r="C736" t="n">
-        <v>-1.072764191028381</v>
+        <v>-1.07276419102838</v>
       </c>
       <c r="D736" t="n">
         <v>-1.450561490049375</v>
@@ -10745,10 +10745,10 @@
         <v>-0.4222482366686509</v>
       </c>
       <c r="B737" t="n">
-        <v>-0.04967390444805726</v>
+        <v>-0.04967390444805723</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.6566814182023263</v>
+        <v>-0.6566814182023262</v>
       </c>
       <c r="D737" t="n">
         <v>0.02338878996397451</v>
@@ -10776,7 +10776,7 @@
         <v>-0.310196499709894</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.2658511055452413</v>
+        <v>-0.2658511055452412</v>
       </c>
       <c r="D739" t="n">
         <v>1.138150202468801</v>
@@ -10815,10 +10815,10 @@
         <v>-0.1418840119319407</v>
       </c>
       <c r="B742" t="n">
-        <v>0.07952937348996209</v>
+        <v>0.07952937348996211</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.9898563237157371</v>
+        <v>-0.989856323715737</v>
       </c>
       <c r="D742" t="n">
         <v>0.276049838410395</v>
@@ -10832,7 +10832,7 @@
         <v>1.243043123723017</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.2743377013546266</v>
+        <v>-0.2743377013546265</v>
       </c>
       <c r="D743" t="n">
         <v>-1.568643241224022</v>
@@ -10846,7 +10846,7 @@
         <v>0.2228966013992087</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.1199848605261639</v>
+        <v>-0.1199848605261638</v>
       </c>
       <c r="D744" t="n">
         <v>0.8745143309766024</v>
@@ -10860,7 +10860,7 @@
         <v>0.2129749939314408</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.71963979590876</v>
+        <v>-0.7196397959087599</v>
       </c>
       <c r="D745" t="n">
         <v>-0.9665581399395807</v>
@@ -10874,7 +10874,7 @@
         <v>1.074204734573242</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.3073018141108646</v>
+        <v>-0.3073018141108645</v>
       </c>
       <c r="D746" t="n">
         <v>-0.9720196563415977</v>
@@ -10902,7 +10902,7 @@
         <v>-0.1785179517708643</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.1539335473999185</v>
+        <v>-0.1539335473999184</v>
       </c>
       <c r="D748" t="n">
         <v>0.867207198687007</v>
@@ -10927,10 +10927,10 @@
         <v>0.1005498318113084</v>
       </c>
       <c r="B750" t="n">
-        <v>-0.2967458791031597</v>
+        <v>-0.2967458791031596</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.6928024340251175</v>
+        <v>-0.6928024340251174</v>
       </c>
       <c r="D750" t="n">
         <v>0.9634005104194313</v>
@@ -10958,7 +10958,7 @@
         <v>0.158115347122593</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.07595776521971083</v>
+        <v>-0.07595776521971082</v>
       </c>
       <c r="D752" t="n">
         <v>0.8258079627189582</v>
@@ -10969,7 +10969,7 @@
         <v>0.166460333517321</v>
       </c>
       <c r="B753" t="n">
-        <v>-0.4443537388938886</v>
+        <v>-0.4443537388938885</v>
       </c>
       <c r="C753" t="n">
         <v>1.343819305692446</v>
@@ -10986,7 +10986,7 @@
         <v>-0.9671831081397829</v>
       </c>
       <c r="C754" t="n">
-        <v>0.3482107707146341</v>
+        <v>0.348210770714634</v>
       </c>
       <c r="D754" t="n">
         <v>0.699176113452878</v>
@@ -10997,10 +10997,10 @@
         <v>-1.514026514290916</v>
       </c>
       <c r="B755" t="n">
-        <v>0.255808968240563</v>
+        <v>0.2558089682405631</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.4010584258058968</v>
+        <v>-0.4010584258058967</v>
       </c>
       <c r="D755" t="n">
         <v>-1.249050367630122</v>
@@ -11011,10 +11011,10 @@
         <v>1.068471233324738</v>
       </c>
       <c r="B756" t="n">
-        <v>-0.2234730973317163</v>
+        <v>-0.2234730973317162</v>
       </c>
       <c r="C756" t="n">
-        <v>0.07739529749222829</v>
+        <v>0.07739529749222827</v>
       </c>
       <c r="D756" t="n">
         <v>0.8720801896146689</v>
@@ -11028,7 +11028,7 @@
         <v>-0.9048822557301092</v>
       </c>
       <c r="C757" t="n">
-        <v>0.3991441673882254</v>
+        <v>0.3991441673882253</v>
       </c>
       <c r="D757" t="n">
         <v>0.1049819617285926</v>
@@ -11042,7 +11042,7 @@
         <v>0.148193739654825</v>
       </c>
       <c r="C758" t="n">
-        <v>-1.152493040366825</v>
+        <v>-1.152493040366824</v>
       </c>
       <c r="D758" t="n">
         <v>-0.8721586538529911</v>
@@ -11053,10 +11053,10 @@
         <v>-1.17943519059539</v>
       </c>
       <c r="B759" t="n">
-        <v>-0.4500176082604023</v>
+        <v>-0.4500176082604022</v>
       </c>
       <c r="C759" t="n">
-        <v>0.2874178110485972</v>
+        <v>0.2874178110485971</v>
       </c>
       <c r="D759" t="n">
         <v>1.217295108260101</v>
@@ -11070,7 +11070,7 @@
         <v>-0.9615038431754745</v>
       </c>
       <c r="C760" t="n">
-        <v>0.5069082694411698</v>
+        <v>0.5069082694411697</v>
       </c>
       <c r="D760" t="n">
         <v>0.6949151890185457</v>
@@ -11126,7 +11126,7 @@
         <v>0.2696136875965781</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.6388973466365134</v>
+        <v>-0.6388973466365133</v>
       </c>
       <c r="D764" t="n">
         <v>-0.7942378810483501</v>
@@ -11151,10 +11151,10 @@
         <v>-0.6925246834605606</v>
       </c>
       <c r="B766" t="n">
-        <v>-0.01780501701279575</v>
+        <v>-0.01780501701279572</v>
       </c>
       <c r="C766" t="n">
-        <v>1.333752415440814</v>
+        <v>1.333752415440813</v>
       </c>
       <c r="D766" t="n">
         <v>0.9883634069396856</v>
@@ -11168,7 +11168,7 @@
         <v>0.5545690965587819</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.9784072517361916</v>
+        <v>-0.9784072517361915</v>
       </c>
       <c r="D767" t="n">
         <v>0.3204952822337069</v>
@@ -11196,7 +11196,7 @@
         <v>1.382869364139456</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.702270378861321</v>
+        <v>-0.7022703788613209</v>
       </c>
       <c r="D769" t="n">
         <v>-1.499244317288045</v>
@@ -11235,10 +11235,10 @@
         <v>-0.4783470455108039</v>
       </c>
       <c r="B772" t="n">
-        <v>0.0002420448466786321</v>
+        <v>0.0002420448466786623</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.8574202778195469</v>
+        <v>-0.8574202778195468</v>
       </c>
       <c r="D772" t="n">
         <v>-0.03141470220799061</v>
@@ -11252,10 +11252,10 @@
         <v>0.6759719382807632</v>
       </c>
       <c r="C773" t="n">
-        <v>0.007917629302471876</v>
+        <v>0.007917629302471882</v>
       </c>
       <c r="D773" t="n">
-        <v>0.02155259048398599</v>
+        <v>0.02155259048398598</v>
       </c>
     </row>
     <row r="774">
@@ -11294,10 +11294,10 @@
         <v>1.157734405719984</v>
       </c>
       <c r="C776" t="n">
-        <v>-1.150143331429373</v>
+        <v>-1.150143331429372</v>
       </c>
       <c r="D776" t="n">
-        <v>-0.0788733964600016</v>
+        <v>-0.07887339646000162</v>
       </c>
     </row>
     <row r="777">
@@ -11308,7 +11308,7 @@
         <v>1.050478407749459</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.8789362400507248</v>
+        <v>-0.8789362400507247</v>
       </c>
       <c r="D777" t="n">
         <v>-0.1196935233612849</v>
@@ -11322,7 +11322,7 @@
         <v>0.8193391661900098</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.6075218214128899</v>
+        <v>-0.6075218214128898</v>
       </c>
       <c r="D778" t="n">
         <v>0.9268742653790444</v>
@@ -11350,7 +11350,7 @@
         <v>0.2239571870250736</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.6225184931607453</v>
+        <v>-0.6225184931607451</v>
       </c>
       <c r="D780" t="n">
         <v>-0.3528437752818787</v>
@@ -11361,7 +11361,7 @@
         <v>-1.242735306111517</v>
       </c>
       <c r="B781" t="n">
-        <v>-0.2425875873049644</v>
+        <v>-0.2425875873049643</v>
       </c>
       <c r="C781" t="n">
         <v>0.310315955007688</v>
@@ -11378,7 +11378,7 @@
         <v>-0.3884249533492898</v>
       </c>
       <c r="C782" t="n">
-        <v>0.01088932001748464</v>
+        <v>0.01088932001748465</v>
       </c>
       <c r="D782" t="n">
         <v>0.3527606028397616</v>
@@ -11389,7 +11389,7 @@
         <v>-1.407581543920513</v>
       </c>
       <c r="B783" t="n">
-        <v>-0.02240659013146746</v>
+        <v>-0.02240659013146742</v>
       </c>
       <c r="C783" t="n">
         <v>-0.2696014253003116</v>
@@ -11403,10 +11403,10 @@
         <v>0.05967594295868933</v>
       </c>
       <c r="B784" t="n">
-        <v>0.1885473120970052</v>
+        <v>0.1885473120970053</v>
       </c>
       <c r="C784" t="n">
-        <v>0.6764558947318221</v>
+        <v>0.676455894731822</v>
       </c>
       <c r="D784" t="n">
         <v>0.8732949061937383</v>
@@ -11420,7 +11420,7 @@
         <v>-1.470875749326726</v>
       </c>
       <c r="C785" t="n">
-        <v>0.7860168330310533</v>
+        <v>0.7860168330310532</v>
       </c>
       <c r="D785" t="n">
         <v>0.1244550926240606</v>
@@ -11448,7 +11448,7 @@
         <v>0.2533285663736211</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.7235790138333119</v>
+        <v>-0.7235790138333118</v>
       </c>
       <c r="D787" t="n">
         <v>-1.243541769190157</v>
@@ -11473,7 +11473,7 @@
         <v>1.361807257853037</v>
       </c>
       <c r="B789" t="n">
-        <v>-0.2673659466447262</v>
+        <v>-0.2673659466447261</v>
       </c>
       <c r="C789" t="n">
         <v>0.01641804692913635</v>
@@ -11490,7 +11490,7 @@
         <v>-0.878333402643944</v>
       </c>
       <c r="C790" t="n">
-        <v>0.2526789769537191</v>
+        <v>0.252678976953719</v>
       </c>
       <c r="D790" t="n">
         <v>0.8136325477054959</v>
@@ -11501,10 +11501,10 @@
         <v>-0.974803308042427</v>
       </c>
       <c r="B791" t="n">
-        <v>0.009804421699234329</v>
+        <v>0.009804421699234359</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.4204043627242513</v>
+        <v>-0.4204043627242512</v>
       </c>
       <c r="D791" t="n">
         <v>-0.220731576798602</v>
@@ -11515,10 +11515,10 @@
         <v>1.157350334159985</v>
       </c>
       <c r="B792" t="n">
-        <v>0.09403544785662969</v>
+        <v>0.09403544785662972</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.01083396947288013</v>
+        <v>-0.01083396947288012</v>
       </c>
       <c r="D792" t="n">
         <v>0.8349418780809523</v>
@@ -11532,7 +11532,7 @@
         <v>-0.9236306726002361</v>
       </c>
       <c r="C793" t="n">
-        <v>0.2858283020614974</v>
+        <v>0.2858283020614973</v>
       </c>
       <c r="D793" t="n">
         <v>0.8288541705742212</v>
@@ -11546,7 +11546,7 @@
         <v>-0.1979865404933931</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.8455795876837595</v>
+        <v>-0.8455795876837594</v>
       </c>
       <c r="D794" t="n">
         <v>0.9567054446231655</v>
@@ -11588,7 +11588,7 @@
         <v>-0.1933849673747214</v>
       </c>
       <c r="C797" t="n">
-        <v>1.013593054531917</v>
+        <v>1.013593054531916</v>
       </c>
       <c r="D797" t="n">
         <v>0.5140966222776248</v>
@@ -11602,7 +11602,7 @@
         <v>-0.4808139357159585</v>
       </c>
       <c r="C798" t="n">
-        <v>0.3817747503407863</v>
+        <v>0.3817747503407862</v>
       </c>
       <c r="D798" t="n">
         <v>0.9274816236685791</v>
@@ -11616,7 +11616,7 @@
         <v>1.219693133734218</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.7932640092822553</v>
+        <v>-0.7932640092822552</v>
       </c>
       <c r="D799" t="n">
         <v>0.1889904420399648</v>
@@ -11627,7 +11627,7 @@
         <v>0.2938583769507731</v>
       </c>
       <c r="B800" t="n">
-        <v>0.4310279773652991</v>
+        <v>0.4310279773652992</v>
       </c>
       <c r="C800" t="n">
         <v>0.2157747248184439</v>
@@ -11644,7 +11644,7 @@
         <v>0.8904839342218147</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.5593527881951246</v>
+        <v>-0.5593527881951245</v>
       </c>
       <c r="D801" t="n">
         <v>-0.6511555677230907</v>
@@ -11655,10 +11655,10 @@
         <v>-0.8664687819849758</v>
       </c>
       <c r="B802" t="n">
-        <v>-0.4312572170364349</v>
+        <v>-0.4312572170364348</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.005489533458283507</v>
+        <v>-0.005489533458283499</v>
       </c>
       <c r="D802" t="n">
         <v>1.347571107263389</v>
@@ -11672,7 +11672,7 @@
         <v>-2.520769987834066</v>
       </c>
       <c r="C803" t="n">
-        <v>2.635099548632965</v>
+        <v>2.635099548632964</v>
       </c>
       <c r="D803" t="n">
         <v>-0.7613746185603505</v>
@@ -11686,7 +11686,7 @@
         <v>1.509592240210534</v>
       </c>
       <c r="C804" t="n">
-        <v>-1.037426411518074</v>
+        <v>-1.037426411518073</v>
       </c>
       <c r="D804" t="n">
         <v>-1.304418844257469</v>
@@ -11700,7 +11700,7 @@
         <v>-0.9243491338306609</v>
       </c>
       <c r="C805" t="n">
-        <v>0.6367872791407211</v>
+        <v>0.636787279140721</v>
       </c>
       <c r="D805" t="n">
         <v>1.276948050340753</v>
@@ -11753,7 +11753,7 @@
         <v>-0.1900438875467311</v>
       </c>
       <c r="B809" t="n">
-        <v>0.293322908200589</v>
+        <v>0.2933229082005891</v>
       </c>
       <c r="C809" t="n">
         <v>-1.358760626895697</v>
@@ -11770,7 +11770,7 @@
         <v>-1.520791698621462</v>
       </c>
       <c r="C810" t="n">
-        <v>1.56075272788838</v>
+        <v>1.560752727888379</v>
       </c>
       <c r="D810" t="n">
         <v>0.4556489803684517</v>
@@ -11781,10 +11781,10 @@
         <v>0.868738198849308</v>
       </c>
       <c r="B811" t="n">
-        <v>-0.1625920611631196</v>
+        <v>-0.1625920611631195</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.1638023249372168</v>
+        <v>-0.1638023249372167</v>
       </c>
       <c r="D811" t="n">
         <v>0.9895781235187548</v>
@@ -11812,7 +11812,7 @@
         <v>1.672768470615772</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.4057970054964249</v>
+        <v>-0.4057970054964248</v>
       </c>
       <c r="D813" t="n">
         <v>-3.137557991779342</v>
@@ -11826,7 +11826,7 @@
         <v>-1.75158881578547</v>
       </c>
       <c r="C814" t="n">
-        <v>2.0101921530814</v>
+        <v>2.010192153081399</v>
       </c>
       <c r="D814" t="n">
         <v>1.024282293690538</v>
@@ -11896,7 +11896,7 @@
         <v>1.01260523717422</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.06510763865559432</v>
+        <v>-0.06510763865559431</v>
       </c>
       <c r="D819" t="n">
         <v>-1.004270852336268</v>
@@ -11907,10 +11907,10 @@
         <v>-0.07966479225234946</v>
       </c>
       <c r="B820" t="n">
-        <v>-0.0946290500089092</v>
+        <v>-0.09462905000890917</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.6394962920519424</v>
+        <v>-0.6394962920519423</v>
       </c>
       <c r="D820" t="n">
         <v>0.2930982443515192</v>
@@ -11935,10 +11935,10 @@
         <v>1.236291771752236</v>
       </c>
       <c r="B822" t="n">
-        <v>-0.2680741441432876</v>
+        <v>-0.2680741441432875</v>
       </c>
       <c r="C822" t="n">
-        <v>0.00121404792209421</v>
+        <v>0.001214047922094217</v>
       </c>
       <c r="D822" t="n">
         <v>1.33052740952606</v>
@@ -11966,7 +11966,7 @@
         <v>-1.400449442525346</v>
       </c>
       <c r="C824" t="n">
-        <v>0.9788542204370382</v>
+        <v>0.9788542204370381</v>
       </c>
       <c r="D824" t="n">
         <v>0.7971962082577012</v>
@@ -12008,7 +12008,7 @@
         <v>-1.022042754948631</v>
       </c>
       <c r="C827" t="n">
-        <v>0.6693606951952024</v>
+        <v>0.6693606951952022</v>
       </c>
       <c r="D827" t="n">
         <v>1.113761706811517</v>
@@ -12022,7 +12022,7 @@
         <v>-0.6489561017210125</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.3919797954897221</v>
+        <v>-0.391979795489722</v>
       </c>
       <c r="D828" t="n">
         <v>0.5104430561328271</v>
@@ -12050,7 +12050,7 @@
         <v>-0.8776149414135193</v>
       </c>
       <c r="C830" t="n">
-        <v>0.2347106144908511</v>
+        <v>0.234710614490851</v>
       </c>
       <c r="D830" t="n">
         <v>0.9384376138991772</v>
@@ -12064,7 +12064,7 @@
         <v>1.604104104450909</v>
       </c>
       <c r="C831" t="n">
-        <v>0.2724211393007421</v>
+        <v>0.272421139300742</v>
       </c>
       <c r="D831" t="n">
         <v>-2.058155189773782</v>
@@ -12078,7 +12078,7 @@
         <v>-0.36470889025737</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.01774487811244476</v>
+        <v>-0.01774487811244475</v>
       </c>
       <c r="D832" t="n">
         <v>1.059005296677501</v>
@@ -12092,7 +12092,7 @@
         <v>1.733649506784369</v>
       </c>
       <c r="C833" t="n">
-        <v>0.3371533168913307</v>
+        <v>0.3371533168913306</v>
       </c>
       <c r="D833" t="n">
         <v>-1.193022742471498</v>
@@ -12106,7 +12106,7 @@
         <v>0.6373974126948723</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.3552667451601416</v>
+        <v>-0.3552667451601415</v>
       </c>
       <c r="D834" t="n">
         <v>0.4270372259071947</v>
@@ -12117,10 +12117,10 @@
         <v>0.2422805050487438</v>
       </c>
       <c r="B835" t="n">
-        <v>0.3227113937689085</v>
+        <v>0.3227113937689086</v>
       </c>
       <c r="C835" t="n">
-        <v>-1.36173231761071</v>
+        <v>-1.361732317610709</v>
       </c>
       <c r="D835" t="n">
         <v>-1.252063618058821</v>
@@ -12134,7 +12134,7 @@
         <v>0.2122736389207882</v>
       </c>
       <c r="C836" t="n">
-        <v>-1.131783350810263</v>
+        <v>-1.131783350810262</v>
       </c>
       <c r="D836" t="n">
         <v>-0.885577034668292</v>
@@ -12159,10 +12159,10 @@
         <v>0.1545036450309414</v>
       </c>
       <c r="B838" t="n">
-        <v>0.2242993114205138</v>
+        <v>0.2242993114205139</v>
       </c>
       <c r="C838" t="n">
-        <v>-1.246849979659014</v>
+        <v>-1.246849979659013</v>
       </c>
       <c r="D838" t="n">
         <v>-0.219507443811943</v>
@@ -12204,7 +12204,7 @@
         <v>-0.487538390708337</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.1316297415838303</v>
+        <v>-0.1316297415838302</v>
       </c>
       <c r="D841" t="n">
         <v>0.919567133089449</v>
@@ -12243,7 +12243,7 @@
         <v>0.5511178845652372</v>
       </c>
       <c r="B844" t="n">
-        <v>0.0006012754618909178</v>
+        <v>0.000601275461890948</v>
       </c>
       <c r="C844" t="n">
         <v>0.1887300356756144</v>
@@ -12260,7 +12260,7 @@
         <v>0.8299621286684303</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.209398196504851</v>
+        <v>-0.2093981965048509</v>
       </c>
       <c r="D845" t="n">
         <v>-0.4776582578831496</v>
@@ -12274,7 +12274,7 @@
         <v>0.693317645129585</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.4456683410742864</v>
+        <v>-0.4456683410742863</v>
       </c>
       <c r="D846" t="n">
         <v>-0.4813306568431267</v>
@@ -12302,7 +12302,7 @@
         <v>0.9237555316783812</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.02799605926113228</v>
+        <v>-0.02799605926113227</v>
       </c>
       <c r="D848" t="n">
         <v>-0.8246999596009801</v>
@@ -12330,7 +12330,7 @@
         <v>-2.581308899607222</v>
       </c>
       <c r="C850" t="n">
-        <v>3.629325901882864</v>
+        <v>3.629325901882863</v>
       </c>
       <c r="D850" t="n">
         <v>-0.7504045037183676</v>
@@ -12341,10 +12341,10 @@
         <v>-1.528023223083868</v>
       </c>
       <c r="B851" t="n">
-        <v>0.3060670419307392</v>
+        <v>0.3060670419307393</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.3846772686939154</v>
+        <v>-0.3846772686939153</v>
       </c>
       <c r="D851" t="n">
         <v>-1.229558403919475</v>
@@ -12355,10 +12355,10 @@
         <v>0.03463933010529582</v>
       </c>
       <c r="B852" t="n">
-        <v>-0.3509043419635527</v>
+        <v>-0.3509043419635526</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.02642958663616432</v>
+        <v>-0.02642958663616431</v>
       </c>
       <c r="D852" t="n">
         <v>0.3040542345821173</v>
@@ -12369,10 +12369,10 @@
         <v>-0.3735291925375821</v>
       </c>
       <c r="B853" t="n">
-        <v>0.07776743285344469</v>
+        <v>0.07776743285344472</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.9730858520837268</v>
+        <v>-0.9730858520837267</v>
       </c>
       <c r="D853" t="n">
         <v>0.1457644229995171</v>
@@ -12386,10 +12386,10 @@
         <v>-0.3558600138315051</v>
       </c>
       <c r="C854" t="n">
-        <v>0.9936666012878382</v>
+        <v>0.9936666012878381</v>
       </c>
       <c r="D854" t="n">
-        <v>-0.06733829716263784</v>
+        <v>-0.06733829716263785</v>
       </c>
     </row>
     <row r="855">
@@ -12397,7 +12397,7 @@
         <v>0.7226125590508857</v>
       </c>
       <c r="B855" t="n">
-        <v>0.09793566596464884</v>
+        <v>0.09793566596464887</v>
       </c>
       <c r="C855" t="n">
         <v>0.1697711096410754</v>
@@ -12428,7 +12428,7 @@
         <v>0.2140355795573056</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.5279772629715012</v>
+        <v>-0.527977262971501</v>
       </c>
       <c r="D857" t="n">
         <v>-0.9123667142609451</v>
@@ -12439,10 +12439,10 @@
         <v>0.06023931048760565</v>
       </c>
       <c r="B858" t="n">
-        <v>0.2972231263086081</v>
+        <v>0.2972231263086082</v>
       </c>
       <c r="C858" t="n">
-        <v>-1.343165009732413</v>
+        <v>-1.343165009732412</v>
       </c>
       <c r="D858" t="n">
         <v>-1.337329188783417</v>
@@ -12453,7 +12453,7 @@
         <v>1.086631962983594</v>
       </c>
       <c r="B859" t="n">
-        <v>0.0639627134974296</v>
+        <v>0.06396271349742963</v>
       </c>
       <c r="C859" t="n">
         <v>0.1230072945133548</v>
@@ -12470,7 +12470,7 @@
         <v>0.6051864008641705</v>
       </c>
       <c r="C860" t="n">
-        <v>0.07364037046473151</v>
+        <v>0.0736403704647315</v>
       </c>
       <c r="D860" t="n">
         <v>0.4897410840469052</v>
@@ -12512,7 +12512,7 @@
         <v>1.798430761060985</v>
       </c>
       <c r="C863" t="n">
-        <v>0.3655801877620732</v>
+        <v>0.3655801877620731</v>
       </c>
       <c r="D863" t="n">
         <v>-1.091325540502903</v>
@@ -12526,10 +12526,10 @@
         <v>-1.516891480513443</v>
       </c>
       <c r="C864" t="n">
-        <v>2.161587125012129</v>
+        <v>2.161587125012128</v>
       </c>
       <c r="D864" t="n">
-        <v>0.08977446347125173</v>
+        <v>0.08977446347125172</v>
       </c>
     </row>
     <row r="865">
@@ -12540,7 +12540,7 @@
         <v>-0.2323221448197789</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.779442192003126</v>
+        <v>-0.7794421920031259</v>
       </c>
       <c r="D865" t="n">
         <v>1.052272565250876</v>
@@ -12579,10 +12579,10 @@
         <v>1.511991943201416</v>
       </c>
       <c r="B868" t="n">
-        <v>-0.05463470818194121</v>
+        <v>-0.05463470818194118</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.3244742702620761</v>
+        <v>-0.324474270262076</v>
       </c>
       <c r="D868" t="n">
         <v>1.271439451900788</v>
@@ -12596,7 +12596,7 @@
         <v>1.65295946811978</v>
       </c>
       <c r="C869" t="n">
-        <v>0.273803321028655</v>
+        <v>0.2738033210286549</v>
       </c>
       <c r="D869" t="n">
         <v>-0.9738558558215861</v>
@@ -12607,7 +12607,7 @@
         <v>0.4604542033588884</v>
       </c>
       <c r="B870" t="n">
-        <v>0.4710223191922672</v>
+        <v>0.4710223191922673</v>
       </c>
       <c r="C870" t="n">
         <v>-1.495757872493999</v>
@@ -12624,7 +12624,7 @@
         <v>0.8313819449095073</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.06865523842390418</v>
+        <v>-0.06865523842390417</v>
       </c>
       <c r="D871" t="n">
         <v>0.2504795836006061</v>
@@ -12638,7 +12638,7 @@
         <v>-0.702053807893343</v>
       </c>
       <c r="C872" t="n">
-        <v>0.3345962806946918</v>
+        <v>0.3345962806946917</v>
       </c>
       <c r="D872" t="n">
         <v>0.8544244253840101</v>
@@ -12652,7 +12652,7 @@
         <v>0.7248273019496342</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.7620727749556869</v>
+        <v>-0.7620727749556868</v>
       </c>
       <c r="D873" t="n">
         <v>0.3984207632421428</v>
@@ -12677,7 +12677,7 @@
         <v>1.517275700770755</v>
       </c>
       <c r="B875" t="n">
-        <v>0.03527558293976267</v>
+        <v>0.0352755829397627</v>
       </c>
       <c r="C875" t="n">
         <v>-0.37322819671437</v>
@@ -12722,7 +12722,7 @@
         <v>-1.008597266207828</v>
       </c>
       <c r="C878" t="n">
-        <v>0.6190262439370399</v>
+        <v>0.6190262439370398</v>
       </c>
       <c r="D878" t="n">
         <v>1.017587227894272</v>
@@ -12736,7 +12736,7 @@
         <v>-0.9873513412509871</v>
       </c>
       <c r="C879" t="n">
-        <v>0.3387428258784306</v>
+        <v>0.3387428258784305</v>
       </c>
       <c r="D879" t="n">
         <v>0.2334311776594819</v>
@@ -12778,7 +12778,7 @@
         <v>-0.5218739950347229</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.5291613319850799</v>
+        <v>-0.5291613319850798</v>
       </c>
       <c r="D882" t="n">
         <v>0.8745143309766024</v>
@@ -12789,10 +12789,10 @@
         <v>-1.550487940696557</v>
       </c>
       <c r="B883" t="n">
-        <v>0.3425375024846724</v>
+        <v>0.3425375024846725</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.3951380807380031</v>
+        <v>-0.395138080738003</v>
       </c>
       <c r="D883" t="n">
         <v>-1.265481998874122</v>
@@ -12806,7 +12806,7 @@
         <v>0.2313812864061276</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.5948978949646186</v>
+        <v>-0.5948978949646185</v>
       </c>
       <c r="D884" t="n">
         <v>-0.6846779787423685</v>
@@ -12820,7 +12820,7 @@
         <v>-0.4730254738537606</v>
       </c>
       <c r="C885" t="n">
-        <v>0.9468797497979858</v>
+        <v>0.9468797497979857</v>
       </c>
       <c r="D885" t="n">
         <v>0.2279555366460803</v>
@@ -12831,10 +12831,10 @@
         <v>-0.7305607396054087</v>
       </c>
       <c r="B886" t="n">
-        <v>-0.2082519829785785</v>
+        <v>-0.2082519829785784</v>
       </c>
       <c r="C886" t="n">
-        <v>1.567847927425</v>
+        <v>1.567847927424999</v>
       </c>
       <c r="D886" t="n">
         <v>0.8550317836735448</v>
@@ -12848,7 +12848,7 @@
         <v>0.1312072634212154</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.2382166855318355</v>
+        <v>-0.2382166855318354</v>
       </c>
       <c r="D887" t="n">
         <v>0.163420187230176</v>
@@ -12862,7 +12862,7 @@
         <v>0.9287163354122652</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.6185792752361934</v>
+        <v>-0.6185792752361933</v>
       </c>
       <c r="D888" t="n">
         <v>-0.9860030216122795</v>
@@ -12873,10 +12873,10 @@
         <v>0.2962728092175574</v>
       </c>
       <c r="B889" t="n">
-        <v>-0.02134600450560261</v>
+        <v>-0.02134600450560258</v>
       </c>
       <c r="C889" t="n">
-        <v>-1.07532122722502</v>
+        <v>-1.075321227225019</v>
       </c>
       <c r="D889" t="n">
         <v>0.5993297063960356</v>
@@ -12890,7 +12890,7 @@
         <v>1.057218258339632</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.953527980633759</v>
+        <v>-0.9535279806337589</v>
       </c>
       <c r="D890" t="n">
         <v>-0.1062751425459842</v>
@@ -12901,7 +12901,7 @@
         <v>-1.173941482394157</v>
       </c>
       <c r="B891" t="n">
-        <v>-0.04365251508830843</v>
+        <v>-0.0436525150883084</v>
       </c>
       <c r="C891" t="n">
         <v>-0.1537377383217975</v>
@@ -12918,7 +12918,7 @@
         <v>-0.2779854878791923</v>
       </c>
       <c r="C892" t="n">
-        <v>0.0229143010503271</v>
+        <v>0.02291430105032711</v>
       </c>
       <c r="D892" t="n">
         <v>0.8763411140490013</v>
@@ -12932,7 +12932,7 @@
         <v>-0.6057628967966779</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.03175098628862906</v>
+        <v>-0.03175098628862905</v>
       </c>
       <c r="D893" t="n">
         <v>0.7783210192441782</v>
@@ -12946,7 +12946,7 @@
         <v>-0.2641807685231772</v>
       </c>
       <c r="C894" t="n">
-        <v>0.7804881061194016</v>
+        <v>0.7804881061194014</v>
       </c>
       <c r="D894" t="n">
         <v>1.145447918350806</v>
@@ -12960,7 +12960,7 @@
         <v>1.508172423969457</v>
       </c>
       <c r="C895" t="n">
-        <v>0.27398761192571</v>
+        <v>0.2739876119257099</v>
       </c>
       <c r="D895" t="n">
         <v>-0.8137298447589975</v>
@@ -12971,10 +12971,10 @@
         <v>1.393824729216915</v>
       </c>
       <c r="B896" t="n">
-        <v>0.08058995911582689</v>
+        <v>0.08058995911582692</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.07499023801017173</v>
+        <v>-0.07499023801017171</v>
       </c>
       <c r="D896" t="n">
         <v>1.024889651980073</v>
@@ -12988,7 +12988,7 @@
         <v>-1.107710703566875</v>
       </c>
       <c r="C897" t="n">
-        <v>0.503544960569915</v>
+        <v>0.5035449605699149</v>
       </c>
       <c r="D897" t="n">
         <v>0.6413358298332397</v>
@@ -12999,10 +12999,10 @@
         <v>0.2915839117719184</v>
       </c>
       <c r="B898" t="n">
-        <v>-0.3732055496181292</v>
+        <v>-0.3732055496181291</v>
       </c>
       <c r="C898" t="n">
-        <v>1.182749061666327</v>
+        <v>1.182749061666326</v>
       </c>
       <c r="D898" t="n">
         <v>0.2139486303564242</v>
@@ -13058,7 +13058,7 @@
         <v>1.003059966541437</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.9160247830830549</v>
+        <v>-0.9160247830830548</v>
       </c>
       <c r="D902" t="n">
         <v>0.3393657630434351</v>
@@ -13069,10 +13069,10 @@
         <v>-0.1818225707194707</v>
       </c>
       <c r="B903" t="n">
-        <v>-0.4425832451474851</v>
+        <v>-0.442583245147485</v>
       </c>
       <c r="C903" t="n">
-        <v>1.466188461337004</v>
+        <v>1.466188461337003</v>
       </c>
       <c r="D903" t="n">
         <v>0.7819745853889758</v>
@@ -13086,7 +13086,7 @@
         <v>-0.1282598780806881</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.4604715073802338</v>
+        <v>-0.4604715073802337</v>
       </c>
       <c r="D904" t="n">
         <v>-0.02651817026135457</v>
@@ -13100,7 +13100,7 @@
         <v>-1.473356151193668</v>
       </c>
       <c r="C905" t="n">
-        <v>0.8043768136501632</v>
+        <v>0.8043768136501631</v>
       </c>
       <c r="D905" t="n">
         <v>0.5585392411786598</v>
@@ -13108,10 +13108,10 @@
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>0.01824218575435216</v>
+        <v>0.01824218575435215</v>
       </c>
       <c r="B906" t="n">
-        <v>0.2766956625821917</v>
+        <v>0.2766956625821918</v>
       </c>
       <c r="C906" t="n">
         <v>-1.251203852101939</v>
@@ -13128,7 +13128,7 @@
         <v>1.072425687716952</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.9024102930631126</v>
+        <v>-0.9024102930631125</v>
       </c>
       <c r="D907" t="n">
         <v>-0.1330648221386372</v>
@@ -13156,7 +13156,7 @@
         <v>0.3308539543803871</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.7693753017514936</v>
+        <v>-0.7693753017514935</v>
       </c>
       <c r="D909" t="n">
         <v>0.7606652550135192</v>
@@ -13170,7 +13170,7 @@
         <v>1.243402354338229</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.4130995322922316</v>
+        <v>-0.4130995322922315</v>
       </c>
       <c r="D910" t="n">
         <v>-2.430150371604277</v>
@@ -13184,7 +13184,7 @@
         <v>-0.3611696133865404</v>
       </c>
       <c r="C911" t="n">
-        <v>0.6500101510044213</v>
+        <v>0.6500101510044212</v>
       </c>
       <c r="D911" t="n">
         <v>0.8471172930944147</v>
@@ -13201,7 +13201,7 @@
         <v>2.31081667890246</v>
       </c>
       <c r="D912" t="n">
-        <v>0.06298478387859871</v>
+        <v>0.0629847838785987</v>
       </c>
     </row>
     <row r="913">
@@ -13212,7 +13212,7 @@
         <v>1.040933137116675</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.9924133599123758</v>
+        <v>-0.9924133599123757</v>
       </c>
       <c r="D913" t="n">
         <v>-0.1245429732699725</v>
@@ -13223,10 +13223,10 @@
         <v>1.103218062903242</v>
       </c>
       <c r="B914" t="n">
-        <v>-0.0967502212606389</v>
+        <v>-0.09675022126063887</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.001550315533731643</v>
+        <v>-0.001550315533731636</v>
       </c>
       <c r="D914" t="n">
         <v>1.476622973280018</v>
@@ -13240,7 +13240,7 @@
         <v>-0.5434620443870042</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.5317275827265715</v>
+        <v>-0.5317275827265714</v>
       </c>
       <c r="D915" t="n">
         <v>0.8410295855876836</v>
@@ -13254,7 +13254,7 @@
         <v>-0.9165486976146225</v>
       </c>
       <c r="C916" t="n">
-        <v>0.8693163184999387</v>
+        <v>0.8693163184999386</v>
       </c>
       <c r="D916" t="n">
         <v>0.9579201612022349</v>
@@ -13268,7 +13268,7 @@
         <v>-1.173894667864796</v>
       </c>
       <c r="C917" t="n">
-        <v>1.218870077489118</v>
+        <v>1.218870077489117</v>
       </c>
       <c r="D917" t="n">
         <v>0.5402751770177073</v>
@@ -13310,7 +13310,7 @@
         <v>-1.10877128919274</v>
       </c>
       <c r="C920" t="n">
-        <v>0.7406121632691135</v>
+        <v>0.7406121632691134</v>
       </c>
       <c r="D920" t="n">
         <v>0.1031457622486041</v>
@@ -13321,7 +13321,7 @@
         <v>1.17211686193655</v>
       </c>
       <c r="B921" t="n">
-        <v>-0.3070113215883451</v>
+        <v>-0.307011321588345</v>
       </c>
       <c r="C921" t="n">
         <v>0.1512268381249104</v>
@@ -13338,7 +13338,7 @@
         <v>-1.539916452326573</v>
       </c>
       <c r="C922" t="n">
-        <v>0.9632586032737539</v>
+        <v>0.9632586032737538</v>
       </c>
       <c r="D922" t="n">
         <v>0.5080089147708936</v>
@@ -13352,7 +13352,7 @@
         <v>-1.04115040243397</v>
       </c>
       <c r="C923" t="n">
-        <v>0.5227112138636409</v>
+        <v>0.5227112138636408</v>
       </c>
       <c r="D923" t="n">
         <v>0.415469169183267</v>
@@ -13366,7 +13366,7 @@
         <v>0.3729694674590848</v>
       </c>
       <c r="C924" t="n">
-        <v>-1.358369008739455</v>
+        <v>-1.358369008739454</v>
       </c>
       <c r="D924" t="n">
         <v>-0.5580272966611088</v>
@@ -13377,10 +13377,10 @@
         <v>-1.02085247997124</v>
       </c>
       <c r="B925" t="n">
-        <v>-0.06808019692274396</v>
+        <v>-0.06808019692274393</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.5165304946281689</v>
+        <v>-0.5165304946281688</v>
       </c>
       <c r="D925" t="n">
         <v>-0.1282153722299496</v>
@@ -13408,7 +13408,7 @@
         <v>0.1821837983418162</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.8647228046153534</v>
+        <v>-0.8647228046153533</v>
       </c>
       <c r="D927" t="n">
         <v>-0.6889153621577265</v>
@@ -13422,7 +13422,7 @@
         <v>1.206949000004068</v>
       </c>
       <c r="C928" t="n">
-        <v>-1.07532122722502</v>
+        <v>-1.075321227225019</v>
       </c>
       <c r="D928" t="n">
         <v>0.1128870359001329</v>
@@ -13436,7 +13436,7 @@
         <v>-1.27867026396838</v>
       </c>
       <c r="C929" t="n">
-        <v>1.024443181096033</v>
+        <v>1.024443181096032</v>
       </c>
       <c r="D929" t="n">
         <v>0.9841024825053534</v>
@@ -13450,7 +13450,7 @@
         <v>0.1535137740039213</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.1120879955873547</v>
+        <v>-0.1120879955873546</v>
       </c>
       <c r="D930" t="n">
         <v>0.2608282155416696</v>
@@ -13464,7 +13464,7 @@
         <v>1.136505586982915</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.9786145789953786</v>
+        <v>-0.9786145789953785</v>
       </c>
       <c r="D931" t="n">
         <v>-0.1415866710073019</v>
@@ -13478,7 +13478,7 @@
         <v>-1.223810617159532</v>
       </c>
       <c r="C932" t="n">
-        <v>0.7384467452287167</v>
+        <v>0.7384467452287166</v>
       </c>
       <c r="D932" t="n">
         <v>1.265365869005441</v>
@@ -13506,7 +13506,7 @@
         <v>-0.8248764658564013</v>
       </c>
       <c r="C934" t="n">
-        <v>0.1644497099886107</v>
+        <v>0.1644497099886106</v>
       </c>
       <c r="D934" t="n">
         <v>0.8860823877005302</v>
@@ -13520,7 +13520,7 @@
         <v>0.9988005178182053</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.854264296207479</v>
+        <v>-0.8542642962074789</v>
       </c>
       <c r="D935" t="n">
         <v>0.2297776115146842</v>
@@ -13531,7 +13531,7 @@
         <v>-0.5166910292490968</v>
       </c>
       <c r="B936" t="n">
-        <v>-0.3321436086151899</v>
+        <v>-0.3321436086151898</v>
       </c>
       <c r="C936" t="n">
         <v>-0.3692797642449654</v>
@@ -13548,7 +13548,7 @@
         <v>0.8834019592362009</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.01774487811244476</v>
+        <v>-0.01774487811244475</v>
       </c>
       <c r="D937" t="n">
         <v>-0.5878773087204094</v>
@@ -13562,7 +13562,7 @@
         <v>1.213671744374469</v>
       </c>
       <c r="C938" t="n">
-        <v>0.08884436947177364</v>
+        <v>0.08884436947177363</v>
       </c>
       <c r="D938" t="n">
         <v>-1.843837753032558</v>
@@ -13576,7 +13576,7 @@
         <v>-0.5165642244174898</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.06038518441855851</v>
+        <v>-0.06038518441855849</v>
       </c>
       <c r="D939" t="n">
         <v>0.9859292655777522</v>
@@ -13590,7 +13590,7 @@
         <v>-0.6652412229439696</v>
       </c>
       <c r="C940" t="n">
-        <v>0.6148796987533012</v>
+        <v>0.6148796987533011</v>
       </c>
       <c r="D940" t="n">
         <v>0.8282421040808917</v>
@@ -13618,7 +13618,7 @@
         <v>0.176880870212492</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.7354197039690993</v>
+        <v>-0.7354197039690992</v>
       </c>
       <c r="D942" t="n">
         <v>-0.7656120019757086</v>
@@ -13632,7 +13632,7 @@
         <v>0.1662579077340715</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.5812603685825444</v>
+        <v>-0.5812603685825443</v>
       </c>
       <c r="D943" t="n">
         <v>-0.1933298307126195</v>
@@ -13646,7 +13646,7 @@
         <v>0.4621784035701361</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.4257326732853557</v>
+        <v>-0.4257326732853556</v>
       </c>
       <c r="D944" t="n">
         <v>-1.887059063869211</v>
@@ -13654,1276 +13654,1276 @@
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>-0.8857342652893799</v>
+        <v>-0.9118309061810927</v>
       </c>
       <c r="B945" t="n">
-        <v>-1.285043914744727</v>
+        <v>-0.07788757230277815</v>
       </c>
       <c r="C945" t="n">
-        <v>1.008367184778954</v>
+        <v>-0.3324327215626368</v>
       </c>
       <c r="D945" t="n">
-        <v>1.060771897251766</v>
+        <v>-0.2528626420757418</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>-0.6136543113614957</v>
+        <v>-0.5220722179676979</v>
       </c>
       <c r="B946" t="n">
-        <v>-1.634687984002778</v>
+        <v>-1.492390547189016</v>
       </c>
       <c r="C946" t="n">
-        <v>1.219820757832817</v>
+        <v>1.025794633966909</v>
       </c>
       <c r="D946" t="n">
-        <v>0.6043434907588924</v>
+        <v>0.8167932451368248</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>-1.264685918128231</v>
+        <v>-1.554231829309857</v>
       </c>
       <c r="B947" t="n">
-        <v>-0.4637477278551749</v>
+        <v>0.1040992744335207</v>
       </c>
       <c r="C947" t="n">
-        <v>0.2971314952547252</v>
+        <v>-0.1564976253627986</v>
       </c>
       <c r="D947" t="n">
-        <v>0.950147696500159</v>
+        <v>0.07697717740865655</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>-0.9800014544836775</v>
+        <v>-0.6432672589748407</v>
       </c>
       <c r="B948" t="n">
-        <v>-1.173543444726849</v>
+        <v>-0.6391738253414838</v>
       </c>
       <c r="C948" t="n">
-        <v>1.2153002614075</v>
+        <v>0.5107493398897062</v>
       </c>
       <c r="D948" t="n">
-        <v>0.5479177871134726</v>
+        <v>0.8089290827260338</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>-1.426349120769045</v>
+        <v>-0.8137935614360855</v>
       </c>
       <c r="B949" t="n">
-        <v>-1.368725944812138</v>
+        <v>-1.410842506748551</v>
       </c>
       <c r="C949" t="n">
-        <v>2.012306005607052</v>
+        <v>1.019016257057084</v>
       </c>
       <c r="D949" t="n">
-        <v>0.1785988140517772</v>
+        <v>0.7401074487671817</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>-1.48713789569892</v>
+        <v>-0.05815155893180669</v>
       </c>
       <c r="B950" t="n">
-        <v>-1.79016322166531</v>
+        <v>0.4907081158688701</v>
       </c>
       <c r="C950" t="n">
-        <v>2.52717963508131</v>
+        <v>-1.499167978760645</v>
       </c>
       <c r="D950" t="n">
-        <v>0.09782430421061611</v>
+        <v>-2.364033257069766</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="n">
-        <v>0.02859759971158814</v>
+        <v>-0.9014316359530488</v>
       </c>
       <c r="B951" t="n">
-        <v>0.3160814591305403</v>
+        <v>0.1780956808922915</v>
       </c>
       <c r="C951" t="n">
-        <v>-1.393171810465946</v>
+        <v>-0.8389936635815811</v>
       </c>
       <c r="D951" t="n">
-        <v>-1.499235990139458</v>
+        <v>-0.5676104586128903</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>-0.06658432940703733</v>
+        <v>-1.608628638772381</v>
       </c>
       <c r="B952" t="n">
-        <v>0.4881863107291728</v>
+        <v>0.1349008612309259</v>
       </c>
       <c r="C952" t="n">
-        <v>-1.465172837825119</v>
+        <v>-0.1436552268641132</v>
       </c>
       <c r="D952" t="n">
-        <v>-2.242467813368636</v>
+        <v>0.2381533834761602</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>-0.6339560440131194</v>
+        <v>-1.294954176086153</v>
       </c>
       <c r="B953" t="n">
-        <v>-0.4875388893041947</v>
+        <v>-1.58258296777278</v>
       </c>
       <c r="C953" t="n">
-        <v>0.1700696564783118</v>
+        <v>2.37127399792857</v>
       </c>
       <c r="D953" t="n">
-        <v>0.7566623506148092</v>
+        <v>0.1287370183213444</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>-1.002057223224434</v>
+        <v>0.3605865822422019</v>
       </c>
       <c r="B954" t="n">
-        <v>-0.3867059223476649</v>
+        <v>0.3792046637450708</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.00964262821054275</v>
+        <v>-1.391006346358657</v>
       </c>
       <c r="D954" t="n">
-        <v>1.160021209654708</v>
+        <v>-0.6688455405792284</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>-1.815150230194342</v>
+        <v>-0.7836456732145535</v>
       </c>
       <c r="B955" t="n">
-        <v>-1.398875005356625</v>
+        <v>-2.049330484669778</v>
       </c>
       <c r="C955" t="n">
-        <v>2.302051108129223</v>
+        <v>1.941842693016017</v>
       </c>
       <c r="D955" t="n">
-        <v>0.08248457917321154</v>
+        <v>0.4301176732786782</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>0.308327531529532</v>
+        <v>-0.3599679647830621</v>
       </c>
       <c r="B956" t="n">
-        <v>-0.3001977679534813</v>
+        <v>0.06530928273545258</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.7481197326264309</v>
+        <v>-0.9950731143446592</v>
       </c>
       <c r="D956" t="n">
-        <v>1.181300643711279</v>
+        <v>0.08132112695559832</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>-1.244547700917783</v>
+        <v>-0.1747109095324334</v>
       </c>
       <c r="B957" t="n">
-        <v>-0.3630559173839376</v>
+        <v>-0.5373270918899897</v>
       </c>
       <c r="C957" t="n">
-        <v>0.2749277503019485</v>
+        <v>-0.5367383849880576</v>
       </c>
       <c r="D957" t="n">
-        <v>0.7574850601656881</v>
+        <v>0.8193786286075609</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>-1.507505953306415</v>
+        <v>-1.104175824031653</v>
       </c>
       <c r="B958" t="n">
-        <v>-1.71560990091723</v>
+        <v>0.3178958016520006</v>
       </c>
       <c r="C958" t="n">
-        <v>2.002626392751904</v>
+        <v>-0.379959907695038</v>
       </c>
       <c r="D958" t="n">
-        <v>0.8456072662559068</v>
+        <v>0.0182961582863993</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>-0.6332246776385861</v>
+        <v>-1.019694223058458</v>
       </c>
       <c r="B959" t="n">
-        <v>-0.309652596085315</v>
+        <v>-0.6621848382233791</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.1195157887196446</v>
+        <v>0.04982759469066315</v>
       </c>
       <c r="D959" t="n">
-        <v>1.356144612401422</v>
+        <v>0.7423185959954665</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>-0.1524121448089364</v>
+        <v>-2.202327039714185</v>
       </c>
       <c r="B960" t="n">
-        <v>-0.5258206125018412</v>
+        <v>0.8517065333386956</v>
       </c>
       <c r="C960" t="n">
-        <v>0.008107000263610959</v>
+        <v>-0.2449790133827615</v>
       </c>
       <c r="D960" t="n">
-        <v>0.9327366605595641</v>
+        <v>-2.817671167948232</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="n">
-        <v>-0.9682429291080417</v>
+        <v>-0.9680550697660261</v>
       </c>
       <c r="B961" t="n">
-        <v>-0.3927801601366196</v>
+        <v>0.0004071865141865166</v>
       </c>
       <c r="C961" t="n">
-        <v>0.02007296768507823</v>
+        <v>-0.4109771600358125</v>
       </c>
       <c r="D961" t="n">
-        <v>1.196024456625639</v>
+        <v>-0.2241748007849157</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>-0.8530335534262905</v>
+        <v>-1.029424054944975</v>
       </c>
       <c r="B962" t="n">
-        <v>-0.4242764796230726</v>
+        <v>-0.6152938579930195</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.01141212741439568</v>
+        <v>-0.01037659378910757</v>
       </c>
       <c r="D962" t="n">
-        <v>1.345484825556795</v>
+        <v>0.6829885787804167</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>-0.8183023973020914</v>
+        <v>-1.287254571545769</v>
       </c>
       <c r="B963" t="n">
-        <v>-0.3099903693820864</v>
+        <v>-2.443814696886961</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.1190114448113777</v>
+        <v>2.502617688206836</v>
       </c>
       <c r="D963" t="n">
-        <v>1.249964133566694</v>
+        <v>-0.7399172781614999</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>-0.9077199291294075</v>
+        <v>-1.438528719770311</v>
       </c>
       <c r="B964" t="n">
-        <v>-0.1003582050279933</v>
+        <v>-2.506701598573276</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.3789164383447949</v>
+        <v>3.207280522152383</v>
       </c>
       <c r="D964" t="n">
-        <v>-0.1268898118022515</v>
+        <v>0.1896554582615361</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>-1.588537560679957</v>
+        <v>-0.9639364859509995</v>
       </c>
       <c r="B965" t="n">
-        <v>0.2922076787700732</v>
+        <v>-0.4589432545577068</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.4500844375109414</v>
+        <v>-0.1137430043932258</v>
       </c>
       <c r="D965" t="n">
-        <v>-1.368001843818217</v>
+        <v>0.756705222363666</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>-0.6926886515935954</v>
+        <v>-1.137254326393002</v>
       </c>
       <c r="B966" t="n">
-        <v>-0.5386328035844768</v>
+        <v>-2.099879434359534</v>
       </c>
       <c r="C966" t="n">
-        <v>0.2014821522668908</v>
+        <v>1.706592771686328</v>
       </c>
       <c r="D966" t="n">
-        <v>0.7757708639883292</v>
+        <v>-0.4422554704918035</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>-1.48861467632204</v>
+        <v>-0.9455496164003718</v>
       </c>
       <c r="B967" t="n">
-        <v>-1.700410415715272</v>
+        <v>-0.4048611953653878</v>
       </c>
       <c r="C967" t="n">
-        <v>1.974875230807722</v>
+        <v>-0.005168630394156434</v>
       </c>
       <c r="D967" t="n">
-        <v>0.8432086266332662</v>
+        <v>1.240317700836612</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>-0.2733784225521788</v>
+        <v>-1.02357901802096</v>
       </c>
       <c r="B968" t="n">
-        <v>-0.4143944813845427</v>
+        <v>-0.3883249939071672</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.4216191628082888</v>
+        <v>0.01074320906484076</v>
       </c>
       <c r="D968" t="n">
-        <v>0.8817482441021325</v>
+        <v>0.3536574439003788</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>0.3417752035403338</v>
+        <v>-0.8437611068158055</v>
       </c>
       <c r="B969" t="n">
-        <v>0.3039773042332248</v>
+        <v>-0.5859162211892253</v>
       </c>
       <c r="C969" t="n">
-        <v>-1.44626592029262</v>
+        <v>0.003344685141066762</v>
       </c>
       <c r="D969" t="n">
-        <v>-1.239039951415044</v>
+        <v>0.7594499193392181</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>-0.5705748534910103</v>
+        <v>-0.408462926634034</v>
       </c>
       <c r="B970" t="n">
-        <v>0.1872677712997169</v>
+        <v>-0.9222886378405649</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.6012253392245586</v>
+        <v>0.6309971116078534</v>
       </c>
       <c r="D970" t="n">
-        <v>-0.2611813687077761</v>
+        <v>1.264911349271337</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>-1.084648061120187</v>
+        <v>-0.07362884727756631</v>
       </c>
       <c r="B971" t="n">
-        <v>0.2377070592575146</v>
+        <v>0.5092710094248493</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.5801514188958946</v>
+        <v>-1.474700676477799</v>
       </c>
       <c r="D971" t="n">
-        <v>-0.8397968492922178</v>
+        <v>-2.434495709115378</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>-0.951808342128465</v>
+        <v>-1.011054856866729</v>
       </c>
       <c r="B972" t="n">
-        <v>0.2203186678002733</v>
+        <v>0.2148603024454996</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.5179544542058721</v>
+        <v>-0.4294609018624848</v>
       </c>
       <c r="D972" t="n">
-        <v>-0.7929018545955957</v>
+        <v>-0.06012841427748831</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>-0.9372501707776688</v>
+        <v>-1.188711755417139</v>
       </c>
       <c r="B973" t="n">
-        <v>-1.525271670341209</v>
+        <v>-0.1281149650425197</v>
       </c>
       <c r="C973" t="n">
-        <v>1.001041011958627</v>
+        <v>-0.1310130682436972</v>
       </c>
       <c r="D973" t="n">
-        <v>0.3347824731266237</v>
+        <v>0.4999485077710012</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>-1.507866667409509</v>
+        <v>-0.7992967791688457</v>
       </c>
       <c r="B974" t="n">
-        <v>-1.715040930042927</v>
+        <v>-0.5142504354074587</v>
       </c>
       <c r="C974" t="n">
-        <v>2.001595518666793</v>
+        <v>0.2405360339253627</v>
       </c>
       <c r="D974" t="n">
-        <v>0.8445676421245851</v>
+        <v>0.6651951888570533</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>0.0077377184147261</v>
+        <v>-1.822681024280222</v>
       </c>
       <c r="B975" t="n">
-        <v>0.2698512923198144</v>
+        <v>0.8065443906822161</v>
       </c>
       <c r="C975" t="n">
-        <v>-1.334488350496571</v>
+        <v>-0.3630788862550248</v>
       </c>
       <c r="D975" t="n">
-        <v>-1.253817727378314</v>
+        <v>-2.51700071709431</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>0.05824100986641687</v>
+        <v>-0.7903763063489795</v>
       </c>
       <c r="B976" t="n">
-        <v>0.2517555223091339</v>
+        <v>-1.573736832128666</v>
       </c>
       <c r="C976" t="n">
-        <v>-1.216354848771217</v>
+        <v>1.50861783510505</v>
       </c>
       <c r="D976" t="n">
-        <v>-0.2418752489267109</v>
+        <v>1.020087823475832</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>-2.453403177395592</v>
+        <v>-1.811005659306562</v>
       </c>
       <c r="B977" t="n">
-        <v>0.8189982904111229</v>
+        <v>-1.340324504722331</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.1205821310281839</v>
+        <v>2.225541809511867</v>
       </c>
       <c r="D977" t="n">
-        <v>-2.975642875617224</v>
+        <v>0.3437898293995857</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>-0.186479485225647</v>
+        <v>-1.501944143993532</v>
       </c>
       <c r="B978" t="n">
-        <v>-0.7711793182964779</v>
+        <v>0.3230443591677225</v>
       </c>
       <c r="C978" t="n">
-        <v>0.1016481755268636</v>
+        <v>-0.4219312940662289</v>
       </c>
       <c r="D978" t="n">
-        <v>1.177378394103606</v>
+        <v>-1.320903349838578</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>-0.2767825625445043</v>
+        <v>-1.412803814864452</v>
       </c>
       <c r="B979" t="n">
-        <v>0.2043381168420845</v>
+        <v>-1.380438116682024</v>
       </c>
       <c r="C979" t="n">
-        <v>-1.110152160273071</v>
+        <v>2.024119020986574</v>
       </c>
       <c r="D979" t="n">
-        <v>-0.9132523406738514</v>
+        <v>0.1715324721766597</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>-0.2404416382219383</v>
+        <v>-1.55441736892221</v>
       </c>
       <c r="B980" t="n">
-        <v>-0.4886450472156094</v>
+        <v>0.1073204028332198</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.4540532211932447</v>
+        <v>-0.1390624058809343</v>
       </c>
       <c r="D980" t="n">
-        <v>0.9345433371441842</v>
+        <v>0.3200740665307789</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>0.3009439884172845</v>
+        <v>0.2796198804463829</v>
       </c>
       <c r="B981" t="n">
-        <v>-0.1670088684772113</v>
+        <v>0.304621131443288</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.8525616370154848</v>
+        <v>-1.449067875566388</v>
       </c>
       <c r="D981" t="n">
-        <v>0.7577693362616618</v>
+        <v>-1.313076137663104</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>-0.9014629018544241</v>
+        <v>-1.208447860027658</v>
       </c>
       <c r="B982" t="n">
-        <v>-1.535296883884029</v>
+        <v>-0.4580157440087739</v>
       </c>
       <c r="C982" t="n">
-        <v>0.9984091515505594</v>
+        <v>0.3033634770645663</v>
       </c>
       <c r="D982" t="n">
-        <v>0.455714972132113</v>
+        <v>1.049716234877097</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>-0.335076077016213</v>
+        <v>-0.7831774878118248</v>
       </c>
       <c r="B983" t="n">
-        <v>-1.069178535346893</v>
+        <v>-2.016186319859925</v>
       </c>
       <c r="C983" t="n">
-        <v>0.1426071573606688</v>
+        <v>1.600021228448865</v>
       </c>
       <c r="D983" t="n">
-        <v>0.9317197974820342</v>
+        <v>0.07413823700026659</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>0.2670635014873415</v>
+        <v>-0.7539876153614689</v>
       </c>
       <c r="B984" t="n">
-        <v>0.2558021510188479</v>
+        <v>0.1773498765174823</v>
       </c>
       <c r="C984" t="n">
-        <v>-1.237667158637533</v>
+        <v>-0.8468611846408932</v>
       </c>
       <c r="D984" t="n">
-        <v>-0.2079705108834962</v>
+        <v>-0.504893704331117</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-1.412042239644022</v>
+        <v>-1.18538795558901</v>
       </c>
       <c r="B985" t="n">
-        <v>-2.688778613867099</v>
+        <v>-0.3176829118341148</v>
       </c>
       <c r="C985" t="n">
-        <v>3.800197789007162</v>
+        <v>0.2626008905266662</v>
       </c>
       <c r="D985" t="n">
-        <v>-0.5676218600613812</v>
+        <v>0.7159432415288545</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>-1.009419556476192</v>
+        <v>-0.6941178138839518</v>
       </c>
       <c r="B986" t="n">
-        <v>-1.514891966139158</v>
+        <v>-0.6068371874995004</v>
       </c>
       <c r="C986" t="n">
-        <v>1.049205012593742</v>
+        <v>0.2238055522809526</v>
       </c>
       <c r="D986" t="n">
-        <v>0.2844337368633559</v>
+        <v>0.8061143182067625</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>-0.8658768481740948</v>
+        <v>-1.030499161859612</v>
       </c>
       <c r="B987" t="n">
-        <v>-1.478712522961629</v>
+        <v>-0.6324399624929884</v>
       </c>
       <c r="C987" t="n">
-        <v>0.8055623094914861</v>
+        <v>0.0217592896431336</v>
       </c>
       <c r="D987" t="n">
-        <v>0.3701316946707621</v>
+        <v>0.7329437796249079</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-0.4745463189638444</v>
+        <v>-0.4694890819323093</v>
       </c>
       <c r="B988" t="n">
-        <v>0.1761468046322417</v>
+        <v>0.1274848142131033</v>
       </c>
       <c r="C988" t="n">
-        <v>-1.145432521112733</v>
+        <v>-1.033682403913582</v>
       </c>
       <c r="D988" t="n">
-        <v>-1.054300596885395</v>
+        <v>-0.001652649861067934</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>-0.4713568694692008</v>
+        <v>-0.7535706945025629</v>
       </c>
       <c r="B989" t="n">
-        <v>-0.02266511683136571</v>
+        <v>0.1560161382184719</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.7781423012715812</v>
+        <v>-0.5297819683783194</v>
       </c>
       <c r="D989" t="n">
-        <v>0.01207069974655559</v>
+        <v>-0.4836963435697149</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>-0.2702910062128022</v>
+        <v>-2.287572993144271</v>
       </c>
       <c r="B990" t="n">
-        <v>0.08886680658956965</v>
+        <v>1.230677391451845</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.97652582775237</v>
+        <v>-0.3481114806012044</v>
       </c>
       <c r="D990" t="n">
-        <v>0.2581325116228407</v>
+        <v>-2.421525070844077</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-1.604487314380239</v>
+        <v>-1.500182950267464</v>
       </c>
       <c r="B991" t="n">
-        <v>0.1255993915788806</v>
+        <v>-1.773214153114827</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.1521513133772983</v>
+        <v>2.562856104341063</v>
       </c>
       <c r="D991" t="n">
-        <v>0.2259999962379065</v>
+        <v>-0.09397325791542091</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>0.1276415220889705</v>
+        <v>-0.4143191774759233</v>
       </c>
       <c r="B992" t="n">
-        <v>0.3072802594637691</v>
+        <v>-1.307794514982709</v>
       </c>
       <c r="C992" t="n">
-        <v>-1.309763883251005</v>
+        <v>0.6010585795098069</v>
       </c>
       <c r="D992" t="n">
-        <v>-0.4999663227275203</v>
+        <v>1.015176822501799</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>-0.6421186082439528</v>
+        <v>-1.536016203745711</v>
       </c>
       <c r="B993" t="n">
-        <v>0.06821190381161502</v>
+        <v>0.1094909744082645</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.4433961239498584</v>
+        <v>-0.1307417168781688</v>
       </c>
       <c r="D993" t="n">
-        <v>-0.2122909465488501</v>
+        <v>0.2008730878473456</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>-0.4759144332535769</v>
+        <v>-0.7474413909665185</v>
       </c>
       <c r="B994" t="n">
-        <v>0.1333784750917431</v>
+        <v>0.1387689782511839</v>
       </c>
       <c r="C994" t="n">
-        <v>-1.03656638609947</v>
+        <v>-0.7976482014884723</v>
       </c>
       <c r="D994" t="n">
-        <v>0.001233249527383889</v>
+        <v>-0.3419718464573225</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>-0.3970105165457947</v>
+        <v>-1.04594153599926</v>
       </c>
       <c r="B995" t="n">
-        <v>-0.8386341072447625</v>
+        <v>-1.299016022971147</v>
       </c>
       <c r="C995" t="n">
-        <v>0.5546042039837316</v>
+        <v>1.070544386420481</v>
       </c>
       <c r="D995" t="n">
-        <v>1.069076691669494</v>
+        <v>0.9018495100004447</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>-1.879662869515319</v>
+        <v>-1.536080079717358</v>
       </c>
       <c r="B996" t="n">
-        <v>0.8328475276835833</v>
+        <v>0.3082664169155818</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.3447006022886789</v>
+        <v>-0.3974775259297002</v>
       </c>
       <c r="D996" t="n">
-        <v>-2.542295880975343</v>
+        <v>-1.258988981952865</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>-1.516221457141041</v>
+        <v>-0.07465976708612744</v>
       </c>
       <c r="B997" t="n">
-        <v>-2.534191410011635</v>
+        <v>-0.3196980718958137</v>
       </c>
       <c r="C997" t="n">
-        <v>2.663217292583401</v>
+        <v>-0.711858198175309</v>
       </c>
       <c r="D997" t="n">
-        <v>-0.8674934651470463</v>
+        <v>0.8135199836233109</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>-0.8366304803709443</v>
+        <v>-0.2849764964426891</v>
       </c>
       <c r="B998" t="n">
-        <v>-1.842181960785648</v>
+        <v>0.2005229017371181</v>
       </c>
       <c r="C998" t="n">
-        <v>1.519454322394417</v>
+        <v>-1.099752385178578</v>
       </c>
       <c r="D998" t="n">
-        <v>0.292042676965012</v>
+        <v>-0.9265579864095411</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>-0.4367953741482707</v>
+        <v>-1.173976154160275</v>
       </c>
       <c r="B999" t="n">
-        <v>0.2369795314689776</v>
+        <v>-2.14142080353037</v>
       </c>
       <c r="C999" t="n">
-        <v>-1.113795782330572</v>
+        <v>1.761856577495935</v>
       </c>
       <c r="D999" t="n">
-        <v>-1.095531293098288</v>
+        <v>-0.4178163531483649</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>-1.600498866350581</v>
+        <v>0.6417069633794821</v>
       </c>
       <c r="B1000" t="n">
-        <v>0.1565431901346568</v>
+        <v>0.3912475255349049</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.1123578281440538</v>
+        <v>-1.439359312271944</v>
       </c>
       <c r="D1000" t="n">
-        <v>0.249991433895093</v>
+        <v>-0.6009253716241774</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>-0.7941340459635862</v>
+        <v>-1.362349572324134</v>
       </c>
       <c r="B1001" t="n">
-        <v>-1.509764982858067</v>
+        <v>-1.667520707909727</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.8858535423196575</v>
+        <v>2.43465196127954</v>
       </c>
       <c r="D1001" t="n">
-        <v>0.3405032137061924</v>
+        <v>0.1215645447507853</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>0.1130183814355275</v>
+        <v>-0.7084219234317963</v>
       </c>
       <c r="B1002" t="n">
-        <v>-0.000242052242998992</v>
+        <v>-0.3323023318246784</v>
       </c>
       <c r="C1002" t="n">
-        <v>-1.028573608262251</v>
+        <v>-0.083777662734355</v>
       </c>
       <c r="D1002" t="n">
-        <v>0.4848728292476842</v>
+        <v>1.29320774870359</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>-2.164758217840083</v>
+        <v>-0.08570491997821399</v>
       </c>
       <c r="B1003" t="n">
-        <v>0.859395451818876</v>
+        <v>0.0009339268704264304</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.2561396841105127</v>
+        <v>-1.079517682452763</v>
       </c>
       <c r="D1003" t="n">
-        <v>-2.907855954632134</v>
+        <v>0.2627762988417305</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>0.05078852055374126</v>
+        <v>-0.7199334416742124</v>
       </c>
       <c r="B1004" t="n">
-        <v>0.540103549547331</v>
+        <v>-0.3053109220059553</v>
       </c>
       <c r="C1004" t="n">
-        <v>-1.51322398236056</v>
+        <v>-0.1178498361487803</v>
       </c>
       <c r="D1004" t="n">
-        <v>-2.316282321477993</v>
+        <v>1.278171340033415</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>-1.011696824341024</v>
+        <v>-0.3387830401464222</v>
       </c>
       <c r="B1005" t="n">
-        <v>0.1450373981565671</v>
+        <v>0.1688106066081416</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.4686220670607195</v>
+        <v>-0.7340195734657344</v>
       </c>
       <c r="D1005" t="n">
-        <v>-0.780363899795197</v>
+        <v>-0.6995181289512512</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>-0.6837738797751803</v>
+        <v>-0.3390809824720754</v>
       </c>
       <c r="B1006" t="n">
-        <v>-1.793317278259905</v>
+        <v>0.1669840099065526</v>
       </c>
       <c r="C1006" t="n">
-        <v>1.731051051561669</v>
+        <v>-0.7337026725707176</v>
       </c>
       <c r="D1006" t="n">
-        <v>1.023886949559639</v>
+        <v>-0.6845586609114915</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>-0.4774674082095203</v>
+        <v>-0.1313830512919971</v>
       </c>
       <c r="B1007" t="n">
-        <v>0.1322234501655075</v>
+        <v>0.2793260846906044</v>
       </c>
       <c r="C1007" t="n">
-        <v>-1.036279529230593</v>
+        <v>-1.334624704809862</v>
       </c>
       <c r="D1007" t="n">
-        <v>-0.001857538452184691</v>
+        <v>-1.479187005852802</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>-2.315172272931931</v>
+        <v>-0.7273605104205561</v>
       </c>
       <c r="B1008" t="n">
-        <v>1.252860331267608</v>
+        <v>0.1186561557845971</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.3420601038609515</v>
+        <v>-0.490106797587233</v>
       </c>
       <c r="D1008" t="n">
-        <v>-2.463813604097182</v>
+        <v>-0.4777293419407033</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>-0.08598691624640836</v>
+        <v>-2.489711297037414</v>
       </c>
       <c r="B1009" t="n">
-        <v>-0.094058518381372</v>
+        <v>1.122494209231192</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.639343223400528</v>
+        <v>-0.295055256306761</v>
       </c>
       <c r="D1009" t="n">
-        <v>0.2877568153997228</v>
+        <v>-1.117793277326647</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>-0.7514665792150157</v>
+        <v>-0.09311164439675926</v>
       </c>
       <c r="B1010" t="n">
-        <v>0.1805837184930294</v>
+        <v>-1.048417350253511</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.8273427372213972</v>
+        <v>0.1144996528384485</v>
       </c>
       <c r="D1010" t="n">
-        <v>-0.4208160570633452</v>
+        <v>1.165206552902498</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>-0.6972321812473479</v>
+        <v>-0.2547268997799563</v>
       </c>
       <c r="B1011" t="n">
-        <v>-2.106546322706233</v>
+        <v>-0.02182702310606366</v>
       </c>
       <c r="C1011" t="n">
-        <v>1.928131965421754</v>
+        <v>-0.8744470236838882</v>
       </c>
       <c r="D1011" t="n">
-        <v>0.1149997279969443</v>
+        <v>0.1936480818527938</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>-0.3422041496161936</v>
+        <v>-2.38213119864727</v>
       </c>
       <c r="B1012" t="n">
-        <v>-0.323167297659907</v>
+        <v>1.083695946335514</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.3422806328787149</v>
+        <v>-0.2160973796284049</v>
       </c>
       <c r="D1012" t="n">
-        <v>0.398844460831957</v>
+        <v>-1.131171902</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>-1.421175478140489</v>
+        <v>-1.345121002296289</v>
       </c>
       <c r="B1013" t="n">
-        <v>-2.50285165350251</v>
+        <v>-2.527369524907024</v>
       </c>
       <c r="C1013" t="n">
-        <v>3.197099752611694</v>
+        <v>2.624211445489286</v>
       </c>
       <c r="D1013" t="n">
-        <v>0.1989112833921924</v>
+        <v>-0.6004772529519595</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>-0.4130840875592511</v>
+        <v>-1.123286632133808</v>
       </c>
       <c r="B1014" t="n">
-        <v>-1.298433039005114</v>
+        <v>-1.94679511585801</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.6188071713141075</v>
+        <v>1.903399374306864</v>
       </c>
       <c r="D1014" t="n">
-        <v>0.9952049197210179</v>
+        <v>0.276899197723546</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>-0.8134189549757139</v>
+        <v>-0.3263462176187831</v>
       </c>
       <c r="B1015" t="n">
-        <v>-0.1323321653054083</v>
+        <v>-0.4192527746073253</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.2506834457414192</v>
+        <v>-0.4317557673259083</v>
       </c>
       <c r="D1015" t="n">
-        <v>0.06324457293426347</v>
+        <v>0.8164119894112419</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>0.3630207384753545</v>
+        <v>0.008331456015477044</v>
       </c>
       <c r="B1016" t="n">
-        <v>0.3954461082975547</v>
+        <v>-0.2356003878879225</v>
       </c>
       <c r="C1016" t="n">
-        <v>-1.435247121350854</v>
+        <v>-0.5834246353551688</v>
       </c>
       <c r="D1016" t="n">
-        <v>-0.7970601871705125</v>
+        <v>0.7572499234122144</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>-1.541757569611127</v>
+        <v>-0.1278575349322044</v>
       </c>
       <c r="B1017" t="n">
-        <v>-2.550300918355314</v>
+        <v>0.2038657039598964</v>
       </c>
       <c r="C1017" t="n">
-        <v>2.695349529945275</v>
+        <v>-1.102506323309021</v>
       </c>
       <c r="D1017" t="n">
-        <v>-0.9815781833261517</v>
+        <v>-0.7719259339651502</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>0.2533267681206974</v>
+        <v>-0.4735861225503212</v>
       </c>
       <c r="B1018" t="n">
-        <v>0.4840568389243297</v>
+        <v>0.2017770766535096</v>
       </c>
       <c r="C1018" t="n">
-        <v>-1.512918646944845</v>
+        <v>-1.156515865140841</v>
       </c>
       <c r="D1018" t="n">
-        <v>-2.174257054077366</v>
+        <v>-0.9966418275505856</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>-0.810967481007013</v>
+        <v>0.543831668729066</v>
       </c>
       <c r="B1019" t="n">
-        <v>-0.4993443951710501</v>
+        <v>-0.03346169456693089</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.2614330811772302</v>
+        <v>-1.001557698400404</v>
       </c>
       <c r="D1019" t="n">
-        <v>0.6315905646036487</v>
+        <v>0.6083583838217228</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>0.4370924824295055</v>
+        <v>0.5212197996308242</v>
       </c>
       <c r="B1020" t="n">
-        <v>0.3926417407332854</v>
+        <v>-0.04378833856523331</v>
       </c>
       <c r="C1020" t="n">
-        <v>-1.435349608813889</v>
+        <v>-0.9906090125158287</v>
       </c>
       <c r="D1020" t="n">
-        <v>-0.6890491183507836</v>
+        <v>0.5893265430530341</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>-1.034442505395992</v>
+        <v>-0.0689759567546904</v>
       </c>
       <c r="B1021" t="n">
-        <v>-0.3923011540320318</v>
+        <v>0.4877429941705297</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.2847408432159996</v>
+        <v>-1.448658255499881</v>
       </c>
       <c r="D1021" t="n">
-        <v>0.6262692312093077</v>
+        <v>-2.181827558286662</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-1.447353545206655</v>
+        <v>-1.282969458457708</v>
       </c>
       <c r="B1022" t="n">
-        <v>-1.715822573418267</v>
+        <v>-1.840044627006814</v>
       </c>
       <c r="C1022" t="n">
-        <v>2.002564865278083</v>
+        <v>1.987281100784323</v>
       </c>
       <c r="D1022" t="n">
-        <v>0.8993788879503908</v>
+        <v>0.6534825145365666</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>-1.901582306900098</v>
+        <v>-1.793096500497978</v>
       </c>
       <c r="B1023" t="n">
-        <v>0.7932386116458655</v>
+        <v>-1.319007271926034</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.3488788940545079</v>
+        <v>2.211672751656089</v>
       </c>
       <c r="D1023" t="n">
-        <v>-2.516297486916872</v>
+        <v>0.398580158749327</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>0.191067557343303</v>
+        <v>-1.031223586841243</v>
       </c>
       <c r="B1024" t="n">
-        <v>-0.1658249775020074</v>
+        <v>-0.36470889025737</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.8450605210656879</v>
+        <v>0.05862397898254454</v>
       </c>
       <c r="D1024" t="n">
-        <v>0.8304147119725618</v>
+        <v>1.081541706167324</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>-0.329316888914751</v>
+        <v>-2.424177042570613</v>
       </c>
       <c r="B1025" t="n">
-        <v>0.147043155773377</v>
+        <v>1.105266979046301</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.7272025125400339</v>
+        <v>-0.2426534190145299</v>
       </c>
       <c r="D1025" t="n">
-        <v>-0.4847650072271442</v>
+        <v>-1.159728544073255</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>-1.755159006408206</v>
+        <v>-0.9939938846922287</v>
       </c>
       <c r="B1026" t="n">
-        <v>-2.583611702227683</v>
+        <v>-0.02265328993597624</v>
       </c>
       <c r="C1026" t="n">
-        <v>3.620972854125181</v>
+        <v>-0.4604640603275612</v>
       </c>
       <c r="D1026" t="n">
-        <v>-0.9465837171717819</v>
+        <v>-0.1821762838203028</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>-1.422594843526569</v>
+        <v>-0.9010718850398725</v>
       </c>
       <c r="B1027" t="n">
-        <v>-2.449792722555061</v>
+        <v>-1.50818664847745</v>
       </c>
       <c r="C1027" t="n">
-        <v>3.053112661807497</v>
+        <v>0.9438661784880032</v>
       </c>
       <c r="D1027" t="n">
-        <v>0.2475895997670055</v>
+        <v>0.2978914064692275</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>-0.5274568351033715</v>
+        <v>-0.06398741936470682</v>
       </c>
       <c r="B1028" t="n">
-        <v>0.01652864049324455</v>
+        <v>-0.317709450844896</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.8864344023340892</v>
+        <v>-0.7153045697620252</v>
       </c>
       <c r="D1028" t="n">
-        <v>-0.01872889202509027</v>
+        <v>0.8031326679973245</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>-0.4774177190400115</v>
+        <v>0.06924839683261214</v>
       </c>
       <c r="B1029" t="n">
-        <v>0.1322604064790185</v>
+        <v>0.4834783732309242</v>
       </c>
       <c r="C1029" t="n">
-        <v>-1.036288707536739</v>
+        <v>-1.517305612724317</v>
       </c>
       <c r="D1029" t="n">
-        <v>-0.001758645236138473</v>
+        <v>-2.314826537509426</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>-1.036859454598799</v>
+        <v>0.2006638517893947</v>
       </c>
       <c r="B1030" t="n">
-        <v>0.2490528851047333</v>
+        <v>0.3032224872449025</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.6149188544903765</v>
+        <v>-1.426087115937877</v>
       </c>
       <c r="D1030" t="n">
-        <v>-0.7726830663233617</v>
+        <v>-1.352789007573867</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>0.6141181776620135</v>
+        <v>-0.7407600967877728</v>
       </c>
       <c r="B1031" t="n">
-        <v>0.4319031048879253</v>
+        <v>-1.53019568925854</v>
       </c>
       <c r="C1031" t="n">
-        <v>-1.459336745022444</v>
+        <v>1.368940059319365</v>
       </c>
       <c r="D1031" t="n">
-        <v>-0.7278496081611557</v>
+        <v>1.185723953237225</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>-0.8169878501381628</v>
+        <v>-0.6921958213730608</v>
       </c>
       <c r="B1032" t="n">
-        <v>-1.394345077557261</v>
+        <v>-2.111360792308874</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.9569428106736947</v>
+        <v>1.945945022624634</v>
       </c>
       <c r="D1032" t="n">
-        <v>0.7738158980847455</v>
+        <v>0.3929161559599555</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>-0.7218793724529498</v>
+        <v>-0.8615822245428886</v>
       </c>
       <c r="B1033" t="n">
-        <v>-2.073597592461183</v>
+        <v>-0.5868923540859102</v>
       </c>
       <c r="C1033" t="n">
-        <v>1.899081435201238</v>
+        <v>-0.02328873128671716</v>
       </c>
       <c r="D1033" t="n">
-        <v>0.002742295298867881</v>
+        <v>0.7492121176838791</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>-1.318187284559344</v>
+        <v>-0.6928405261490789</v>
       </c>
       <c r="B1034" t="n">
-        <v>-2.543451130006611</v>
+        <v>-1.599001378061526</v>
       </c>
       <c r="C1034" t="n">
-        <v>3.233980012273314</v>
+        <v>1.507273551464895</v>
       </c>
       <c r="D1034" t="n">
-        <v>0.2893580550285362</v>
+        <v>1.147095179169073</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>0.04796699277964486</v>
+        <v>-0.8055646144247687</v>
       </c>
       <c r="B1035" t="n">
-        <v>0.2659675565906544</v>
+        <v>-1.804935752211091</v>
       </c>
       <c r="C1035" t="n">
-        <v>-1.239532758943413</v>
+        <v>1.424989907726128</v>
       </c>
       <c r="D1035" t="n">
-        <v>-0.3328188269124329</v>
+        <v>0.1956317275505341</v>
       </c>
     </row>
   </sheetData>
